--- a/Ejercicio-3/Parte-B/3.B.35/Code/datos/tablas_figuras.xlsx
+++ b/Ejercicio-3/Parte-B/3.B.35/Code/datos/tablas_figuras.xlsx
@@ -49,6 +49,7 @@
     <sheet name="MCCA_complementariedad" sheetId="40" state="visible" r:id="rId40"/>
     <sheet name="MCCA_saldos" sheetId="41" state="visible" r:id="rId41"/>
     <sheet name="MCCA_reparto_manuf" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet name="MERCOSUR_tipo_cambio" sheetId="43" state="visible" r:id="rId43"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -37884,6 +37885,543 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Tipo de cambio real bilateral peso argentino-real (índice 1995 = 100) y saldo comercial de Argentina con Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Banco Mundial (WDI): tipos de cambio oficiales (PA.NUS.FCRF) y deflactores del PIB (NY.GDP.DEFL.ZS), porque WDI no tiene el IPC argentino; saldo con las exportaciones declaradas por cada país (Code/datos_comercio.py). Cálculo propio (Code/figuras_afinidad.py).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Tipo de cambio real (1995 = 100)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Saldo de Argentina con Brasil (miles de millones USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1980</v>
+      </c>
+      <c r="B5" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1981</v>
+      </c>
+      <c r="B6" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1982</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1983</v>
+      </c>
+      <c r="B8" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1984</v>
+      </c>
+      <c r="B9" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B10" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1986</v>
+      </c>
+      <c r="B11" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1987</v>
+      </c>
+      <c r="B12" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1988</v>
+      </c>
+      <c r="B13" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1989</v>
+      </c>
+      <c r="B14" t="n">
+        <v>132.2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B15" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B17" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B18" t="n">
+        <v>56</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B19" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B20" t="n">
+        <v>100</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B21" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B22" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B23" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B24" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B26" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B27" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B28" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B29" t="n">
+        <v>125</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-1.96</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B30" t="n">
+        <v>145.2</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-3.64</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B31" t="n">
+        <v>160.5</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-3.59</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B32" t="n">
+        <v>168.3</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-3.92</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B33" t="n">
+        <v>160.3</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-4.33</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B34" t="n">
+        <v>161.3</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B35" t="n">
+        <v>172.7</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-4.07</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B36" t="n">
+        <v>167.7</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-5.38</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B37" t="n">
+        <v>140</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-1.53</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B38" t="n">
+        <v>132.3</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-3.66</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B39" t="n">
+        <v>137.9</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B40" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-2.7</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B41" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-4.38</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B42" t="n">
+        <v>111.7</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-8.31</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B43" t="n">
+        <v>121.7</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-3.62</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B44" t="n">
+        <v>135</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B45" t="n">
+        <v>115</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B46" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B47" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-2.71</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B48" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-4.86</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B49" t="n">
+        <v>101.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Ejercicio-3/Parte-B/3.B.35/Code/datos/tablas_figuras.xlsx
+++ b/Ejercicio-3/Parte-B/3.B.35/Code/datos/tablas_figuras.xlsx
@@ -37891,13 +37891,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Tipo de cambio real bilateral peso argentino-real (índice 1995 = 100) y saldo comercial de Argentina con Brasil</t>
+          <t>Tipo de cambio real bilateral peso argentino-real (índice 1995 = 100), cuota intrarregional y saldo de Argentina con Brasil</t>
         </is>
       </c>
     </row>
@@ -37922,6 +37922,11 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>Saldo de Argentina con Brasil (miles de millones USD)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Cuota intrarregional (%)</t>
         </is>
       </c>
     </row>
@@ -37935,6 +37940,9 @@
       <c r="C5" t="n">
         <v>-0.33</v>
       </c>
+      <c r="D5" t="n">
+        <v>11.58</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -37946,6 +37954,9 @@
       <c r="C6" t="n">
         <v>-0.29</v>
       </c>
+      <c r="D6" t="n">
+        <v>8.91</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -37957,6 +37968,9 @@
       <c r="C7" t="n">
         <v>-0.08</v>
       </c>
+      <c r="D7" t="n">
+        <v>8.07</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -37968,6 +37982,9 @@
       <c r="C8" t="n">
         <v>-0.3</v>
       </c>
+      <c r="D8" t="n">
+        <v>5.91</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -37979,6 +37996,9 @@
       <c r="C9" t="n">
         <v>-0.37</v>
       </c>
+      <c r="D9" t="n">
+        <v>6.32</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -37990,6 +38010,9 @@
       <c r="C10" t="n">
         <v>-0.05</v>
       </c>
+      <c r="D10" t="n">
+        <v>5.55</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -38001,6 +38024,9 @@
       <c r="C11" t="n">
         <v>0.19</v>
       </c>
+      <c r="D11" t="n">
+        <v>8.58</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -38012,6 +38038,9 @@
       <c r="C12" t="n">
         <v>-0.07000000000000001</v>
       </c>
+      <c r="D12" t="n">
+        <v>7.4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -38023,6 +38052,9 @@
       <c r="C13" t="n">
         <v>-0.15</v>
       </c>
+      <c r="D13" t="n">
+        <v>6.55</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -38034,6 +38066,9 @@
       <c r="C14" t="n">
         <v>0.5600000000000001</v>
       </c>
+      <c r="D14" t="n">
+        <v>8.24</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -38045,6 +38080,9 @@
       <c r="C15" t="n">
         <v>0.78</v>
       </c>
+      <c r="D15" t="n">
+        <v>8.890000000000001</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -38056,6 +38094,9 @@
       <c r="C16" t="n">
         <v>0.01</v>
       </c>
+      <c r="D16" t="n">
+        <v>11.12</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -38067,6 +38108,9 @@
       <c r="C17" t="n">
         <v>-1.37</v>
       </c>
+      <c r="D17" t="n">
+        <v>14.3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -38078,6 +38122,9 @@
       <c r="C18" t="n">
         <v>-0.84</v>
       </c>
+      <c r="D18" t="n">
+        <v>18.52</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -38089,6 +38136,9 @@
       <c r="C19" t="n">
         <v>-0.48</v>
       </c>
+      <c r="D19" t="n">
+        <v>19.47</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -38100,6 +38150,9 @@
       <c r="C20" t="n">
         <v>1.44</v>
       </c>
+      <c r="D20" t="n">
+        <v>20.61</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -38111,6 +38164,9 @@
       <c r="C21" t="n">
         <v>1.44</v>
       </c>
+      <c r="D21" t="n">
+        <v>22.82</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -38122,6 +38178,9 @@
       <c r="C22" t="n">
         <v>1.37</v>
       </c>
+      <c r="D22" t="n">
+        <v>24.71</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -38133,6 +38192,9 @@
       <c r="C23" t="n">
         <v>1.2</v>
       </c>
+      <c r="D23" t="n">
+        <v>25.03</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -38144,6 +38206,9 @@
       <c r="C24" t="n">
         <v>0.33</v>
       </c>
+      <c r="D24" t="n">
+        <v>20.4</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -38155,6 +38220,9 @@
       <c r="C25" t="n">
         <v>0.76</v>
       </c>
+      <c r="D25" t="n">
+        <v>22.19</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -38166,6 +38234,9 @@
       <c r="C26" t="n">
         <v>1.21</v>
       </c>
+      <c r="D26" t="n">
+        <v>18.56</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -38177,6 +38248,9 @@
       <c r="C27" t="n">
         <v>2.49</v>
       </c>
+      <c r="D27" t="n">
+        <v>12.83</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -38188,6 +38262,9 @@
       <c r="C28" t="n">
         <v>0.1</v>
       </c>
+      <c r="D28" t="n">
+        <v>13.06</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -38199,6 +38276,9 @@
       <c r="C29" t="n">
         <v>-1.96</v>
       </c>
+      <c r="D29" t="n">
+        <v>13.58</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -38210,6 +38290,9 @@
       <c r="C30" t="n">
         <v>-3.64</v>
       </c>
+      <c r="D30" t="n">
+        <v>13.71</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -38221,6 +38304,9 @@
       <c r="C31" t="n">
         <v>-3.59</v>
       </c>
+      <c r="D31" t="n">
+        <v>14.27</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -38232,6 +38318,9 @@
       <c r="C32" t="n">
         <v>-3.92</v>
       </c>
+      <c r="D32" t="n">
+        <v>15.16</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -38243,6 +38332,9 @@
       <c r="C33" t="n">
         <v>-4.33</v>
       </c>
+      <c r="D33" t="n">
+        <v>15.51</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -38254,6 +38346,9 @@
       <c r="C34" t="n">
         <v>-1.4</v>
       </c>
+      <c r="D34" t="n">
+        <v>15.62</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -38265,6 +38360,9 @@
       <c r="C35" t="n">
         <v>-4.07</v>
       </c>
+      <c r="D35" t="n">
+        <v>15.85</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -38276,6 +38374,9 @@
       <c r="C36" t="n">
         <v>-5.38</v>
       </c>
+      <c r="D36" t="n">
+        <v>15.38</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -38287,6 +38388,9 @@
       <c r="C37" t="n">
         <v>-1.53</v>
       </c>
+      <c r="D37" t="n">
+        <v>13.03</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -38298,6 +38402,9 @@
       <c r="C38" t="n">
         <v>-3.66</v>
       </c>
+      <c r="D38" t="n">
+        <v>13.85</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -38342,6 +38449,9 @@
       <c r="C42" t="n">
         <v>-8.31</v>
       </c>
+      <c r="D42" t="n">
+        <v>13.88</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -38353,6 +38463,9 @@
       <c r="C43" t="n">
         <v>-3.62</v>
       </c>
+      <c r="D43" t="n">
+        <v>13.36</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -38364,6 +38477,9 @@
       <c r="C44" t="n">
         <v>0.59</v>
       </c>
+      <c r="D44" t="n">
+        <v>11.07</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -38375,6 +38491,9 @@
       <c r="C45" t="n">
         <v>-0.55</v>
       </c>
+      <c r="D45" t="n">
+        <v>10.37</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -38386,6 +38505,9 @@
       <c r="C46" t="n">
         <v>-0.11</v>
       </c>
+      <c r="D46" t="n">
+        <v>10.57</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -38397,6 +38519,9 @@
       <c r="C47" t="n">
         <v>-2.71</v>
       </c>
+      <c r="D47" t="n">
+        <v>10.31</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -38407,6 +38532,9 @@
       </c>
       <c r="C48" t="n">
         <v>-4.86</v>
+      </c>
+      <c r="D48" t="n">
+        <v>11.3</v>
       </c>
     </row>
     <row r="49">

--- a/Ejercicio-3/Parte-B/3.B.35/Code/datos/tablas_figuras.xlsx
+++ b/Ejercicio-3/Parte-B/3.B.35/Code/datos/tablas_figuras.xlsx
@@ -50,6 +50,11 @@
     <sheet name="MCCA_saldos" sheetId="41" state="visible" r:id="rId41"/>
     <sheet name="MCCA_reparto_manuf" sheetId="42" state="visible" r:id="rId42"/>
     <sheet name="MERCOSUR_tipo_cambio" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet name="MERCOSUR_intensidad" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet name="MERCOSUR_composicion" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet name="MERCOSUR_complementariedad" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet name="MERCOSUR_saldos" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet name="MERCOSUR_reparto_manuf" sheetId="48" state="visible" r:id="rId48"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -38550,6 +38555,9004 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Intensidad del comercio intrarregional. MERCOSUR: Argentina, Brasil, Paraguay y Uruguay; Venezuela de 2012 a 2016 (suspendida desde entonces); Bolivia, miembro desde 2024, aún sin datos (la serie empieza antes del Tratado de Asunción)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Cuota: exportaciones a los socios / exportaciones totales (Code/datos_comercio.py). Peso: importaciones de mercancías de los miembros / importaciones mundiales (Banco Mundial, WDI, TM.VAL.MRCH.CD.WT). Intensidad = cuota / peso. Cálculo propio (Code/indicadores_bloque.py).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Cuota intrarregional (%)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Peso en las importaciones mundiales (%)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Intensidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1970</v>
+      </c>
+      <c r="B5" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.548</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B6" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.6843</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1972</v>
+      </c>
+      <c r="B7" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.6974</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1974</v>
+      </c>
+      <c r="B8" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2.2336</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1975</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.1142</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1976</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.7968</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1977</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.6501</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1978</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.5441</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1979</v>
+      </c>
+      <c r="B13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.7364</v>
+      </c>
+      <c r="D13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1980</v>
+      </c>
+      <c r="B14" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.8912</v>
+      </c>
+      <c r="D14" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1981</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.7919</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1982</v>
+      </c>
+      <c r="B16" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.5135</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1983</v>
+      </c>
+      <c r="B17" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.2531</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1984</v>
+      </c>
+      <c r="B18" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.092</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1986</v>
+      </c>
+      <c r="B20" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.0172</v>
+      </c>
+      <c r="D20" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1987</v>
+      </c>
+      <c r="B21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.9635</v>
+      </c>
+      <c r="D21" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1988</v>
+      </c>
+      <c r="B22" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.8016</v>
+      </c>
+      <c r="D22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1989</v>
+      </c>
+      <c r="B23" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.8344</v>
+      </c>
+      <c r="D23" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B24" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8292</v>
+      </c>
+      <c r="D24" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B25" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="D25" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B26" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.0609</v>
+      </c>
+      <c r="D26" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B27" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1.2526</v>
+      </c>
+      <c r="D27" t="n">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B28" t="n">
+        <v>19.47</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1.4312</v>
+      </c>
+      <c r="D28" t="n">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B29" t="n">
+        <v>20.61</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1.5353</v>
+      </c>
+      <c r="D29" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B30" t="n">
+        <v>22.82</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1.5858</v>
+      </c>
+      <c r="D30" t="n">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B31" t="n">
+        <v>24.71</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1.7851</v>
+      </c>
+      <c r="D31" t="n">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B32" t="n">
+        <v>25.03</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1.7504</v>
+      </c>
+      <c r="D32" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B33" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1.4045</v>
+      </c>
+      <c r="D33" t="n">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B34" t="n">
+        <v>22.19</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1.3416</v>
+      </c>
+      <c r="D34" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B35" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1.3056</v>
+      </c>
+      <c r="D35" t="n">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B36" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.9333</v>
+      </c>
+      <c r="D36" t="n">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B37" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.8864</v>
+      </c>
+      <c r="D37" t="n">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B38" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1.0003</v>
+      </c>
+      <c r="D38" t="n">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B39" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1.0503</v>
+      </c>
+      <c r="D39" t="n">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B40" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1.1316</v>
+      </c>
+      <c r="D40" t="n">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B41" t="n">
+        <v>15.16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1.2844</v>
+      </c>
+      <c r="D41" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B42" t="n">
+        <v>15.51</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1.5623</v>
+      </c>
+      <c r="D42" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B43" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1.4665</v>
+      </c>
+      <c r="D43" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B44" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1.7322</v>
+      </c>
+      <c r="D44" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B45" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1.8161</v>
+      </c>
+      <c r="D45" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B46" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="C46" t="n">
+        <v>2.0171</v>
+      </c>
+      <c r="D46" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B47" t="n">
+        <v>13.85</v>
+      </c>
+      <c r="C47" t="n">
+        <v>2.0964</v>
+      </c>
+      <c r="D47" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B48" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1.4042</v>
+      </c>
+      <c r="D48" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B49" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1.4116</v>
+      </c>
+      <c r="D49" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B50" t="n">
+        <v>11.07</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="D50" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B51" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1.2629</v>
+      </c>
+      <c r="D51" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B52" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1.4208</v>
+      </c>
+      <c r="D52" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B53" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="C53" t="n">
+        <v>1.5639</v>
+      </c>
+      <c r="D53" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B54" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1.4568</v>
+      </c>
+      <c r="D54" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N100"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Exportaciones dentro y fuera del bloque por secciones de la CUCI. MERCOSUR: Argentina, Brasil, Paraguay y Uruguay; Venezuela de 2012 a 2016 (suspendida desde entonces); Bolivia, miembro desde 2024, aún sin datos (la serie empieza antes del Tratado de Asunción)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>UN Comtrade, API pública: CUCI Rev. 1 (hasta 1995), Rev. 3 (1996-2006) y Rev. 4 (desde 2007); exportaciones declaradas por cada miembro al mundo y a cada socio, dólares corrientes, en millones. Fuera = mundo menos socios. La división 68 (metales no ferrosos) se resta de la sección 6, como en la definición de manufacturas de la UNCTAD. Cálculo propio (Code/indicadores_bloque.py).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Destino</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Sección 0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sección 3</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sección 4</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sección 5</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Sección 6 (sin la división 68)</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Sección 7</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Sección 8</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Sección 9</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>División 68 (metales no ferrosos)</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Manufacturas (5-8 sin 68, %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1970</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>177.31</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="E5" t="n">
+        <v>81.48999999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="G5" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="H5" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="I5" t="n">
+        <v>72.83</v>
+      </c>
+      <c r="J5" t="n">
+        <v>64.51000000000001</v>
+      </c>
+      <c r="K5" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="N5" t="n">
+        <v>36.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1970</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2753.33</v>
+      </c>
+      <c r="D6" t="n">
+        <v>45.04</v>
+      </c>
+      <c r="E6" t="n">
+        <v>849.76</v>
+      </c>
+      <c r="F6" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="G6" t="n">
+        <v>169.43</v>
+      </c>
+      <c r="H6" t="n">
+        <v>82.45</v>
+      </c>
+      <c r="I6" t="n">
+        <v>258.31</v>
+      </c>
+      <c r="J6" t="n">
+        <v>100.73</v>
+      </c>
+      <c r="K6" t="n">
+        <v>54.29</v>
+      </c>
+      <c r="L6" t="n">
+        <v>21.44</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="N6" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>140.51</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E7" t="n">
+        <v>90.02</v>
+      </c>
+      <c r="F7" t="n">
+        <v>12.98</v>
+      </c>
+      <c r="G7" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="H7" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="I7" t="n">
+        <v>74.89</v>
+      </c>
+      <c r="J7" t="n">
+        <v>76.83</v>
+      </c>
+      <c r="K7" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="M7" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="N7" t="n">
+        <v>40.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2819.85</v>
+      </c>
+      <c r="D8" t="n">
+        <v>51.14</v>
+      </c>
+      <c r="E8" t="n">
+        <v>759.86</v>
+      </c>
+      <c r="F8" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="G8" t="n">
+        <v>156.87</v>
+      </c>
+      <c r="H8" t="n">
+        <v>99.23999999999999</v>
+      </c>
+      <c r="I8" t="n">
+        <v>251.49</v>
+      </c>
+      <c r="J8" t="n">
+        <v>140.67</v>
+      </c>
+      <c r="K8" t="n">
+        <v>77.45999999999999</v>
+      </c>
+      <c r="L8" t="n">
+        <v>78.59</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="N8" t="n">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1972</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>183.68</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>71.88</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="G9" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="H9" t="n">
+        <v>23.52</v>
+      </c>
+      <c r="I9" t="n">
+        <v>76.23</v>
+      </c>
+      <c r="J9" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="K9" t="n">
+        <v>15.19</v>
+      </c>
+      <c r="L9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N9" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1972</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3500.24</v>
+      </c>
+      <c r="D10" t="n">
+        <v>68.81</v>
+      </c>
+      <c r="E10" t="n">
+        <v>947.1799999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>36.09</v>
+      </c>
+      <c r="G10" t="n">
+        <v>156.2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>125.23</v>
+      </c>
+      <c r="I10" t="n">
+        <v>471.29</v>
+      </c>
+      <c r="J10" t="n">
+        <v>263.97</v>
+      </c>
+      <c r="K10" t="n">
+        <v>142.83</v>
+      </c>
+      <c r="L10" t="n">
+        <v>30.74</v>
+      </c>
+      <c r="M10" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="N10" t="n">
+        <v>17.4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1974</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>398.08</v>
+      </c>
+      <c r="D11" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="E11" t="n">
+        <v>113.15</v>
+      </c>
+      <c r="F11" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="G11" t="n">
+        <v>32.13</v>
+      </c>
+      <c r="H11" t="n">
+        <v>69.83</v>
+      </c>
+      <c r="I11" t="n">
+        <v>213.65</v>
+      </c>
+      <c r="J11" t="n">
+        <v>196.92</v>
+      </c>
+      <c r="K11" t="n">
+        <v>34.52</v>
+      </c>
+      <c r="L11" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="N11" t="n">
+        <v>46.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1974</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>6055.58</v>
+      </c>
+      <c r="D12" t="n">
+        <v>137.47</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1973.17</v>
+      </c>
+      <c r="F12" t="n">
+        <v>103.88</v>
+      </c>
+      <c r="G12" t="n">
+        <v>417.44</v>
+      </c>
+      <c r="H12" t="n">
+        <v>308.12</v>
+      </c>
+      <c r="I12" t="n">
+        <v>887.55</v>
+      </c>
+      <c r="J12" t="n">
+        <v>828.48</v>
+      </c>
+      <c r="K12" t="n">
+        <v>440.66</v>
+      </c>
+      <c r="L12" t="n">
+        <v>142.56</v>
+      </c>
+      <c r="M12" t="n">
+        <v>23.56</v>
+      </c>
+      <c r="N12" t="n">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1975</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>299.85</v>
+      </c>
+      <c r="D13" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="E13" t="n">
+        <v>127.7</v>
+      </c>
+      <c r="F13" t="n">
+        <v>72.28</v>
+      </c>
+      <c r="G13" t="n">
+        <v>19.18</v>
+      </c>
+      <c r="H13" t="n">
+        <v>65.95</v>
+      </c>
+      <c r="I13" t="n">
+        <v>173.62</v>
+      </c>
+      <c r="J13" t="n">
+        <v>198.13</v>
+      </c>
+      <c r="K13" t="n">
+        <v>43.96</v>
+      </c>
+      <c r="L13" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="M13" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="N13" t="n">
+        <v>46.6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1975</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>5387.09</v>
+      </c>
+      <c r="D14" t="n">
+        <v>192.47</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2319.47</v>
+      </c>
+      <c r="F14" t="n">
+        <v>147.12</v>
+      </c>
+      <c r="G14" t="n">
+        <v>354.96</v>
+      </c>
+      <c r="H14" t="n">
+        <v>252.8</v>
+      </c>
+      <c r="I14" t="n">
+        <v>750.1900000000001</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1105.44</v>
+      </c>
+      <c r="K14" t="n">
+        <v>456.57</v>
+      </c>
+      <c r="L14" t="n">
+        <v>165.14</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20.71</v>
+      </c>
+      <c r="N14" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1976</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>452.45</v>
+      </c>
+      <c r="D15" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="E15" t="n">
+        <v>84.69</v>
+      </c>
+      <c r="F15" t="n">
+        <v>209.7</v>
+      </c>
+      <c r="G15" t="n">
+        <v>21.52</v>
+      </c>
+      <c r="H15" t="n">
+        <v>69.29000000000001</v>
+      </c>
+      <c r="I15" t="n">
+        <v>167.39</v>
+      </c>
+      <c r="J15" t="n">
+        <v>218.2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>45.71</v>
+      </c>
+      <c r="L15" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="M15" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="N15" t="n">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1976</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>6969.59</v>
+      </c>
+      <c r="D16" t="n">
+        <v>206.28</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2501.86</v>
+      </c>
+      <c r="F16" t="n">
+        <v>62.78</v>
+      </c>
+      <c r="G16" t="n">
+        <v>534.84</v>
+      </c>
+      <c r="H16" t="n">
+        <v>247.44</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1084.87</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1158.05</v>
+      </c>
+      <c r="K16" t="n">
+        <v>518.47</v>
+      </c>
+      <c r="L16" t="n">
+        <v>159.71</v>
+      </c>
+      <c r="M16" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="N16" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1977</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>534.6</v>
+      </c>
+      <c r="D17" t="n">
+        <v>19.65</v>
+      </c>
+      <c r="E17" t="n">
+        <v>115.75</v>
+      </c>
+      <c r="F17" t="n">
+        <v>197.51</v>
+      </c>
+      <c r="G17" t="n">
+        <v>35.18</v>
+      </c>
+      <c r="H17" t="n">
+        <v>81.56</v>
+      </c>
+      <c r="I17" t="n">
+        <v>231.48</v>
+      </c>
+      <c r="J17" t="n">
+        <v>314.12</v>
+      </c>
+      <c r="K17" t="n">
+        <v>69.41</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="M17" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="N17" t="n">
+        <v>43.3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1977</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>9089.049999999999</v>
+      </c>
+      <c r="D18" t="n">
+        <v>241.2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2757.76</v>
+      </c>
+      <c r="F18" t="n">
+        <v>48.29</v>
+      </c>
+      <c r="G18" t="n">
+        <v>812.39</v>
+      </c>
+      <c r="H18" t="n">
+        <v>307.99</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1370.49</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1568.55</v>
+      </c>
+      <c r="K18" t="n">
+        <v>711.3</v>
+      </c>
+      <c r="L18" t="n">
+        <v>98.38</v>
+      </c>
+      <c r="M18" t="n">
+        <v>25.76</v>
+      </c>
+      <c r="N18" t="n">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1978</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>585.87</v>
+      </c>
+      <c r="D19" t="n">
+        <v>20.87</v>
+      </c>
+      <c r="E19" t="n">
+        <v>134.68</v>
+      </c>
+      <c r="F19" t="n">
+        <v>80.38</v>
+      </c>
+      <c r="G19" t="n">
+        <v>54.58</v>
+      </c>
+      <c r="H19" t="n">
+        <v>119.32</v>
+      </c>
+      <c r="I19" t="n">
+        <v>281.53</v>
+      </c>
+      <c r="J19" t="n">
+        <v>373.16</v>
+      </c>
+      <c r="K19" t="n">
+        <v>94.76000000000001</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="M19" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="N19" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1978</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>8499.190000000001</v>
+      </c>
+      <c r="D20" t="n">
+        <v>299.15</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2879.51</v>
+      </c>
+      <c r="F20" t="n">
+        <v>168.74</v>
+      </c>
+      <c r="G20" t="n">
+        <v>864.62</v>
+      </c>
+      <c r="H20" t="n">
+        <v>400.86</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1956.11</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2093.53</v>
+      </c>
+      <c r="K20" t="n">
+        <v>887.05</v>
+      </c>
+      <c r="L20" t="n">
+        <v>123.66</v>
+      </c>
+      <c r="M20" t="n">
+        <v>60.89</v>
+      </c>
+      <c r="N20" t="n">
+        <v>29.3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1979</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1032.7</v>
+      </c>
+      <c r="D21" t="n">
+        <v>24.28</v>
+      </c>
+      <c r="E21" t="n">
+        <v>234.56</v>
+      </c>
+      <c r="F21" t="n">
+        <v>49.05</v>
+      </c>
+      <c r="G21" t="n">
+        <v>111.71</v>
+      </c>
+      <c r="H21" t="n">
+        <v>220.14</v>
+      </c>
+      <c r="I21" t="n">
+        <v>501.44</v>
+      </c>
+      <c r="J21" t="n">
+        <v>588.58</v>
+      </c>
+      <c r="K21" t="n">
+        <v>158.13</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="M21" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="N21" t="n">
+        <v>49.9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1979</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>9363.76</v>
+      </c>
+      <c r="D22" t="n">
+        <v>341.84</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3399.22</v>
+      </c>
+      <c r="F22" t="n">
+        <v>228.64</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1036.16</v>
+      </c>
+      <c r="H22" t="n">
+        <v>534.34</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2634.84</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2394.17</v>
+      </c>
+      <c r="K22" t="n">
+        <v>993.12</v>
+      </c>
+      <c r="L22" t="n">
+        <v>147.19</v>
+      </c>
+      <c r="M22" t="n">
+        <v>126.74</v>
+      </c>
+      <c r="N22" t="n">
+        <v>30.9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1980</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>850.16</v>
+      </c>
+      <c r="D23" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>306.91</v>
+      </c>
+      <c r="F23" t="n">
+        <v>206.14</v>
+      </c>
+      <c r="G23" t="n">
+        <v>62.95</v>
+      </c>
+      <c r="H23" t="n">
+        <v>292.85</v>
+      </c>
+      <c r="I23" t="n">
+        <v>552.01</v>
+      </c>
+      <c r="J23" t="n">
+        <v>870.47</v>
+      </c>
+      <c r="K23" t="n">
+        <v>223.62</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="M23" t="n">
+        <v>23.69</v>
+      </c>
+      <c r="N23" t="n">
+        <v>56.7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1980</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>11480.42</v>
+      </c>
+      <c r="D24" t="n">
+        <v>333.78</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4345.95</v>
+      </c>
+      <c r="F24" t="n">
+        <v>429.25</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1169.25</v>
+      </c>
+      <c r="H24" t="n">
+        <v>876.8</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2816.58</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3079.79</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1074.44</v>
+      </c>
+      <c r="L24" t="n">
+        <v>280.48</v>
+      </c>
+      <c r="M24" t="n">
+        <v>214.04</v>
+      </c>
+      <c r="N24" t="n">
+        <v>30.1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1981</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>573.53</v>
+      </c>
+      <c r="D25" t="n">
+        <v>21.72</v>
+      </c>
+      <c r="E25" t="n">
+        <v>314.81</v>
+      </c>
+      <c r="F25" t="n">
+        <v>335.96</v>
+      </c>
+      <c r="G25" t="n">
+        <v>40.31</v>
+      </c>
+      <c r="H25" t="n">
+        <v>273.63</v>
+      </c>
+      <c r="I25" t="n">
+        <v>492.96</v>
+      </c>
+      <c r="J25" t="n">
+        <v>769.13</v>
+      </c>
+      <c r="K25" t="n">
+        <v>178.75</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="M25" t="n">
+        <v>19.87</v>
+      </c>
+      <c r="N25" t="n">
+        <v>56.7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1981</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>12995.56</v>
+      </c>
+      <c r="D26" t="n">
+        <v>413.39</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4612.66</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1473.8</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1249.74</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1158.12</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3287.94</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3899.99</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1238.44</v>
+      </c>
+      <c r="L26" t="n">
+        <v>357.01</v>
+      </c>
+      <c r="M26" t="n">
+        <v>235.89</v>
+      </c>
+      <c r="N26" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1982</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>507.2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>16.23</v>
+      </c>
+      <c r="E27" t="n">
+        <v>387.12</v>
+      </c>
+      <c r="F27" t="n">
+        <v>167.71</v>
+      </c>
+      <c r="G27" t="n">
+        <v>36.62</v>
+      </c>
+      <c r="H27" t="n">
+        <v>316</v>
+      </c>
+      <c r="I27" t="n">
+        <v>414.17</v>
+      </c>
+      <c r="J27" t="n">
+        <v>373.11</v>
+      </c>
+      <c r="K27" t="n">
+        <v>113.27</v>
+      </c>
+      <c r="L27" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="M27" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="N27" t="n">
+        <v>51.7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1982</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>10611</v>
+      </c>
+      <c r="D28" t="n">
+        <v>547.71</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3704.91</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1826.6</v>
+      </c>
+      <c r="G28" t="n">
+        <v>955.6</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1047.24</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2989.29</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3608.99</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1063.62</v>
+      </c>
+      <c r="L28" t="n">
+        <v>253.64</v>
+      </c>
+      <c r="M28" t="n">
+        <v>190.44</v>
+      </c>
+      <c r="N28" t="n">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1983</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>409.06</v>
+      </c>
+      <c r="D29" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="E29" t="n">
+        <v>199.14</v>
+      </c>
+      <c r="F29" t="n">
+        <v>135.42</v>
+      </c>
+      <c r="G29" t="n">
+        <v>53.66</v>
+      </c>
+      <c r="H29" t="n">
+        <v>263.45</v>
+      </c>
+      <c r="I29" t="n">
+        <v>337.43</v>
+      </c>
+      <c r="J29" t="n">
+        <v>320.94</v>
+      </c>
+      <c r="K29" t="n">
+        <v>82.56</v>
+      </c>
+      <c r="L29" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="M29" t="n">
+        <v>14.76</v>
+      </c>
+      <c r="N29" t="n">
+        <v>54.8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1983</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>12498.29</v>
+      </c>
+      <c r="D30" t="n">
+        <v>534.39</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3760.53</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1358.21</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1105.57</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1389.28</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3648.61</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2995.41</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1188.3</v>
+      </c>
+      <c r="L30" t="n">
+        <v>293.98</v>
+      </c>
+      <c r="M30" t="n">
+        <v>431.05</v>
+      </c>
+      <c r="N30" t="n">
+        <v>31.6</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1984</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>448.47</v>
+      </c>
+      <c r="D31" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="E31" t="n">
+        <v>266.67</v>
+      </c>
+      <c r="F31" t="n">
+        <v>140.54</v>
+      </c>
+      <c r="G31" t="n">
+        <v>85.37</v>
+      </c>
+      <c r="H31" t="n">
+        <v>361.32</v>
+      </c>
+      <c r="I31" t="n">
+        <v>470.35</v>
+      </c>
+      <c r="J31" t="n">
+        <v>391.22</v>
+      </c>
+      <c r="K31" t="n">
+        <v>91.98999999999999</v>
+      </c>
+      <c r="L31" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="M31" t="n">
+        <v>24.28</v>
+      </c>
+      <c r="N31" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1984</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>12642.65</v>
+      </c>
+      <c r="D32" t="n">
+        <v>534.4299999999999</v>
+      </c>
+      <c r="E32" t="n">
+        <v>4617.51</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2021.81</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1728.9</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1734.54</v>
+      </c>
+      <c r="I32" t="n">
+        <v>4774.78</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3369.84</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1745.18</v>
+      </c>
+      <c r="L32" t="n">
+        <v>313.92</v>
+      </c>
+      <c r="M32" t="n">
+        <v>589.72</v>
+      </c>
+      <c r="N32" t="n">
+        <v>34.1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>423.25</v>
+      </c>
+      <c r="D33" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="E33" t="n">
+        <v>203.65</v>
+      </c>
+      <c r="F33" t="n">
+        <v>161.01</v>
+      </c>
+      <c r="G33" t="n">
+        <v>83.15000000000001</v>
+      </c>
+      <c r="H33" t="n">
+        <v>288.6</v>
+      </c>
+      <c r="I33" t="n">
+        <v>294.03</v>
+      </c>
+      <c r="J33" t="n">
+        <v>369.36</v>
+      </c>
+      <c r="K33" t="n">
+        <v>86.68000000000001</v>
+      </c>
+      <c r="L33" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="M33" t="n">
+        <v>25.45</v>
+      </c>
+      <c r="N33" t="n">
+        <v>53.2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>11053.03</v>
+      </c>
+      <c r="D34" t="n">
+        <v>522.54</v>
+      </c>
+      <c r="E34" t="n">
+        <v>4632.3</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2082.18</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1762.03</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1836.76</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4741.97</v>
+      </c>
+      <c r="J34" t="n">
+        <v>4053.83</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1652.22</v>
+      </c>
+      <c r="L34" t="n">
+        <v>290.32</v>
+      </c>
+      <c r="M34" t="n">
+        <v>611.8</v>
+      </c>
+      <c r="N34" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1986</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>820.62</v>
+      </c>
+      <c r="D35" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="E35" t="n">
+        <v>294.98</v>
+      </c>
+      <c r="F35" t="n">
+        <v>139.61</v>
+      </c>
+      <c r="G35" t="n">
+        <v>58.43</v>
+      </c>
+      <c r="H35" t="n">
+        <v>342.62</v>
+      </c>
+      <c r="I35" t="n">
+        <v>435.46</v>
+      </c>
+      <c r="J35" t="n">
+        <v>367.26</v>
+      </c>
+      <c r="K35" t="n">
+        <v>109.88</v>
+      </c>
+      <c r="L35" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="M35" t="n">
+        <v>35.88</v>
+      </c>
+      <c r="N35" t="n">
+        <v>47.9</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1986</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>9653.360000000001</v>
+      </c>
+      <c r="D36" t="n">
+        <v>470.16</v>
+      </c>
+      <c r="E36" t="n">
+        <v>3665.43</v>
+      </c>
+      <c r="F36" t="n">
+        <v>718.3</v>
+      </c>
+      <c r="G36" t="n">
+        <v>877.33</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1317.17</v>
+      </c>
+      <c r="I36" t="n">
+        <v>4532.51</v>
+      </c>
+      <c r="J36" t="n">
+        <v>4005.06</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1821.02</v>
+      </c>
+      <c r="L36" t="n">
+        <v>184.62</v>
+      </c>
+      <c r="M36" t="n">
+        <v>682.09</v>
+      </c>
+      <c r="N36" t="n">
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1987</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>554.65</v>
+      </c>
+      <c r="D37" t="n">
+        <v>17.91</v>
+      </c>
+      <c r="E37" t="n">
+        <v>276.3</v>
+      </c>
+      <c r="F37" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="G37" t="n">
+        <v>33.74</v>
+      </c>
+      <c r="H37" t="n">
+        <v>428.58</v>
+      </c>
+      <c r="I37" t="n">
+        <v>456.22</v>
+      </c>
+      <c r="J37" t="n">
+        <v>514.04</v>
+      </c>
+      <c r="K37" t="n">
+        <v>103.83</v>
+      </c>
+      <c r="L37" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="M37" t="n">
+        <v>32.26</v>
+      </c>
+      <c r="N37" t="n">
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1987</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>9832.309999999999</v>
+      </c>
+      <c r="D38" t="n">
+        <v>493.27</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4156.89</v>
+      </c>
+      <c r="F38" t="n">
+        <v>928.6799999999999</v>
+      </c>
+      <c r="G38" t="n">
+        <v>964.4400000000001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1700.96</v>
+      </c>
+      <c r="I38" t="n">
+        <v>5105.48</v>
+      </c>
+      <c r="J38" t="n">
+        <v>5262.1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1998.91</v>
+      </c>
+      <c r="L38" t="n">
+        <v>202.49</v>
+      </c>
+      <c r="M38" t="n">
+        <v>960.37</v>
+      </c>
+      <c r="N38" t="n">
+        <v>44.5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1988</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>514.35</v>
+      </c>
+      <c r="D39" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="E39" t="n">
+        <v>348.5</v>
+      </c>
+      <c r="F39" t="n">
+        <v>122.22</v>
+      </c>
+      <c r="G39" t="n">
+        <v>57.71</v>
+      </c>
+      <c r="H39" t="n">
+        <v>570.24</v>
+      </c>
+      <c r="I39" t="n">
+        <v>567.8</v>
+      </c>
+      <c r="J39" t="n">
+        <v>606.24</v>
+      </c>
+      <c r="K39" t="n">
+        <v>114.57</v>
+      </c>
+      <c r="L39" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M39" t="n">
+        <v>24.53</v>
+      </c>
+      <c r="N39" t="n">
+        <v>63.2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1988</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>12019.6</v>
+      </c>
+      <c r="D40" t="n">
+        <v>633.85</v>
+      </c>
+      <c r="E40" t="n">
+        <v>5612.8</v>
+      </c>
+      <c r="F40" t="n">
+        <v>920.3099999999999</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1327.41</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2371.59</v>
+      </c>
+      <c r="I40" t="n">
+        <v>8364.49</v>
+      </c>
+      <c r="J40" t="n">
+        <v>6346.45</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2279.46</v>
+      </c>
+      <c r="L40" t="n">
+        <v>280.7</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1777.39</v>
+      </c>
+      <c r="N40" t="n">
+        <v>46.2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1989</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1048.08</v>
+      </c>
+      <c r="D41" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="E41" t="n">
+        <v>486.88</v>
+      </c>
+      <c r="F41" t="n">
+        <v>132.7</v>
+      </c>
+      <c r="G41" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="H41" t="n">
+        <v>619.27</v>
+      </c>
+      <c r="I41" t="n">
+        <v>669.27</v>
+      </c>
+      <c r="J41" t="n">
+        <v>589.63</v>
+      </c>
+      <c r="K41" t="n">
+        <v>156.43</v>
+      </c>
+      <c r="L41" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="M41" t="n">
+        <v>45.96</v>
+      </c>
+      <c r="N41" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1989</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>10896.85</v>
+      </c>
+      <c r="D42" t="n">
+        <v>669.67</v>
+      </c>
+      <c r="E42" t="n">
+        <v>6143.34</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1042.62</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1366.72</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2257.77</v>
+      </c>
+      <c r="I42" t="n">
+        <v>8890.719999999999</v>
+      </c>
+      <c r="J42" t="n">
+        <v>6934.22</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2474.9</v>
+      </c>
+      <c r="L42" t="n">
+        <v>320.21</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1716.06</v>
+      </c>
+      <c r="N42" t="n">
+        <v>48.1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1303.99</v>
+      </c>
+      <c r="D43" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="E43" t="n">
+        <v>404.63</v>
+      </c>
+      <c r="F43" t="n">
+        <v>139.1</v>
+      </c>
+      <c r="G43" t="n">
+        <v>39.01</v>
+      </c>
+      <c r="H43" t="n">
+        <v>602.09</v>
+      </c>
+      <c r="I43" t="n">
+        <v>684</v>
+      </c>
+      <c r="J43" t="n">
+        <v>712.21</v>
+      </c>
+      <c r="K43" t="n">
+        <v>169.36</v>
+      </c>
+      <c r="L43" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="M43" t="n">
+        <v>32.63</v>
+      </c>
+      <c r="N43" t="n">
+        <v>52.5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>11023.91</v>
+      </c>
+      <c r="D44" t="n">
+        <v>779.53</v>
+      </c>
+      <c r="E44" t="n">
+        <v>6767.26</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1503.01</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1623</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2307.58</v>
+      </c>
+      <c r="I44" t="n">
+        <v>8115.1</v>
+      </c>
+      <c r="J44" t="n">
+        <v>5851.59</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2204.23</v>
+      </c>
+      <c r="L44" t="n">
+        <v>395.59</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1705.07</v>
+      </c>
+      <c r="N44" t="n">
+        <v>43.7</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1233.52</v>
+      </c>
+      <c r="D45" t="n">
+        <v>75.89</v>
+      </c>
+      <c r="E45" t="n">
+        <v>433.48</v>
+      </c>
+      <c r="F45" t="n">
+        <v>184.51</v>
+      </c>
+      <c r="G45" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="H45" t="n">
+        <v>646.65</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1010.29</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1145.55</v>
+      </c>
+      <c r="K45" t="n">
+        <v>257.09</v>
+      </c>
+      <c r="L45" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M45" t="n">
+        <v>45.73</v>
+      </c>
+      <c r="N45" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>10419.53</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1006.1</v>
+      </c>
+      <c r="E46" t="n">
+        <v>6454.48</v>
+      </c>
+      <c r="F46" t="n">
+        <v>997.5599999999999</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1521.8</v>
+      </c>
+      <c r="H46" t="n">
+        <v>2155.9</v>
+      </c>
+      <c r="I46" t="n">
+        <v>8317.52</v>
+      </c>
+      <c r="J46" t="n">
+        <v>5572.07</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2326.16</v>
+      </c>
+      <c r="L46" t="n">
+        <v>352.98</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1669</v>
+      </c>
+      <c r="N46" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1413.76</v>
+      </c>
+      <c r="D47" t="n">
+        <v>117.14</v>
+      </c>
+      <c r="E47" t="n">
+        <v>403.55</v>
+      </c>
+      <c r="F47" t="n">
+        <v>347.26</v>
+      </c>
+      <c r="G47" t="n">
+        <v>86.63</v>
+      </c>
+      <c r="H47" t="n">
+        <v>797.79</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1359.69</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2247.96</v>
+      </c>
+      <c r="K47" t="n">
+        <v>373.84</v>
+      </c>
+      <c r="L47" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M47" t="n">
+        <v>65.17</v>
+      </c>
+      <c r="N47" t="n">
+        <v>66.2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>11571.02</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1129.25</v>
+      </c>
+      <c r="E48" t="n">
+        <v>6096.2</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1298.35</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1476.82</v>
+      </c>
+      <c r="H48" t="n">
+        <v>2221.24</v>
+      </c>
+      <c r="I48" t="n">
+        <v>8371.51</v>
+      </c>
+      <c r="J48" t="n">
+        <v>6197.7</v>
+      </c>
+      <c r="K48" t="n">
+        <v>2892.09</v>
+      </c>
+      <c r="L48" t="n">
+        <v>308.87</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1688.04</v>
+      </c>
+      <c r="N48" t="n">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1852.15</v>
+      </c>
+      <c r="D49" t="n">
+        <v>182.03</v>
+      </c>
+      <c r="E49" t="n">
+        <v>419.8</v>
+      </c>
+      <c r="F49" t="n">
+        <v>851.01</v>
+      </c>
+      <c r="G49" t="n">
+        <v>115.48</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1001.99</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1750.01</v>
+      </c>
+      <c r="J49" t="n">
+        <v>3217.21</v>
+      </c>
+      <c r="K49" t="n">
+        <v>548.6900000000001</v>
+      </c>
+      <c r="L49" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="M49" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="N49" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>11684.63</v>
+      </c>
+      <c r="D50" t="n">
+        <v>971.85</v>
+      </c>
+      <c r="E50" t="n">
+        <v>5995.15</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1031.85</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1406.06</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2187.07</v>
+      </c>
+      <c r="I50" t="n">
+        <v>8854.450000000001</v>
+      </c>
+      <c r="J50" t="n">
+        <v>6613.89</v>
+      </c>
+      <c r="K50" t="n">
+        <v>3581.36</v>
+      </c>
+      <c r="L50" t="n">
+        <v>210.51</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1559.33</v>
+      </c>
+      <c r="N50" t="n">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>2363.48</v>
+      </c>
+      <c r="D51" t="n">
+        <v>244.59</v>
+      </c>
+      <c r="E51" t="n">
+        <v>576.03</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1006.27</v>
+      </c>
+      <c r="G51" t="n">
+        <v>224.6</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1277.47</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1956.34</v>
+      </c>
+      <c r="J51" t="n">
+        <v>3695.16</v>
+      </c>
+      <c r="K51" t="n">
+        <v>609.97</v>
+      </c>
+      <c r="L51" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="M51" t="n">
+        <v>76.15000000000001</v>
+      </c>
+      <c r="N51" t="n">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>13327.89</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1053.14</v>
+      </c>
+      <c r="E52" t="n">
+        <v>7079.21</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1444.99</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2323.54</v>
+      </c>
+      <c r="H52" t="n">
+        <v>2400.89</v>
+      </c>
+      <c r="I52" t="n">
+        <v>9339.99</v>
+      </c>
+      <c r="J52" t="n">
+        <v>7432.1</v>
+      </c>
+      <c r="K52" t="n">
+        <v>3344.56</v>
+      </c>
+      <c r="L52" t="n">
+        <v>447.37</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1648.2</v>
+      </c>
+      <c r="N52" t="n">
+        <v>45.2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>3170.46</v>
+      </c>
+      <c r="D53" t="n">
+        <v>357.98</v>
+      </c>
+      <c r="E53" t="n">
+        <v>686.97</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1078.71</v>
+      </c>
+      <c r="G53" t="n">
+        <v>222.68</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1682.24</v>
+      </c>
+      <c r="I53" t="n">
+        <v>2307.08</v>
+      </c>
+      <c r="J53" t="n">
+        <v>4035.22</v>
+      </c>
+      <c r="K53" t="n">
+        <v>752.23</v>
+      </c>
+      <c r="L53" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="M53" t="n">
+        <v>134.81</v>
+      </c>
+      <c r="N53" t="n">
+        <v>60.7</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>15073.49</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1202.92</v>
+      </c>
+      <c r="E54" t="n">
+        <v>8056.39</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1523.58</v>
+      </c>
+      <c r="G54" t="n">
+        <v>3162.35</v>
+      </c>
+      <c r="H54" t="n">
+        <v>2903.5</v>
+      </c>
+      <c r="I54" t="n">
+        <v>10495.51</v>
+      </c>
+      <c r="J54" t="n">
+        <v>7343.11</v>
+      </c>
+      <c r="K54" t="n">
+        <v>3275.03</v>
+      </c>
+      <c r="L54" t="n">
+        <v>614.64</v>
+      </c>
+      <c r="M54" t="n">
+        <v>2026.74</v>
+      </c>
+      <c r="N54" t="n">
+        <v>43.1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>3513.72</v>
+      </c>
+      <c r="D55" t="n">
+        <v>404.24</v>
+      </c>
+      <c r="E55" t="n">
+        <v>954.97</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1668.96</v>
+      </c>
+      <c r="G55" t="n">
+        <v>219.66</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1829.4</v>
+      </c>
+      <c r="I55" t="n">
+        <v>2563.01</v>
+      </c>
+      <c r="J55" t="n">
+        <v>4995.47</v>
+      </c>
+      <c r="K55" t="n">
+        <v>805.95</v>
+      </c>
+      <c r="L55" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="M55" t="n">
+        <v>152.35</v>
+      </c>
+      <c r="N55" t="n">
+        <v>59.6</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>17719.47</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1552.86</v>
+      </c>
+      <c r="E56" t="n">
+        <v>7904.61</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1872.87</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2636.87</v>
+      </c>
+      <c r="H56" t="n">
+        <v>2833.03</v>
+      </c>
+      <c r="I56" t="n">
+        <v>10050.6</v>
+      </c>
+      <c r="J56" t="n">
+        <v>7233.06</v>
+      </c>
+      <c r="K56" t="n">
+        <v>3148.94</v>
+      </c>
+      <c r="L56" t="n">
+        <v>1221.21</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1707.9</v>
+      </c>
+      <c r="N56" t="n">
+        <v>40.2</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>3655.93</v>
+      </c>
+      <c r="D57" t="n">
+        <v>472.52</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1006.07</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1490.01</v>
+      </c>
+      <c r="G57" t="n">
+        <v>220.73</v>
+      </c>
+      <c r="H57" t="n">
+        <v>2098.47</v>
+      </c>
+      <c r="I57" t="n">
+        <v>3012.56</v>
+      </c>
+      <c r="J57" t="n">
+        <v>7454.39</v>
+      </c>
+      <c r="K57" t="n">
+        <v>984.65</v>
+      </c>
+      <c r="L57" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="M57" t="n">
+        <v>181.59</v>
+      </c>
+      <c r="N57" t="n">
+        <v>65.8</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>19200.68</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1708.11</v>
+      </c>
+      <c r="E58" t="n">
+        <v>8950.9</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1938.85</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2830.85</v>
+      </c>
+      <c r="H58" t="n">
+        <v>3031.64</v>
+      </c>
+      <c r="I58" t="n">
+        <v>9933.780000000001</v>
+      </c>
+      <c r="J58" t="n">
+        <v>8704.620000000001</v>
+      </c>
+      <c r="K58" t="n">
+        <v>3056.54</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1574.52</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1772.56</v>
+      </c>
+      <c r="N58" t="n">
+        <v>39.4</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>4053.61</v>
+      </c>
+      <c r="D59" t="n">
+        <v>526.23</v>
+      </c>
+      <c r="E59" t="n">
+        <v>920.5599999999999</v>
+      </c>
+      <c r="F59" t="n">
+        <v>897.8</v>
+      </c>
+      <c r="G59" t="n">
+        <v>318.53</v>
+      </c>
+      <c r="H59" t="n">
+        <v>2128.83</v>
+      </c>
+      <c r="I59" t="n">
+        <v>2866.64</v>
+      </c>
+      <c r="J59" t="n">
+        <v>7477.34</v>
+      </c>
+      <c r="K59" t="n">
+        <v>991.87</v>
+      </c>
+      <c r="L59" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M59" t="n">
+        <v>175.17</v>
+      </c>
+      <c r="N59" t="n">
+        <v>66.09999999999999</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>17094.3</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1528.99</v>
+      </c>
+      <c r="E60" t="n">
+        <v>9967.610000000001</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1754.36</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3459.21</v>
+      </c>
+      <c r="H60" t="n">
+        <v>3021.78</v>
+      </c>
+      <c r="I60" t="n">
+        <v>9156.209999999999</v>
+      </c>
+      <c r="J60" t="n">
+        <v>9568.25</v>
+      </c>
+      <c r="K60" t="n">
+        <v>2779.84</v>
+      </c>
+      <c r="L60" t="n">
+        <v>1307.55</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1337.7</v>
+      </c>
+      <c r="N60" t="n">
+        <v>40.2</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>2962.34</v>
+      </c>
+      <c r="D61" t="n">
+        <v>245.35</v>
+      </c>
+      <c r="E61" t="n">
+        <v>717.88</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1039.63</v>
+      </c>
+      <c r="G61" t="n">
+        <v>167.41</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1935.59</v>
+      </c>
+      <c r="I61" t="n">
+        <v>2324.71</v>
+      </c>
+      <c r="J61" t="n">
+        <v>4742.46</v>
+      </c>
+      <c r="K61" t="n">
+        <v>877.34</v>
+      </c>
+      <c r="L61" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="M61" t="n">
+        <v>143.24</v>
+      </c>
+      <c r="N61" t="n">
+        <v>65.2</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>16515.56</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1236.77</v>
+      </c>
+      <c r="E62" t="n">
+        <v>8977.809999999999</v>
+      </c>
+      <c r="F62" t="n">
+        <v>2205.74</v>
+      </c>
+      <c r="G62" t="n">
+        <v>2997.16</v>
+      </c>
+      <c r="H62" t="n">
+        <v>3001.58</v>
+      </c>
+      <c r="I62" t="n">
+        <v>8667.17</v>
+      </c>
+      <c r="J62" t="n">
+        <v>9608.09</v>
+      </c>
+      <c r="K62" t="n">
+        <v>2776.78</v>
+      </c>
+      <c r="L62" t="n">
+        <v>1559.63</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1612.63</v>
+      </c>
+      <c r="N62" t="n">
+        <v>40.7</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>3118.19</v>
+      </c>
+      <c r="D63" t="n">
+        <v>251.44</v>
+      </c>
+      <c r="E63" t="n">
+        <v>824.16</v>
+      </c>
+      <c r="F63" t="n">
+        <v>3290.84</v>
+      </c>
+      <c r="G63" t="n">
+        <v>163.25</v>
+      </c>
+      <c r="H63" t="n">
+        <v>2193.9</v>
+      </c>
+      <c r="I63" t="n">
+        <v>2520.81</v>
+      </c>
+      <c r="J63" t="n">
+        <v>5477.3</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1022.96</v>
+      </c>
+      <c r="L63" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="M63" t="n">
+        <v>171.41</v>
+      </c>
+      <c r="N63" t="n">
+        <v>58.9</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>15780.69</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1086.63</v>
+      </c>
+      <c r="E64" t="n">
+        <v>10322.38</v>
+      </c>
+      <c r="F64" t="n">
+        <v>3624.86</v>
+      </c>
+      <c r="G64" t="n">
+        <v>2018.5</v>
+      </c>
+      <c r="H64" t="n">
+        <v>3435.33</v>
+      </c>
+      <c r="I64" t="n">
+        <v>9837.129999999999</v>
+      </c>
+      <c r="J64" t="n">
+        <v>13469.63</v>
+      </c>
+      <c r="K64" t="n">
+        <v>3320.97</v>
+      </c>
+      <c r="L64" t="n">
+        <v>1895.71</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1994.42</v>
+      </c>
+      <c r="N64" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>2629.23</v>
+      </c>
+      <c r="D65" t="n">
+        <v>188.32</v>
+      </c>
+      <c r="E65" t="n">
+        <v>715.88</v>
+      </c>
+      <c r="F65" t="n">
+        <v>2973.48</v>
+      </c>
+      <c r="G65" t="n">
+        <v>130.33</v>
+      </c>
+      <c r="H65" t="n">
+        <v>2171.66</v>
+      </c>
+      <c r="I65" t="n">
+        <v>2287.83</v>
+      </c>
+      <c r="J65" t="n">
+        <v>4352.07</v>
+      </c>
+      <c r="K65" t="n">
+        <v>932.9299999999999</v>
+      </c>
+      <c r="L65" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="M65" t="n">
+        <v>135.48</v>
+      </c>
+      <c r="N65" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>18511.14</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1244.64</v>
+      </c>
+      <c r="E66" t="n">
+        <v>11111.63</v>
+      </c>
+      <c r="F66" t="n">
+        <v>5056.64</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2158.86</v>
+      </c>
+      <c r="H66" t="n">
+        <v>3265.5</v>
+      </c>
+      <c r="I66" t="n">
+        <v>9568.299999999999</v>
+      </c>
+      <c r="J66" t="n">
+        <v>14629.53</v>
+      </c>
+      <c r="K66" t="n">
+        <v>3455.76</v>
+      </c>
+      <c r="L66" t="n">
+        <v>1948.93</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1578.68</v>
+      </c>
+      <c r="N66" t="n">
+        <v>42.6</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>2111.25</v>
+      </c>
+      <c r="D67" t="n">
+        <v>128.23</v>
+      </c>
+      <c r="E67" t="n">
+        <v>695.97</v>
+      </c>
+      <c r="F67" t="n">
+        <v>2635.09</v>
+      </c>
+      <c r="G67" t="n">
+        <v>165.52</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1829.14</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1335.15</v>
+      </c>
+      <c r="J67" t="n">
+        <v>2170.42</v>
+      </c>
+      <c r="K67" t="n">
+        <v>386.08</v>
+      </c>
+      <c r="L67" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="M67" t="n">
+        <v>91.55</v>
+      </c>
+      <c r="N67" t="n">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>18871.28</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1283.16</v>
+      </c>
+      <c r="E68" t="n">
+        <v>11469.73</v>
+      </c>
+      <c r="F68" t="n">
+        <v>6084.13</v>
+      </c>
+      <c r="G68" t="n">
+        <v>2857.49</v>
+      </c>
+      <c r="H68" t="n">
+        <v>3888.02</v>
+      </c>
+      <c r="I68" t="n">
+        <v>11534.52</v>
+      </c>
+      <c r="J68" t="n">
+        <v>15177.21</v>
+      </c>
+      <c r="K68" t="n">
+        <v>3686.9</v>
+      </c>
+      <c r="L68" t="n">
+        <v>1782.65</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1854.25</v>
+      </c>
+      <c r="N68" t="n">
+        <v>43.7</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>2392.7</v>
+      </c>
+      <c r="D69" t="n">
+        <v>112.35</v>
+      </c>
+      <c r="E69" t="n">
+        <v>954.23</v>
+      </c>
+      <c r="F69" t="n">
+        <v>2563.32</v>
+      </c>
+      <c r="G69" t="n">
+        <v>168.54</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2306.98</v>
+      </c>
+      <c r="I69" t="n">
+        <v>1790.21</v>
+      </c>
+      <c r="J69" t="n">
+        <v>3115.24</v>
+      </c>
+      <c r="K69" t="n">
+        <v>511.45</v>
+      </c>
+      <c r="L69" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M69" t="n">
+        <v>116.13</v>
+      </c>
+      <c r="N69" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>22608.75</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1435.01</v>
+      </c>
+      <c r="E70" t="n">
+        <v>15081.28</v>
+      </c>
+      <c r="F70" t="n">
+        <v>7661.62</v>
+      </c>
+      <c r="G70" t="n">
+        <v>4067.82</v>
+      </c>
+      <c r="H70" t="n">
+        <v>4473.85</v>
+      </c>
+      <c r="I70" t="n">
+        <v>13563.81</v>
+      </c>
+      <c r="J70" t="n">
+        <v>16237.73</v>
+      </c>
+      <c r="K70" t="n">
+        <v>3876.64</v>
+      </c>
+      <c r="L70" t="n">
+        <v>2381.83</v>
+      </c>
+      <c r="M70" t="n">
+        <v>2079.4</v>
+      </c>
+      <c r="N70" t="n">
+        <v>40.8</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>2372.43</v>
+      </c>
+      <c r="D71" t="n">
+        <v>134.54</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1061.03</v>
+      </c>
+      <c r="F71" t="n">
+        <v>2688.01</v>
+      </c>
+      <c r="G71" t="n">
+        <v>186.84</v>
+      </c>
+      <c r="H71" t="n">
+        <v>3096.29</v>
+      </c>
+      <c r="I71" t="n">
+        <v>2439.52</v>
+      </c>
+      <c r="J71" t="n">
+        <v>5458.45</v>
+      </c>
+      <c r="K71" t="n">
+        <v>753.5</v>
+      </c>
+      <c r="L71" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="M71" t="n">
+        <v>205.14</v>
+      </c>
+      <c r="N71" t="n">
+        <v>63.8</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>29080.95</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1839.31</v>
+      </c>
+      <c r="E72" t="n">
+        <v>19007.46</v>
+      </c>
+      <c r="F72" t="n">
+        <v>8715.76</v>
+      </c>
+      <c r="G72" t="n">
+        <v>4586.9</v>
+      </c>
+      <c r="H72" t="n">
+        <v>5752.01</v>
+      </c>
+      <c r="I72" t="n">
+        <v>17457.79</v>
+      </c>
+      <c r="J72" t="n">
+        <v>20696.66</v>
+      </c>
+      <c r="K72" t="n">
+        <v>4677.72</v>
+      </c>
+      <c r="L72" t="n">
+        <v>2664.33</v>
+      </c>
+      <c r="M72" t="n">
+        <v>2624.19</v>
+      </c>
+      <c r="N72" t="n">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>2497.19</v>
+      </c>
+      <c r="D73" t="n">
+        <v>142.72</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1239.15</v>
+      </c>
+      <c r="F73" t="n">
+        <v>3045.66</v>
+      </c>
+      <c r="G73" t="n">
+        <v>160.62</v>
+      </c>
+      <c r="H73" t="n">
+        <v>3644.53</v>
+      </c>
+      <c r="I73" t="n">
+        <v>2959.29</v>
+      </c>
+      <c r="J73" t="n">
+        <v>7768.51</v>
+      </c>
+      <c r="K73" t="n">
+        <v>951.97</v>
+      </c>
+      <c r="L73" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="M73" t="n">
+        <v>247.69</v>
+      </c>
+      <c r="N73" t="n">
+        <v>67.59999999999999</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>33936.52</v>
+      </c>
+      <c r="D74" t="n">
+        <v>2237.42</v>
+      </c>
+      <c r="E74" t="n">
+        <v>22967.37</v>
+      </c>
+      <c r="F74" t="n">
+        <v>12290.04</v>
+      </c>
+      <c r="G74" t="n">
+        <v>4662.84</v>
+      </c>
+      <c r="H74" t="n">
+        <v>7296.11</v>
+      </c>
+      <c r="I74" t="n">
+        <v>20572.47</v>
+      </c>
+      <c r="J74" t="n">
+        <v>27289.74</v>
+      </c>
+      <c r="K74" t="n">
+        <v>5084.86</v>
+      </c>
+      <c r="L74" t="n">
+        <v>3446.42</v>
+      </c>
+      <c r="M74" t="n">
+        <v>2825.9</v>
+      </c>
+      <c r="N74" t="n">
+        <v>42.2</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3096.5</v>
+      </c>
+      <c r="D75" t="n">
+        <v>177.37</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1284.6</v>
+      </c>
+      <c r="F75" t="n">
+        <v>4048.54</v>
+      </c>
+      <c r="G75" t="n">
+        <v>159.58</v>
+      </c>
+      <c r="H75" t="n">
+        <v>3996.5</v>
+      </c>
+      <c r="I75" t="n">
+        <v>3436.49</v>
+      </c>
+      <c r="J75" t="n">
+        <v>9656.49</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1101.87</v>
+      </c>
+      <c r="L75" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="M75" t="n">
+        <v>372.33</v>
+      </c>
+      <c r="N75" t="n">
+        <v>66.59999999999999</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>39475.25</v>
+      </c>
+      <c r="D76" t="n">
+        <v>2367.47</v>
+      </c>
+      <c r="E76" t="n">
+        <v>26394.72</v>
+      </c>
+      <c r="F76" t="n">
+        <v>15414.97</v>
+      </c>
+      <c r="G76" t="n">
+        <v>5143.89</v>
+      </c>
+      <c r="H76" t="n">
+        <v>9332.379999999999</v>
+      </c>
+      <c r="I76" t="n">
+        <v>22238.29</v>
+      </c>
+      <c r="J76" t="n">
+        <v>29767.52</v>
+      </c>
+      <c r="K76" t="n">
+        <v>5108.88</v>
+      </c>
+      <c r="L76" t="n">
+        <v>4656.72</v>
+      </c>
+      <c r="M76" t="n">
+        <v>4347.48</v>
+      </c>
+      <c r="N76" t="n">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>3960.29</v>
+      </c>
+      <c r="D77" t="n">
+        <v>215.45</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1612.35</v>
+      </c>
+      <c r="F77" t="n">
+        <v>4944.99</v>
+      </c>
+      <c r="G77" t="n">
+        <v>153.03</v>
+      </c>
+      <c r="H77" t="n">
+        <v>4734.47</v>
+      </c>
+      <c r="I77" t="n">
+        <v>4228.19</v>
+      </c>
+      <c r="J77" t="n">
+        <v>12431.19</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1314.3</v>
+      </c>
+      <c r="L77" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="M77" t="n">
+        <v>495.31</v>
+      </c>
+      <c r="N77" t="n">
+        <v>66.59999999999999</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>48561.05</v>
+      </c>
+      <c r="D78" t="n">
+        <v>3006.84</v>
+      </c>
+      <c r="E78" t="n">
+        <v>33179.86</v>
+      </c>
+      <c r="F78" t="n">
+        <v>16545.35</v>
+      </c>
+      <c r="G78" t="n">
+        <v>7382.1</v>
+      </c>
+      <c r="H78" t="n">
+        <v>10491.34</v>
+      </c>
+      <c r="I78" t="n">
+        <v>24120.72</v>
+      </c>
+      <c r="J78" t="n">
+        <v>31926.39</v>
+      </c>
+      <c r="K78" t="n">
+        <v>5408.88</v>
+      </c>
+      <c r="L78" t="n">
+        <v>5341.88</v>
+      </c>
+      <c r="M78" t="n">
+        <v>4779.76</v>
+      </c>
+      <c r="N78" t="n">
+        <v>37.7</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>4998.19</v>
+      </c>
+      <c r="D79" t="n">
+        <v>286.82</v>
+      </c>
+      <c r="E79" t="n">
+        <v>2346.44</v>
+      </c>
+      <c r="F79" t="n">
+        <v>5534.98</v>
+      </c>
+      <c r="G79" t="n">
+        <v>184.79</v>
+      </c>
+      <c r="H79" t="n">
+        <v>5723.19</v>
+      </c>
+      <c r="I79" t="n">
+        <v>5430.64</v>
+      </c>
+      <c r="J79" t="n">
+        <v>16519</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1612.04</v>
+      </c>
+      <c r="L79" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="M79" t="n">
+        <v>501.04</v>
+      </c>
+      <c r="N79" t="n">
+        <v>67.90000000000001</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>61094.28</v>
+      </c>
+      <c r="D80" t="n">
+        <v>3700.58</v>
+      </c>
+      <c r="E80" t="n">
+        <v>46591.65</v>
+      </c>
+      <c r="F80" t="n">
+        <v>21856.13</v>
+      </c>
+      <c r="G80" t="n">
+        <v>10233.04</v>
+      </c>
+      <c r="H80" t="n">
+        <v>13217.65</v>
+      </c>
+      <c r="I80" t="n">
+        <v>26750.1</v>
+      </c>
+      <c r="J80" t="n">
+        <v>33526.06</v>
+      </c>
+      <c r="K80" t="n">
+        <v>5464.03</v>
+      </c>
+      <c r="L80" t="n">
+        <v>8022.02</v>
+      </c>
+      <c r="M80" t="n">
+        <v>4535.02</v>
+      </c>
+      <c r="N80" t="n">
+        <v>33.6</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>4320.45</v>
+      </c>
+      <c r="D81" t="n">
+        <v>300.95</v>
+      </c>
+      <c r="E81" t="n">
+        <v>978.15</v>
+      </c>
+      <c r="F81" t="n">
+        <v>5667.28</v>
+      </c>
+      <c r="G81" t="n">
+        <v>127.97</v>
+      </c>
+      <c r="H81" t="n">
+        <v>4476.08</v>
+      </c>
+      <c r="I81" t="n">
+        <v>3740.01</v>
+      </c>
+      <c r="J81" t="n">
+        <v>12724.21</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1395.97</v>
+      </c>
+      <c r="L81" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="M81" t="n">
+        <v>309.58</v>
+      </c>
+      <c r="N81" t="n">
+        <v>65.59999999999999</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>55967.19</v>
+      </c>
+      <c r="D82" t="n">
+        <v>4002.74</v>
+      </c>
+      <c r="E82" t="n">
+        <v>38737.72</v>
+      </c>
+      <c r="F82" t="n">
+        <v>15647.99</v>
+      </c>
+      <c r="G82" t="n">
+        <v>5921.08</v>
+      </c>
+      <c r="H82" t="n">
+        <v>11542.23</v>
+      </c>
+      <c r="I82" t="n">
+        <v>17312.09</v>
+      </c>
+      <c r="J82" t="n">
+        <v>21367.35</v>
+      </c>
+      <c r="K82" t="n">
+        <v>4263.59</v>
+      </c>
+      <c r="L82" t="n">
+        <v>6195.97</v>
+      </c>
+      <c r="M82" t="n">
+        <v>2944.91</v>
+      </c>
+      <c r="N82" t="n">
+        <v>29.6</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>5184.1</v>
+      </c>
+      <c r="D83" t="n">
+        <v>391.34</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1771.33</v>
+      </c>
+      <c r="F83" t="n">
+        <v>4986.67</v>
+      </c>
+      <c r="G83" t="n">
+        <v>169.17</v>
+      </c>
+      <c r="H83" t="n">
+        <v>5530.96</v>
+      </c>
+      <c r="I83" t="n">
+        <v>5008.97</v>
+      </c>
+      <c r="J83" t="n">
+        <v>19315.29</v>
+      </c>
+      <c r="K83" t="n">
+        <v>1829.06</v>
+      </c>
+      <c r="L83" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="M83" t="n">
+        <v>488.88</v>
+      </c>
+      <c r="N83" t="n">
+        <v>70.90000000000001</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>67555.60000000001</v>
+      </c>
+      <c r="D84" t="n">
+        <v>3729.37</v>
+      </c>
+      <c r="E84" t="n">
+        <v>62055.22</v>
+      </c>
+      <c r="F84" t="n">
+        <v>22439.92</v>
+      </c>
+      <c r="G84" t="n">
+        <v>6739.68</v>
+      </c>
+      <c r="H84" t="n">
+        <v>13154.45</v>
+      </c>
+      <c r="I84" t="n">
+        <v>20148.3</v>
+      </c>
+      <c r="J84" t="n">
+        <v>24741.94</v>
+      </c>
+      <c r="K84" t="n">
+        <v>4465.72</v>
+      </c>
+      <c r="L84" t="n">
+        <v>8908.82</v>
+      </c>
+      <c r="M84" t="n">
+        <v>3224.78</v>
+      </c>
+      <c r="N84" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>6737.5</v>
+      </c>
+      <c r="D85" t="n">
+        <v>408.47</v>
+      </c>
+      <c r="E85" t="n">
+        <v>2295.75</v>
+      </c>
+      <c r="F85" t="n">
+        <v>6281.92</v>
+      </c>
+      <c r="G85" t="n">
+        <v>200.01</v>
+      </c>
+      <c r="H85" t="n">
+        <v>6314.21</v>
+      </c>
+      <c r="I85" t="n">
+        <v>5893.54</v>
+      </c>
+      <c r="J85" t="n">
+        <v>23094.08</v>
+      </c>
+      <c r="K85" t="n">
+        <v>2175.13</v>
+      </c>
+      <c r="L85" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="M85" t="n">
+        <v>778.48</v>
+      </c>
+      <c r="N85" t="n">
+        <v>69.2</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>83952.34</v>
+      </c>
+      <c r="D86" t="n">
+        <v>4118.75</v>
+      </c>
+      <c r="E86" t="n">
+        <v>83963.46000000001</v>
+      </c>
+      <c r="F86" t="n">
+        <v>27804.12</v>
+      </c>
+      <c r="G86" t="n">
+        <v>9257.02</v>
+      </c>
+      <c r="H86" t="n">
+        <v>16747.78</v>
+      </c>
+      <c r="I86" t="n">
+        <v>24632.16</v>
+      </c>
+      <c r="J86" t="n">
+        <v>27933.35</v>
+      </c>
+      <c r="K86" t="n">
+        <v>4384.61</v>
+      </c>
+      <c r="L86" t="n">
+        <v>11609.14</v>
+      </c>
+      <c r="M86" t="n">
+        <v>3738.69</v>
+      </c>
+      <c r="N86" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>5489.39</v>
+      </c>
+      <c r="D87" t="n">
+        <v>456.09</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1706.01</v>
+      </c>
+      <c r="F87" t="n">
+        <v>3864.26</v>
+      </c>
+      <c r="G87" t="n">
+        <v>231.81</v>
+      </c>
+      <c r="H87" t="n">
+        <v>4527.02</v>
+      </c>
+      <c r="I87" t="n">
+        <v>4363.34</v>
+      </c>
+      <c r="J87" t="n">
+        <v>17506.4</v>
+      </c>
+      <c r="K87" t="n">
+        <v>1521.71</v>
+      </c>
+      <c r="L87" t="n">
+        <v>24.84</v>
+      </c>
+      <c r="M87" t="n">
+        <v>559.41</v>
+      </c>
+      <c r="N87" t="n">
+        <v>69.40000000000001</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>74618.03</v>
+      </c>
+      <c r="D88" t="n">
+        <v>3122.55</v>
+      </c>
+      <c r="E88" t="n">
+        <v>69828.28999999999</v>
+      </c>
+      <c r="F88" t="n">
+        <v>18792.94</v>
+      </c>
+      <c r="G88" t="n">
+        <v>6422.59</v>
+      </c>
+      <c r="H88" t="n">
+        <v>13669.26</v>
+      </c>
+      <c r="I88" t="n">
+        <v>21737.91</v>
+      </c>
+      <c r="J88" t="n">
+        <v>26241.23</v>
+      </c>
+      <c r="K88" t="n">
+        <v>4071.52</v>
+      </c>
+      <c r="L88" t="n">
+        <v>8669.049999999999</v>
+      </c>
+      <c r="M88" t="n">
+        <v>2517.84</v>
+      </c>
+      <c r="N88" t="n">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>5797.69</v>
+      </c>
+      <c r="D89" t="n">
+        <v>449.65</v>
+      </c>
+      <c r="E89" t="n">
+        <v>3016.34</v>
+      </c>
+      <c r="F89" t="n">
+        <v>4194.75</v>
+      </c>
+      <c r="G89" t="n">
+        <v>212.24</v>
+      </c>
+      <c r="H89" t="n">
+        <v>4382.81</v>
+      </c>
+      <c r="I89" t="n">
+        <v>3947.07</v>
+      </c>
+      <c r="J89" t="n">
+        <v>14696.51</v>
+      </c>
+      <c r="K89" t="n">
+        <v>1473.68</v>
+      </c>
+      <c r="L89" t="n">
+        <v>2759.2</v>
+      </c>
+      <c r="M89" t="n">
+        <v>489.36</v>
+      </c>
+      <c r="N89" t="n">
+        <v>59.2</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>71650.89</v>
+      </c>
+      <c r="D90" t="n">
+        <v>2910.19</v>
+      </c>
+      <c r="E90" t="n">
+        <v>77120.09</v>
+      </c>
+      <c r="F90" t="n">
+        <v>30148.62</v>
+      </c>
+      <c r="G90" t="n">
+        <v>5123.75</v>
+      </c>
+      <c r="H90" t="n">
+        <v>12862.17</v>
+      </c>
+      <c r="I90" t="n">
+        <v>22170.54</v>
+      </c>
+      <c r="J90" t="n">
+        <v>26129.67</v>
+      </c>
+      <c r="K90" t="n">
+        <v>4060.36</v>
+      </c>
+      <c r="L90" t="n">
+        <v>14688.88</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1708.75</v>
+      </c>
+      <c r="N90" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>5645.64</v>
+      </c>
+      <c r="D91" t="n">
+        <v>375.24</v>
+      </c>
+      <c r="E91" t="n">
+        <v>2073.52</v>
+      </c>
+      <c r="F91" t="n">
+        <v>3312.98</v>
+      </c>
+      <c r="G91" t="n">
+        <v>215.69</v>
+      </c>
+      <c r="H91" t="n">
+        <v>3749.82</v>
+      </c>
+      <c r="I91" t="n">
+        <v>3363.34</v>
+      </c>
+      <c r="J91" t="n">
+        <v>10425.96</v>
+      </c>
+      <c r="K91" t="n">
+        <v>1310.48</v>
+      </c>
+      <c r="L91" t="n">
+        <v>2544.14</v>
+      </c>
+      <c r="M91" t="n">
+        <v>412.82</v>
+      </c>
+      <c r="N91" t="n">
+        <v>56.4</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>76894.63</v>
+      </c>
+      <c r="D92" t="n">
+        <v>3061.58</v>
+      </c>
+      <c r="E92" t="n">
+        <v>75157.92</v>
+      </c>
+      <c r="F92" t="n">
+        <v>31311.36</v>
+      </c>
+      <c r="G92" t="n">
+        <v>5184.61</v>
+      </c>
+      <c r="H92" t="n">
+        <v>11998.92</v>
+      </c>
+      <c r="I92" t="n">
+        <v>20654.6</v>
+      </c>
+      <c r="J92" t="n">
+        <v>24237.87</v>
+      </c>
+      <c r="K92" t="n">
+        <v>4343.94</v>
+      </c>
+      <c r="L92" t="n">
+        <v>13824.97</v>
+      </c>
+      <c r="M92" t="n">
+        <v>1790.25</v>
+      </c>
+      <c r="N92" t="n">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>5371.72</v>
+      </c>
+      <c r="D93" t="n">
+        <v>382.9</v>
+      </c>
+      <c r="E93" t="n">
+        <v>2727.33</v>
+      </c>
+      <c r="F93" t="n">
+        <v>2403.06</v>
+      </c>
+      <c r="G93" t="n">
+        <v>409.63</v>
+      </c>
+      <c r="H93" t="n">
+        <v>3499.31</v>
+      </c>
+      <c r="I93" t="n">
+        <v>2904.33</v>
+      </c>
+      <c r="J93" t="n">
+        <v>8043.07</v>
+      </c>
+      <c r="K93" t="n">
+        <v>1085.55</v>
+      </c>
+      <c r="L93" t="n">
+        <v>1780.79</v>
+      </c>
+      <c r="M93" t="n">
+        <v>382.65</v>
+      </c>
+      <c r="N93" t="n">
+        <v>53.6</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>77656.87</v>
+      </c>
+      <c r="D94" t="n">
+        <v>2526.17</v>
+      </c>
+      <c r="E94" t="n">
+        <v>78327.87</v>
+      </c>
+      <c r="F94" t="n">
+        <v>25762.47</v>
+      </c>
+      <c r="G94" t="n">
+        <v>5527.16</v>
+      </c>
+      <c r="H94" t="n">
+        <v>10500.42</v>
+      </c>
+      <c r="I94" t="n">
+        <v>17007.26</v>
+      </c>
+      <c r="J94" t="n">
+        <v>16502.75</v>
+      </c>
+      <c r="K94" t="n">
+        <v>3042.99</v>
+      </c>
+      <c r="L94" t="n">
+        <v>12402.53</v>
+      </c>
+      <c r="M94" t="n">
+        <v>1199.08</v>
+      </c>
+      <c r="N94" t="n">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>6925.42</v>
+      </c>
+      <c r="D95" t="n">
+        <v>396.01</v>
+      </c>
+      <c r="E95" t="n">
+        <v>3879.34</v>
+      </c>
+      <c r="F95" t="n">
+        <v>2708.93</v>
+      </c>
+      <c r="G95" t="n">
+        <v>317.34</v>
+      </c>
+      <c r="H95" t="n">
+        <v>4321.35</v>
+      </c>
+      <c r="I95" t="n">
+        <v>4355.77</v>
+      </c>
+      <c r="J95" t="n">
+        <v>11294.63</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1439.35</v>
+      </c>
+      <c r="L95" t="n">
+        <v>3824.3</v>
+      </c>
+      <c r="M95" t="n">
+        <v>578.36</v>
+      </c>
+      <c r="N95" t="n">
+        <v>53.5</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>87865.97</v>
+      </c>
+      <c r="D96" t="n">
+        <v>2363.99</v>
+      </c>
+      <c r="E96" t="n">
+        <v>111257.76</v>
+      </c>
+      <c r="F96" t="n">
+        <v>39872.4</v>
+      </c>
+      <c r="G96" t="n">
+        <v>8960.540000000001</v>
+      </c>
+      <c r="H96" t="n">
+        <v>13636.35</v>
+      </c>
+      <c r="I96" t="n">
+        <v>24234.26</v>
+      </c>
+      <c r="J96" t="n">
+        <v>20764.65</v>
+      </c>
+      <c r="K96" t="n">
+        <v>4113.72</v>
+      </c>
+      <c r="L96" t="n">
+        <v>24085.74</v>
+      </c>
+      <c r="M96" t="n">
+        <v>1658.97</v>
+      </c>
+      <c r="N96" t="n">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>7944.94</v>
+      </c>
+      <c r="D97" t="n">
+        <v>442.77</v>
+      </c>
+      <c r="E97" t="n">
+        <v>2949.02</v>
+      </c>
+      <c r="F97" t="n">
+        <v>4276.2</v>
+      </c>
+      <c r="G97" t="n">
+        <v>497.78</v>
+      </c>
+      <c r="H97" t="n">
+        <v>5377.79</v>
+      </c>
+      <c r="I97" t="n">
+        <v>5126.42</v>
+      </c>
+      <c r="J97" t="n">
+        <v>14336.61</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1783.64</v>
+      </c>
+      <c r="L97" t="n">
+        <v>2362.57</v>
+      </c>
+      <c r="M97" t="n">
+        <v>680.29</v>
+      </c>
+      <c r="N97" t="n">
+        <v>58.2</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>119091.19</v>
+      </c>
+      <c r="D98" t="n">
+        <v>3486.99</v>
+      </c>
+      <c r="E98" t="n">
+        <v>107253.93</v>
+      </c>
+      <c r="F98" t="n">
+        <v>59873.53</v>
+      </c>
+      <c r="G98" t="n">
+        <v>12972.05</v>
+      </c>
+      <c r="H98" t="n">
+        <v>17373.78</v>
+      </c>
+      <c r="I98" t="n">
+        <v>27961.01</v>
+      </c>
+      <c r="J98" t="n">
+        <v>25910.79</v>
+      </c>
+      <c r="K98" t="n">
+        <v>4517.36</v>
+      </c>
+      <c r="L98" t="n">
+        <v>17656.18</v>
+      </c>
+      <c r="M98" t="n">
+        <v>2165.79</v>
+      </c>
+      <c r="N98" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>7546.25</v>
+      </c>
+      <c r="D99" t="n">
+        <v>485.85</v>
+      </c>
+      <c r="E99" t="n">
+        <v>6808.69</v>
+      </c>
+      <c r="F99" t="n">
+        <v>4598.21</v>
+      </c>
+      <c r="G99" t="n">
+        <v>294.47</v>
+      </c>
+      <c r="H99" t="n">
+        <v>4822.1</v>
+      </c>
+      <c r="I99" t="n">
+        <v>4799.57</v>
+      </c>
+      <c r="J99" t="n">
+        <v>14467.13</v>
+      </c>
+      <c r="K99" t="n">
+        <v>1855.42</v>
+      </c>
+      <c r="L99" t="n">
+        <v>1800.74</v>
+      </c>
+      <c r="M99" t="n">
+        <v>563.7</v>
+      </c>
+      <c r="N99" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>111165.62</v>
+      </c>
+      <c r="D100" t="n">
+        <v>3553.6</v>
+      </c>
+      <c r="E100" t="n">
+        <v>109672.83</v>
+      </c>
+      <c r="F100" t="n">
+        <v>58025.86</v>
+      </c>
+      <c r="G100" t="n">
+        <v>9281.33</v>
+      </c>
+      <c r="H100" t="n">
+        <v>14062.3</v>
+      </c>
+      <c r="I100" t="n">
+        <v>24140.09</v>
+      </c>
+      <c r="J100" t="n">
+        <v>29218.5</v>
+      </c>
+      <c r="K100" t="n">
+        <v>4579.04</v>
+      </c>
+      <c r="L100" t="n">
+        <v>13736.1</v>
+      </c>
+      <c r="M100" t="n">
+        <v>2068.74</v>
+      </c>
+      <c r="N100" t="n">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D109"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Complementariedad comercial (MICHAELY, 1996). MERCOSUR: Argentina, Brasil, Paraguay y Uruguay; Venezuela de 2012 a 2016 (suspendida desde entonces); Bolivia, miembro desde 2024, aún sin datos (la serie empieza antes del Tratado de Asunción)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>UN Comtrade, API pública, grupos de 3 dígitos de la CUCI (Rev. 1 hasta 1995, Rev. 3 de 1996 a 2006 y Rev. 4 desde 2007): exportaciones del primer país y importaciones del segundo, con el mundo. Cálculo propio (Code/indicadores_bloque.py).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Exportador</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Importador</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Índice (0-100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1965</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1965</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1965</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1965</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1975</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1975</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1975</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1975</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1975</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1975</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1975</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1975</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1975</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>38.2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>33.7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>33.8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>42.9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>44.2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>36.6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>45.9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>38.7</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>37.3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>46.4</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>38.3</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>34.3</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>38.7</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>50.9</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>40.9</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>36.7</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>44.4</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>47.9</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>19.9</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>16.1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>35.3</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>29.3</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>34.7</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>39.3</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>39.6</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>18.9</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>19.4</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>33.8</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>34.6</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>44.6</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>31.6</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>16.1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Saldo comercial de cada miembro con el resto del bloque, % del PIB. MERCOSUR: Argentina, Brasil, Paraguay y Uruguay; Venezuela de 2012 a 2016 (suspendida desde entonces); Bolivia, miembro desde 2024, aún sin datos (la serie empieza antes del Tratado de Asunción)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Exportaciones a los socios menos importaciones desde ellos (exportaciones declaradas por los socios), con Code/datos_comercio.py; PIB en dólares corrientes del Banco Mundial (WDI). Cálculo propio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1970</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-1.94</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-1.35</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1972</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-2.12</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1974</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-7.84</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1975</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-6.64</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1976</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-9.06</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-3.78</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1977</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-10.09</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-4.41</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1978</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-12.07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-1.76</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1979</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-12.49</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-2.35</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1980</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-10.97</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-1.53</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1981</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-8.880000000000001</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-1.92</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1982</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-6.15</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1983</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-4.24</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1984</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-7.41</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-9.07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1986</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-9.06</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1987</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-6.82</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-2.96</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1988</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-6.24</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-3.85</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1989</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-2.69</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-2.41</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-2.67</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-6.08</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B26" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-8.09</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-2.83</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B27" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-14.44</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-4.22</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B28" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-14.63</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-2.81</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B29" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-15.77</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-2.67</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B30" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-13.27</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-1.72</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B31" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-15.11</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-15.38</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B33" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-12.23</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-2.09</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="D34" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-2.59</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B35" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="D35" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-3.47</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B36" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="D36" t="n">
+        <v>13.48</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-3.75</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B37" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="D37" t="n">
+        <v>11.07</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-4.4</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B38" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D38" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-7.54</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B39" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="D39" t="n">
+        <v>8</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-8.119999999999999</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B40" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-8.24</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B41" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-5.51</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B42" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="D42" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-6.36</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B43" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-4.59</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B44" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D44" t="n">
+        <v>-3.84</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-2.35</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B45" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="D45" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-3.65</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B46" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-1.62</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-2.61</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-2.04</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B47" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="D47" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-2.82</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B48" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-2.94</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B49" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-4.12</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B50" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-3.47</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B51" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D51" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-2.71</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B52" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-1.94</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B53" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-2.7</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B54" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="D54" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-3.33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Reparto entre los miembros de las exportaciones de manufacturas dentro del bloque (%). MERCOSUR: Argentina, Brasil, Paraguay y Uruguay; Venezuela de 2012 a 2016 (suspendida desde entonces); Bolivia, miembro desde 2024, aún sin datos (la serie empieza antes del Tratado de Asunción)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>UN Comtrade, API pública (CUCI, secciones 5 a 8; revisiones como en la hoja de composición). Cálculo propio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1970</v>
+      </c>
+      <c r="B5" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="C5" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B6" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1972</v>
+      </c>
+      <c r="B7" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1974</v>
+      </c>
+      <c r="B8" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1975</v>
+      </c>
+      <c r="B9" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>61</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1976</v>
+      </c>
+      <c r="B10" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="C10" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1977</v>
+      </c>
+      <c r="B11" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="C11" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9.699999999999999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1978</v>
+      </c>
+      <c r="B12" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="C12" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E12" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1979</v>
+      </c>
+      <c r="B13" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1980</v>
+      </c>
+      <c r="B14" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1981</v>
+      </c>
+      <c r="B15" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="C15" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1982</v>
+      </c>
+      <c r="B16" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E16" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1983</v>
+      </c>
+      <c r="B17" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="C17" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E17" t="n">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1984</v>
+      </c>
+      <c r="B18" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="C18" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B19" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="C19" t="n">
+        <v>68</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1986</v>
+      </c>
+      <c r="B20" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="C20" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E20" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1987</v>
+      </c>
+      <c r="B21" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>59</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1988</v>
+      </c>
+      <c r="B22" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="C22" t="n">
+        <v>62</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E22" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1989</v>
+      </c>
+      <c r="B23" t="n">
+        <v>34</v>
+      </c>
+      <c r="C23" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E23" t="n">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B24" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="C24" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E24" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B25" t="n">
+        <v>29</v>
+      </c>
+      <c r="C25" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B26" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="C26" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E26" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B27" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="C27" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E27" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B28" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C28" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B29" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="C29" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B30" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="C30" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B31" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="C31" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B32" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="C32" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E32" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B33" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="C33" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E33" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B34" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="C34" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E34" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B35" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="C35" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B36" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="C36" t="n">
+        <v>45</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B37" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="C37" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B38" t="n">
+        <v>30</v>
+      </c>
+      <c r="C38" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E38" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B39" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="C39" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B40" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="C40" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E40" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B41" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="C41" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B42" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="C42" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B43" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="C43" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B44" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="C44" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B45" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="C45" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B46" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="C46" t="n">
+        <v>68</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E46" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B47" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="C47" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="D47" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B48" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="C48" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="D48" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E48" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B49" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="C49" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>5</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B50" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="C50" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="D50" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E50" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B51" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="C51" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="D51" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E51" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B52" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="C52" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="D52" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Ejercicio-3/Parte-B/3.B.35/Code/datos/tablas_figuras.xlsx
+++ b/Ejercicio-3/Parte-B/3.B.35/Code/datos/tablas_figuras.xlsx
@@ -55,6 +55,13 @@
     <sheet name="MERCOSUR_complementariedad" sheetId="46" state="visible" r:id="rId46"/>
     <sheet name="MERCOSUR_saldos" sheetId="47" state="visible" r:id="rId47"/>
     <sheet name="MERCOSUR_reparto_manuf" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet name="CEFTA_convergencia" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet name="CEFTA_ancla" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet name="AFCFTA_composicion" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet name="AFCFTA_materias" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet name="AFCFTA_aranceles" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet name="PAFTA_sin_petroleo" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet name="PAFTA_composicion" sheetId="55" state="visible" r:id="rId55"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -47553,6 +47560,1226 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>PIB per cápita en PPA de los miembros del CEFTA y de los últimos en adherirse a la UE, en % de la UE-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Banco Mundial (WDI), NY.GDP.PCAP.PP.KD (dólares internacionales constantes de 2021); UE-27 = agregado EUU. Cálculo propio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BIH</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>MKD</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>MNE</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SRB</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>MDA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>XKX</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>BGR</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ROU</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>HRV</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B5" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="C5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="K5" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="I6" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="K6" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B7" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B8" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>46.6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B9" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D9" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>19</v>
+      </c>
+      <c r="I9" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="K9" t="n">
+        <v>47.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B10" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="C10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="F10" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="G10" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>49.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B11" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="C11" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="D11" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="I11" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>52.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>40</v>
+      </c>
+      <c r="F12" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="G12" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="I12" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>54.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B13" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="C13" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="F13" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="G13" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="I13" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>54.6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B14" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="C14" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E14" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>27</v>
+      </c>
+      <c r="G14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B15" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="C15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E15" t="n">
+        <v>36</v>
+      </c>
+      <c r="F15" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="G15" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>37</v>
+      </c>
+      <c r="K15" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B16" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="C16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>29</v>
+      </c>
+      <c r="G16" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="I16" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="J16" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="K16" t="n">
+        <v>55.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B17" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="C17" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="F17" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="G17" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="I17" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>58.3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B18" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="D18" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="E18" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="G18" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="I18" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B19" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="C19" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="D19" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="E19" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="F19" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="I19" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="K19" t="n">
+        <v>62.1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B20" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="C20" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="D20" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E20" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="F20" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="G20" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="I20" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>63.6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B21" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="C21" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E21" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="F21" t="n">
+        <v>35</v>
+      </c>
+      <c r="G21" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="K21" t="n">
+        <v>64.59999999999999</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B22" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="C22" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="E22" t="n">
+        <v>41</v>
+      </c>
+      <c r="F22" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="G22" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="K22" t="n">
+        <v>65.90000000000001</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B23" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="C23" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="D23" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="G23" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="H23" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="I23" t="n">
+        <v>47</v>
+      </c>
+      <c r="J23" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>66.90000000000001</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B24" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="C24" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="D24" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="F24" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="G24" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="H24" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I24" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="J24" t="n">
+        <v>58</v>
+      </c>
+      <c r="K24" t="n">
+        <v>65.3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B25" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>37</v>
+      </c>
+      <c r="E25" t="n">
+        <v>43</v>
+      </c>
+      <c r="F25" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="G25" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="H25" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>48</v>
+      </c>
+      <c r="J25" t="n">
+        <v>55</v>
+      </c>
+      <c r="K25" t="n">
+        <v>63.4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B26" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="C26" t="n">
+        <v>27</v>
+      </c>
+      <c r="D26" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="G26" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="K26" t="n">
+        <v>62.3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B27" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="C27" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="D27" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="E27" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="F27" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="G27" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="H27" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="I27" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>61.7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B28" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C28" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="D28" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="E28" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="G28" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="H28" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="K28" t="n">
+        <v>62.1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B29" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="C29" t="n">
+        <v>29</v>
+      </c>
+      <c r="D29" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="E29" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="F29" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="G29" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="I29" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="K29" t="n">
+        <v>61.3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B30" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="C30" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="D30" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="E30" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="G30" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="H30" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="I30" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="J30" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="K30" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B31" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="C31" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="D31" t="n">
+        <v>41</v>
+      </c>
+      <c r="E31" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="H31" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="I31" t="n">
+        <v>53</v>
+      </c>
+      <c r="J31" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="K31" t="n">
+        <v>63.8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B32" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="C32" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="E32" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="F32" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="H32" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="I32" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="J32" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="K32" t="n">
+        <v>65.09999999999999</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B33" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="C33" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>41</v>
+      </c>
+      <c r="E33" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="F33" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="G33" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="H33" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="J33" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="K33" t="n">
+        <v>66.5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B34" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="C34" t="n">
+        <v>33</v>
+      </c>
+      <c r="D34" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="F34" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="G34" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="H34" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="I34" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="J34" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="K34" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B35" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="C35" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="D35" t="n">
+        <v>43</v>
+      </c>
+      <c r="E35" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F35" t="n">
+        <v>44</v>
+      </c>
+      <c r="G35" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="H35" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="I35" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="J35" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="K35" t="n">
+        <v>66.59999999999999</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B36" t="n">
+        <v>35</v>
+      </c>
+      <c r="C36" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="E36" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F36" t="n">
+        <v>45</v>
+      </c>
+      <c r="G36" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="H36" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="I36" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="J36" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="K36" t="n">
+        <v>71.09999999999999</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B37" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="C37" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="D37" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="E37" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="F37" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="G37" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="H37" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I37" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="J37" t="n">
+        <v>73</v>
+      </c>
+      <c r="K37" t="n">
+        <v>74.09999999999999</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B38" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="C38" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="D38" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="E38" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="F38" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="G38" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="H38" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="I38" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="J38" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="K38" t="n">
+        <v>76.7</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B39" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="C39" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="D39" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="E39" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="F39" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="G39" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="H39" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="I39" t="n">
+        <v>63</v>
+      </c>
+      <c r="J39" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="K39" t="n">
+        <v>78.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -48111,6 +49338,4021 @@
       </c>
       <c r="E34" t="n">
         <v>3168471.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Peso de la UE-27 y de los socios del CEFTA en las exportaciones e importaciones de los miembros del CEFTA (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>WITS (Banco Mundial), exportaciones e importaciones declaradas por cada miembro; UE-27 como suma de sus Estados miembros. Kosovo no declara. Cálculo propio (Code/figuras_afinidad.py).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Flujo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>UE-27 (%)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Socios del CEFTA (%)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ALB: UE / CEFTA</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>BIH: UE / CEFTA</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>MKD: UE / CEFTA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>MNE: UE / CEFTA</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>SRB: UE / CEFTA</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>MDA: UE / CEFTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>21</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>88.8 / 7.3</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>78.1 / 14.2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>64.9 / 27.6</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>67.9 / 30.3</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>58.3 / 26.5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>48.5 / 0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>83.0 / 9.8</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>75.3 / 17.4</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>67.8 / 24.6</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>69.9 / 27.7</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>58.0 / 28.5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>48.1 / 0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>79.8 / 13.4</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>71.3 / 19.8</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>63.6 / 29.7</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>62.4 / 34.2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>56.8 / 29.2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>48.3 / 0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>84.7 / 6.4</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>70.6 / 18.8</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>60.5 / 31.3</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>50.9 / 42.9</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>55.7 / 28.2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>47.3 / 0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>70.1 / 10.2</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>69.1 / 18.5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>63.7 / 26.7</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>55.9 / 38.3</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>58.9 / 25.6</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>42.0 / 0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>72.8 / 12.3</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>70.0 / 18.3</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>62.3 / 24.7</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>58.9 / 25.2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>60.1 / 23.3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>44.3 / 0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="D11" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>75.5 / 11.8</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>72.3 / 14.5</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>63.7 / 22.0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>50.0 / 33.1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>60.1 / 21.7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>43.0 / 0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>16</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>76.1 / 10.7</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>73.0 / 14.0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>70.8 / 17.6</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>40.1 / 44.7</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>61.6 / 18.9</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>42.5 / 0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>77.3 / 11.6</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>71.5 / 14.2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>75.2 / 13.9</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>34.2 / 39.1</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>63.6 / 19.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>48.6 / 0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>75.1 / 14.2</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>70.9 / 13.2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>76.0 / 12.7</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>33.9 / 37.0</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>64.2 / 18.6</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>54.9 / 0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="D15" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>77.7 / 13.6</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>70.8 / 13.1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>78.8 / 12.4</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>35.6 / 39.8</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>64.4 / 17.8</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>59.6 / 0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>77.0 / 14.9</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>70.4 / 16.2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2.2 / 0.1</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>33.3 / 35.0</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>64.2 / 17.4</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>60.2 / 0.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>76.0 / 16.4</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>72.2 / 16.3</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>80.3 / 11.0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>42.2 / 36.5</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>65.4 / 17.4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>65.9 / 0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="D18" t="n">
+        <v>15</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>75.7 / 16.7</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>72.3 / 16.6</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>78.5 / 11.6</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>37.1 / 37.8</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>64.8 / 17.0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>64.1 / 0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="D19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>74.5 / 17.9</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>72.4 / 16.0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>77.6 / 11.0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>36.2 / 39.5</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>64.9 / 15.9</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>66.5 / 0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="D20" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>68.6 / 16.9</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>72.9 / 16.8</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>77.4 / 11.8</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>31.2 / 37.9</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>64.5 / 15.8</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>61.0 / 1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="D21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>72.6 / 24.1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>73.6 / 18.4</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>78.3 / 12.1</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>30.3 / 38.1</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>64.1 / 15.9</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>58.6 / 0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="D22" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>71.8 / 18.1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>73.0 / 18.7</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>78.7 / 12.7</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>35.5 / 45.0</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>63.2 / 15.4</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>65.4 / 0.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>55</v>
+      </c>
+      <c r="D23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>65.5 / 3.4</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>69.5 / 10.9</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>54.0 / 8.6</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>50.6 / 30.1</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>47.3 / 5.4</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>44.1 / 0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="D24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>59.6 / 5.9</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>64.9 / 11.5</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>50.8 / 9.7</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>48.2 / 29.5</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>56.8 / 5.3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>44.6 / 0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="D25" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>60.7 / 7.3</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>64.4 / 11.8</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>49.1 / 9.1</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>46.2 / 30.6</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>54.5 / 5.5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>41.8 / 0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>57</v>
+      </c>
+      <c r="D26" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>64.7 / 5.0</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>63.3 / 11.8</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>53.3 / 9.5</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>41.3 / 34.3</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>58.2 / 5.5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>41.9 / 0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="D27" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>65.0 / 7.2</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>60.3 / 11.9</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>50.1 / 9.4</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>41.8 / 35.6</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>57.4 / 6.1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>42.9 / 0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="D28" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>64.2 / 7.4</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>59.1 / 10.6</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>47.9 / 9.5</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>39.9 / 38.2</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>56.8 / 6.1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>42.3 / 0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="D29" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>62.2 / 7.9</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>60.6 / 10.7</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>51.6 / 9.5</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>43.5 / 38.3</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>59.7 / 5.1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>43.4 / 0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="D30" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>63.4 / 6.8</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>59.2 / 11.0</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>51.7 / 10.0</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>43.4 / 38.6</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>60.8 / 4.9</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>43.9 / 0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>60.1 / 7.9</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>58.0 / 11.4</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>51.2 / 10.3</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>45.1 / 37.3</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>61.9 / 4.5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>47.0 / 0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="D32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>60.8 / 7.6</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>59.9 / 12.3</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>52.4 / 9.9</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>40.6 / 37.8</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>61.2 / 4.1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>47.7 / 0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="D33" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>62.5 / 6.6</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>61.0 / 12.7</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>51.3 / 9.8</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>47.3 / 30.3</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>62.0 / 4.0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>47.6 / 0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="D34" t="n">
+        <v>8</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>60.7 / 7.9</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>60.0 / 12.8</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>52.8 / 9.6</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>46.5 / 31.0</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>61.1 / 4.2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>48.3 / 0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="D35" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>60.0 / 7.0</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>59.6 / 12.1</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>52.9 / 8.9</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>47.0 / 28.3</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>59.2 / 4.2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>48.4 / 0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="D36" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>56.7 / 5.5</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>61.1 / 12.4</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>50.9 / 9.2</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>46.8 / 29.8</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>57.3 / 4.0</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>48.5 / 0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="D37" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>57.7 / 7.5</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>60.8 / 12.7</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>46.2 / 9.7</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>44.1 / 28.6</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>58.8 / 3.8</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>45.6 / 0.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="D38" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>53.8 / 7.4</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>59.0 / 12.8</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>46.2 / 9.4</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>45.5 / 28.3</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>57.1 / 4.4</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>43.9 / 0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>57.4 / 10.3</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>56.9 / 12.3</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>46.8 / 8.7</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>44.3 / 25.4</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>54.9 / 5.2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>47.3 / 0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="D40" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>50.9 / 6.4</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>59.0 / 11.7</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>49.2 / 9.0</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>45.7 / 25.2</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>56.9 / 4.6</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>48.3 / 0.7</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Manufacturas en las exportaciones de los países africanos a África y fuera de África (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>WITS (Banco Mundial), grupo «manuf» (CUCI 5 a 8 sin 667 y 68) y total, exportaciones declaradas por cada país a cada socio; solo los países que declaran cada año. Cálculo propio (Code/figuras_afinidad.py).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>A África (%)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Fuera de África (%)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Países que declaran</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AGO 2023: África / fuera</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>TUN 2023: África / fuera</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>MAR 2023: África / fuera</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>EGY 2023: África / fuera</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ZAF 2023: África / fuera</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>KEN 2023: África / fuera</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>GHA 2023: África / fuera</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>CIV 2023: África / fuera</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>TZA 2023: África / fuera</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>ETH 2023: África / fuera</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>NGA 2023: África / fuera</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B5" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="C5" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B6" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B7" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="C7" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="D7" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B8" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="C8" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B9" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B10" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="C10" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>40</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>72.8 / 2.4</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>71.9 / 80.0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>70.9 / 75.2</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>69.0 / 48.2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>61.9 / 32.9</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>57.6 / 14.3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>33.3 / 1.2</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>32.7 / 6.8</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>27.4 / 5.3</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>13.9 / 8.4</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>8.5 / 2.2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Estructura de las exportaciones de las grandes economías africanas y complementariedad entre ellas, 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>WITS (Banco Mundial): exportaciones por grupos de la CUCI (alimentos, materias primas agrícolas, combustibles, minerales y metales, manufacturas) y exportaciones e importaciones por las 16 secciones del SA de WITS (complementariedad aproximada, MICHAELY, 1996). Cálculo propio (Code/figuras_afinidad.py).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>País</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Alimentos (%)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Materias primas agrícolas (%)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Combustibles (%)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Minerales y metales (%)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Manufacturas (%)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Otros (%)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Complementariedad media con los demás</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TUN</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>63.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>61.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EGY</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F7" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>67.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ZAF</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="F8" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="n">
+        <v>61.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KEN</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>47.9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CIV</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="C10" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F10" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="G10" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="H10" t="n">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TZA</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F11" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>32.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>GHA</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>18</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>24</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G13" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="H13" t="n">
+        <v>39.6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AGO</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>30.7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NGA</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>29.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Arancel aplicado y de nación más favorecida de los países africanos según el origen de las importaciones (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>WITS (Banco Mundial), tradestats-tariff: AHS-WGHTD-AVRG y MFN-WGHTD-AVRG por socio, ponderados por las importaciones de cada socio (MPRT-TRD-VL); último año disponible entre 2019 y 2022. Comunidad = socio de la misma comunidad con libre comercio (CEDEAO, CEEAC, EAC, COMESA, SADC, UEMOA, CEMAC). Cálculo propio (Code/figuras_afinidad.py).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>País</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Aplicado, comunidad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Aplicado, resto de África</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Aplicado, fuera de África</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NMF, a África</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Importaciones desde África (USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AGO</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C5" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="D5" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>951044110.8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BDI</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>23.08</v>
+      </c>
+      <c r="G6" t="n">
+        <v>337075571.31</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="G7" t="n">
+        <v>567693170.35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BFA</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="F8" t="n">
+        <v>12.49</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1419494174.66</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BWA</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5854608627.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CAF</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D10" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="F10" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>22459046.35</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CIV</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="E11" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4021617897.02</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CMR</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D12" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="E12" t="n">
+        <v>17.33</v>
+      </c>
+      <c r="F12" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="G12" t="n">
+        <v>371674071.87</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C13" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="E13" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="F13" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1379316852.59</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>COG</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D14" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="E14" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="G14" t="n">
+        <v>202024283.93</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>COM</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="G15" t="n">
+        <v>22904623.97</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="D16" t="n">
+        <v>17.36</v>
+      </c>
+      <c r="E16" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="F16" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="G16" t="n">
+        <v>70756941.48999999</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EGY</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="F17" t="n">
+        <v>19.22</v>
+      </c>
+      <c r="G17" t="n">
+        <v>761727452.4299999</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C18" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="E18" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="F18" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1029169935.49</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>GAB</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D19" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.03</v>
+      </c>
+      <c r="F19" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="G19" t="n">
+        <v>186213242.18</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>GHA</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="E20" t="n">
+        <v>12.21</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1237100115.8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>GMB</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>18.37</v>
+      </c>
+      <c r="E21" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="F21" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="G21" t="n">
+        <v>90345213.42</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>KEN</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C22" t="n">
+        <v>14.03</v>
+      </c>
+      <c r="D22" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="E22" t="n">
+        <v>11.52</v>
+      </c>
+      <c r="F22" t="n">
+        <v>24.16</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2294567366.06</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>LBR</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="E23" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="F23" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="G23" t="n">
+        <v>49785499.63</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>LSO</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="F24" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1544637963.59</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E25" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="F25" t="n">
+        <v>11.87</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2518423003.76</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MDG</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C26" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="D26" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="E26" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="F26" t="n">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="G26" t="n">
+        <v>737281525.1799999</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MLI</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="E27" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="F27" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2096499380.4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MOZ</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="F28" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2716694116.89</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MRT</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D29" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="E29" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="F29" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="G29" t="n">
+        <v>493725760.13</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MUS</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G30" t="n">
+        <v>894165200.62</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MWI</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C31" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="D31" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="E31" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="F31" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="G31" t="n">
+        <v>900781299.25</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>NAM</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C32" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="D32" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="F32" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3123882039.18</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NER</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="E33" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="F33" t="n">
+        <v>14.76</v>
+      </c>
+      <c r="G33" t="n">
+        <v>607050897.11</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>NGA</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="E34" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="F34" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1749043591</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>RWA</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="D35" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="E35" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="F35" t="n">
+        <v>25.16</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1409956136.3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SEN</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="E36" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="F36" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1430596294.78</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>STP</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C37" t="n">
+        <v>20</v>
+      </c>
+      <c r="D37" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="E37" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="F37" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="G37" t="n">
+        <v>989374.77</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SWZ</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C38" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="F38" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1622034238.66</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SYC</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="D39" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G39" t="n">
+        <v>169149139.64</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TGO</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="E40" t="n">
+        <v>13.07</v>
+      </c>
+      <c r="F40" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="G40" t="n">
+        <v>265012207.4</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TZA</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D41" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="E41" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="F41" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1605554493.25</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>UGA</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D42" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="E42" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="F42" t="n">
+        <v>24.97</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1692966805.45</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ZAF</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E43" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="F43" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="G43" t="n">
+        <v>9537394398.440001</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ZMB</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="D44" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="E44" t="n">
+        <v>55.07</v>
+      </c>
+      <c r="F44" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="G44" t="n">
+        <v>4150351584.85</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ZWE</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C45" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="D45" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="E45" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F45" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="G45" t="n">
+        <v>4096558244.66</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Exportaciones de los miembros de la PAFTA a otros miembros, con y sin combustibles (% del total)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>WITS (Banco Mundial), exportaciones declaradas por cada miembro, total y grupo «Fuels» (CUCI 3); solo los miembros que declaran cada año (al menos la mitad). El petróleo que se declara sin destino cuenta en el total pero no en ningún socio. Cálculo propio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Todas las exportaciones (%)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Sin combustibles (%)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Miembros que declaran</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B7" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="C7" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C8" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="D8" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C9" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="C10" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B11" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C12" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="D12" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B13" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C13" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B14" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="C14" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="C15" t="n">
+        <v>27</v>
+      </c>
+      <c r="D15" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B16" t="n">
+        <v>9</v>
+      </c>
+      <c r="C16" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B17" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C17" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B18" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="C18" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B19" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="C19" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="C20" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B21" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="C21" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="D21" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B22" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="C22" t="n">
+        <v>20</v>
+      </c>
+      <c r="D22" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B23" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="C23" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="D23" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B24" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="C24" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B25" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="C25" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B26" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="C26" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B27" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="C27" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B28" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="C28" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="C29" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="D29" t="n">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Composición de las exportaciones de los miembros de la PAFTA a otros miembros y fuera de la PAFTA (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>WITS (Banco Mundial), exportaciones declaradas por grupos de la CUCI. «Otros y sin clasificar» incluye el petróleo declarado sin desglose de producto. Cálculo propio (Code/figuras_afinidad.py).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Destino</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Alimentos (%)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Materias primas agrícolas (%)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Combustibles (%)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Minerales y metales (%)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Manufacturas (%)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Otros (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G7" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6.1</v>
       </c>
     </row>
   </sheetData>

--- a/Ejercicio-3/Parte-B/3.B.35/Code/datos/tablas_figuras.xlsx
+++ b/Ejercicio-3/Parte-B/3.B.35/Code/datos/tablas_figuras.xlsx
@@ -51770,22 +51770,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C5" t="n">
-        <v>13.56</v>
+        <v>19.71</v>
       </c>
       <c r="D5" t="n">
-        <v>12.06</v>
+        <v>13.39</v>
       </c>
       <c r="E5" t="n">
-        <v>8.359999999999999</v>
+        <v>12.07</v>
       </c>
       <c r="F5" t="n">
-        <v>13.1</v>
+        <v>15.64</v>
       </c>
       <c r="G5" t="n">
-        <v>951044110.8</v>
+        <v>1204584255.78</v>
       </c>
     </row>
     <row r="6">
@@ -51795,22 +51795,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="D6" t="n">
-        <v>12.74</v>
+        <v>15.96</v>
       </c>
       <c r="E6" t="n">
-        <v>10.12</v>
+        <v>9.17</v>
       </c>
       <c r="F6" t="n">
-        <v>23.08</v>
+        <v>24.36</v>
       </c>
       <c r="G6" t="n">
-        <v>337075571.31</v>
+        <v>308315205.21</v>
       </c>
     </row>
     <row r="7">
@@ -51820,22 +51820,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>9.25</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>10.85</v>
+        <v>11.29</v>
       </c>
       <c r="F7" t="n">
-        <v>10.16</v>
+        <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>567693170.35</v>
+        <v>606400220.78</v>
       </c>
     </row>
     <row r="8">
@@ -51845,22 +51845,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>3.8</v>
+        <v>4.38</v>
       </c>
       <c r="E8" t="n">
-        <v>7.93</v>
+        <v>7.82</v>
       </c>
       <c r="F8" t="n">
-        <v>12.49</v>
+        <v>12.73</v>
       </c>
       <c r="G8" t="n">
-        <v>1419494174.66</v>
+        <v>1226339315.57</v>
       </c>
     </row>
     <row r="9">
@@ -51870,22 +51870,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C9" t="n">
-        <v>2.74</v>
+        <v>0.31</v>
       </c>
       <c r="D9" t="n">
-        <v>7.16</v>
+        <v>7.96</v>
       </c>
       <c r="E9" t="n">
-        <v>3.46</v>
+        <v>1.15</v>
       </c>
       <c r="F9" t="n">
-        <v>7.98</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>5854608627.5</v>
+        <v>5225078128.78</v>
       </c>
     </row>
     <row r="10">
@@ -51917,22 +51917,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>8.81</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>7.81</v>
+        <v>8.73</v>
       </c>
       <c r="F11" t="n">
-        <v>5.67</v>
+        <v>6.08</v>
       </c>
       <c r="G11" t="n">
-        <v>4021617897.02</v>
+        <v>2684932850.6</v>
       </c>
     </row>
     <row r="12">
@@ -52036,22 +52036,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C16" t="n">
-        <v>0.39</v>
+        <v>0.28</v>
       </c>
       <c r="D16" t="n">
-        <v>17.36</v>
+        <v>10.9</v>
       </c>
       <c r="E16" t="n">
-        <v>12.37</v>
+        <v>10.22</v>
       </c>
       <c r="F16" t="n">
-        <v>17.15</v>
+        <v>10.96</v>
       </c>
       <c r="G16" t="n">
-        <v>70756941.48999999</v>
+        <v>35981705.72</v>
       </c>
     </row>
     <row r="17">
@@ -52136,22 +52136,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>8.67</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>12.21</v>
+        <v>10.65</v>
       </c>
       <c r="F20" t="n">
-        <v>10.07</v>
+        <v>11.67</v>
       </c>
       <c r="G20" t="n">
-        <v>1237100115.8</v>
+        <v>1570813372.57</v>
       </c>
     </row>
     <row r="21">
@@ -52161,22 +52161,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>18.37</v>
+        <v>18.2</v>
       </c>
       <c r="E21" t="n">
-        <v>13.45</v>
+        <v>13.17</v>
       </c>
       <c r="F21" t="n">
-        <v>16.9</v>
+        <v>16.61</v>
       </c>
       <c r="G21" t="n">
-        <v>90345213.42</v>
+        <v>217160662.91</v>
       </c>
     </row>
     <row r="22">
@@ -52186,22 +52186,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C22" t="n">
-        <v>14.03</v>
+        <v>2.82</v>
       </c>
       <c r="D22" t="n">
-        <v>6.84</v>
+        <v>10.35</v>
       </c>
       <c r="E22" t="n">
-        <v>11.52</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>24.16</v>
+        <v>28.12</v>
       </c>
       <c r="G22" t="n">
-        <v>2294567366.06</v>
+        <v>2082304715.01</v>
       </c>
     </row>
     <row r="23">
@@ -52211,22 +52211,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>11.57</v>
+        <v>14.02</v>
       </c>
       <c r="E23" t="n">
-        <v>9.529999999999999</v>
+        <v>10.32</v>
       </c>
       <c r="F23" t="n">
-        <v>11.83</v>
+        <v>14.16</v>
       </c>
       <c r="G23" t="n">
-        <v>49785499.63</v>
+        <v>33434518.2</v>
       </c>
     </row>
     <row r="24">
@@ -52236,22 +52236,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C24" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>5.84</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>4.69</v>
+        <v>3.17</v>
       </c>
       <c r="F24" t="n">
-        <v>10.57</v>
+        <v>12.27</v>
       </c>
       <c r="G24" t="n">
-        <v>1544637963.59</v>
+        <v>1283905541.77</v>
       </c>
     </row>
     <row r="25">
@@ -52261,19 +52261,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D25" t="n">
-        <v>1.11</v>
+        <v>0.97</v>
       </c>
       <c r="E25" t="n">
-        <v>6.96</v>
+        <v>3.96</v>
       </c>
       <c r="F25" t="n">
-        <v>11.87</v>
+        <v>12.64</v>
       </c>
       <c r="G25" t="n">
-        <v>2518423003.76</v>
+        <v>2209677095.37</v>
       </c>
     </row>
     <row r="26">
@@ -52283,22 +52283,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C26" t="n">
-        <v>8.140000000000001</v>
+        <v>3.97</v>
       </c>
       <c r="D26" t="n">
-        <v>12.28</v>
+        <v>11.28</v>
       </c>
       <c r="E26" t="n">
-        <v>8.779999999999999</v>
+        <v>7.12</v>
       </c>
       <c r="F26" t="n">
-        <v>9.789999999999999</v>
+        <v>12.33</v>
       </c>
       <c r="G26" t="n">
-        <v>737281525.1799999</v>
+        <v>674841386.13</v>
       </c>
     </row>
     <row r="27">
@@ -52333,22 +52333,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>7.56</v>
+        <v>6.61</v>
       </c>
       <c r="E28" t="n">
-        <v>4.42</v>
+        <v>5.4</v>
       </c>
       <c r="F28" t="n">
-        <v>8.58</v>
+        <v>8.51</v>
       </c>
       <c r="G28" t="n">
-        <v>2716694116.89</v>
+        <v>2684781614.41</v>
       </c>
     </row>
     <row r="29">
@@ -52358,19 +52358,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D29" t="n">
-        <v>8.720000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>8.84</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>8.720000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>493725760.13</v>
+        <v>439429615.63</v>
       </c>
     </row>
     <row r="30">
@@ -52380,22 +52380,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C30" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>4.3</v>
+        <v>0.11</v>
       </c>
       <c r="E30" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="F30" t="n">
-        <v>1.05</v>
+        <v>0.91</v>
       </c>
       <c r="G30" t="n">
-        <v>894165200.62</v>
+        <v>626086169.5700001</v>
       </c>
     </row>
     <row r="31">
@@ -52430,22 +52430,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C32" t="n">
-        <v>3.27</v>
+        <v>0.16</v>
       </c>
       <c r="D32" t="n">
-        <v>4.11</v>
+        <v>14.48</v>
       </c>
       <c r="E32" t="n">
-        <v>3.67</v>
+        <v>2.97</v>
       </c>
       <c r="F32" t="n">
-        <v>10.64</v>
+        <v>12.33</v>
       </c>
       <c r="G32" t="n">
-        <v>3123882039.18</v>
+        <v>3108338702.96</v>
       </c>
     </row>
     <row r="33">
@@ -52455,22 +52455,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>2.52</v>
+        <v>3.08</v>
       </c>
       <c r="E33" t="n">
-        <v>9.4</v>
+        <v>9.01</v>
       </c>
       <c r="F33" t="n">
-        <v>14.76</v>
+        <v>16.77</v>
       </c>
       <c r="G33" t="n">
-        <v>607050897.11</v>
+        <v>613708212.34</v>
       </c>
     </row>
     <row r="34">
@@ -52480,22 +52480,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>8.49</v>
+        <v>9.08</v>
       </c>
       <c r="E34" t="n">
-        <v>9.08</v>
+        <v>10.83</v>
       </c>
       <c r="F34" t="n">
-        <v>9.300000000000001</v>
+        <v>9.94</v>
       </c>
       <c r="G34" t="n">
-        <v>1749043591</v>
+        <v>1004758955.42</v>
       </c>
     </row>
     <row r="35">
@@ -52505,22 +52505,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C35" t="n">
-        <v>1.32</v>
+        <v>0.71</v>
       </c>
       <c r="D35" t="n">
-        <v>20.24</v>
+        <v>28.71</v>
       </c>
       <c r="E35" t="n">
-        <v>15.72</v>
+        <v>13.62</v>
       </c>
       <c r="F35" t="n">
-        <v>25.16</v>
+        <v>22.88</v>
       </c>
       <c r="G35" t="n">
-        <v>1409956136.3</v>
+        <v>1150118515.52</v>
       </c>
     </row>
     <row r="36">
@@ -52530,22 +52530,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>9.58</v>
+        <v>10.87</v>
       </c>
       <c r="E36" t="n">
-        <v>8.98</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>7.89</v>
+        <v>8.25</v>
       </c>
       <c r="G36" t="n">
-        <v>1430596294.78</v>
+        <v>1303126876.8</v>
       </c>
     </row>
     <row r="37">
@@ -52580,22 +52580,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C38" t="n">
-        <v>2.74</v>
+        <v>0.01</v>
       </c>
       <c r="D38" t="n">
-        <v>2.8</v>
+        <v>4.87</v>
       </c>
       <c r="E38" t="n">
-        <v>4.88</v>
+        <v>3.78</v>
       </c>
       <c r="F38" t="n">
-        <v>9.109999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G38" t="n">
-        <v>1622034238.66</v>
+        <v>1603658639.66</v>
       </c>
     </row>
     <row r="39">
@@ -52605,22 +52605,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C39" t="n">
-        <v>1.08</v>
+        <v>0.98</v>
       </c>
       <c r="D39" t="n">
-        <v>6.4</v>
+        <v>4.69</v>
       </c>
       <c r="E39" t="n">
-        <v>1.55</v>
+        <v>3.65</v>
       </c>
       <c r="F39" t="n">
-        <v>3.1</v>
+        <v>3.98</v>
       </c>
       <c r="G39" t="n">
-        <v>169149139.64</v>
+        <v>402117461.92</v>
       </c>
     </row>
     <row r="40">
@@ -52630,22 +52630,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>10.76</v>
+        <v>9.76</v>
       </c>
       <c r="E40" t="n">
-        <v>13.07</v>
+        <v>11.27</v>
       </c>
       <c r="F40" t="n">
-        <v>6.76</v>
+        <v>12.48</v>
       </c>
       <c r="G40" t="n">
-        <v>265012207.4</v>
+        <v>414699470.15</v>
       </c>
     </row>
     <row r="41">
@@ -52655,22 +52655,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C41" t="n">
-        <v>0.02</v>
+        <v>0.21</v>
       </c>
       <c r="D41" t="n">
-        <v>9.17</v>
+        <v>19.78</v>
       </c>
       <c r="E41" t="n">
-        <v>9.31</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>17.71</v>
+        <v>17.23</v>
       </c>
       <c r="G41" t="n">
-        <v>1605554493.25</v>
+        <v>1210013969</v>
       </c>
     </row>
     <row r="42">
@@ -52680,22 +52680,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C42" t="n">
-        <v>0.35</v>
+        <v>0.21</v>
       </c>
       <c r="D42" t="n">
-        <v>10.06</v>
+        <v>19.2</v>
       </c>
       <c r="E42" t="n">
-        <v>8.83</v>
+        <v>9.52</v>
       </c>
       <c r="F42" t="n">
-        <v>24.97</v>
+        <v>24.73</v>
       </c>
       <c r="G42" t="n">
-        <v>1692966805.45</v>
+        <v>2473782299.73</v>
       </c>
     </row>
     <row r="43">
@@ -52705,22 +52705,22 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C43" t="n">
-        <v>0.9</v>
+        <v>0.33</v>
       </c>
       <c r="D43" t="n">
-        <v>0.83</v>
+        <v>1.07</v>
       </c>
       <c r="E43" t="n">
-        <v>4.87</v>
+        <v>4.59</v>
       </c>
       <c r="F43" t="n">
-        <v>6.12</v>
+        <v>7.95</v>
       </c>
       <c r="G43" t="n">
-        <v>9537394398.440001</v>
+        <v>8571329481.81</v>
       </c>
     </row>
     <row r="44">
@@ -52730,22 +52730,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C44" t="n">
-        <v>0.34</v>
+        <v>0.59</v>
       </c>
       <c r="D44" t="n">
-        <v>3.34</v>
+        <v>2.94</v>
       </c>
       <c r="E44" t="n">
-        <v>55.07</v>
+        <v>5.75</v>
       </c>
       <c r="F44" t="n">
-        <v>102.9</v>
+        <v>10.31</v>
       </c>
       <c r="G44" t="n">
-        <v>4150351584.85</v>
+        <v>3116458590.37</v>
       </c>
     </row>
     <row r="45">

--- a/Ejercicio-3/Parte-B/3.B.35/Code/datos/tablas_figuras.xlsx
+++ b/Ejercicio-3/Parte-B/3.B.35/Code/datos/tablas_figuras.xlsx
@@ -57,11 +57,11 @@
     <sheet name="MERCOSUR_reparto_manuf" sheetId="48" state="visible" r:id="rId48"/>
     <sheet name="CEFTA_convergencia" sheetId="49" state="visible" r:id="rId49"/>
     <sheet name="CEFTA_ancla" sheetId="50" state="visible" r:id="rId50"/>
-    <sheet name="AFCFTA_composicion" sheetId="51" state="visible" r:id="rId51"/>
-    <sheet name="AFCFTA_materias" sheetId="52" state="visible" r:id="rId52"/>
-    <sheet name="AFCFTA_aranceles" sheetId="53" state="visible" r:id="rId53"/>
-    <sheet name="PAFTA_sin_petroleo" sheetId="54" state="visible" r:id="rId54"/>
-    <sheet name="PAFTA_composicion" sheetId="55" state="visible" r:id="rId55"/>
+    <sheet name="AFCFTA_materias" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet name="AFCFTA_aranceles" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet name="PAFTA_sin_petroleo" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet name="PAFTA_composicion" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet name="AFCFTA_composicion" sheetId="55" state="visible" r:id="rId55"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -51087,237 +51087,371 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Manufacturas en las exportaciones de los países africanos a África y fuera de África (%)</t>
+          <t>Estructura de las exportaciones de las grandes economías africanas y complementariedad entre ellas, 2023</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WITS (Banco Mundial), grupo «manuf» (CUCI 5 a 8 sin 667 y 68) y total, exportaciones declaradas por cada país a cada socio; solo los países que declaran cada año. Cálculo propio (Code/figuras_afinidad.py).</t>
+          <t>WITS (Banco Mundial): exportaciones por grupos de la CUCI (alimentos, materias primas agrícolas, combustibles, minerales y metales, manufacturas) y exportaciones e importaciones por las 16 secciones del SA de WITS (complementariedad aproximada, MICHAELY, 1996). Cálculo propio (Code/figuras_afinidad.py).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Año</t>
+          <t>País</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A África (%)</t>
+          <t>Alimentos (%)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fuera de África (%)</t>
+          <t>Materias primas agrícolas (%)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Países que declaran</t>
+          <t>Combustibles (%)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AGO 2023: África / fuera</t>
+          <t>Minerales y metales (%)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>TUN 2023: África / fuera</t>
+          <t>Manufacturas (%)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MAR 2023: África / fuera</t>
+          <t>Otros (%)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>EGY 2023: África / fuera</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>ZAF 2023: África / fuera</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>KEN 2023: África / fuera</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>GHA 2023: África / fuera</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>CIV 2023: África / fuera</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>TZA 2023: África / fuera</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>ETH 2023: África / fuera</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>NGA 2023: África / fuera</t>
+          <t>Complementariedad media con los demás</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>2000</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TUN</t>
+        </is>
       </c>
       <c r="B5" t="n">
-        <v>40.6</v>
+        <v>12.8</v>
       </c>
       <c r="C5" t="n">
-        <v>26.2</v>
+        <v>0.3</v>
       </c>
       <c r="D5" t="n">
-        <v>39</v>
+        <v>6.2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>63.5</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>2005</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
       </c>
       <c r="B6" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>61.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EGY</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F7" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>67.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ZAF</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="F8" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="n">
+        <v>61.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KEN</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>45.3</v>
       </c>
-      <c r="C6" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="D6" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>2010</v>
-      </c>
-      <c r="B7" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="C7" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="D7" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B8" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="C8" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="D8" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B9" t="n">
-        <v>49.3</v>
-      </c>
       <c r="C9" t="n">
-        <v>24.5</v>
+        <v>11.3</v>
       </c>
       <c r="D9" t="n">
-        <v>43</v>
+        <v>5.2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>47.9</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>2023</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CIV</t>
+        </is>
       </c>
       <c r="B10" t="n">
-        <v>48.8</v>
+        <v>44.3</v>
       </c>
       <c r="C10" t="n">
-        <v>26.5</v>
+        <v>12.4</v>
       </c>
       <c r="D10" t="n">
-        <v>40</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>72.8 / 2.4</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>71.9 / 80.0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>70.9 / 75.2</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>69.0 / 48.2</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>61.9 / 32.9</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>57.6 / 14.3</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>33.3 / 1.2</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>32.7 / 6.8</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>27.4 / 5.3</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>13.9 / 8.4</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>8.5 / 2.2</t>
-        </is>
+        <v>15.8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F10" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="G10" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="H10" t="n">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TZA</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F11" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>32.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>GHA</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>18</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>24</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G13" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="H13" t="n">
+        <v>39.6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AGO</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>30.7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NGA</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>29.7</v>
       </c>
     </row>
   </sheetData>
@@ -51331,20 +51465,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Estructura de las exportaciones de las grandes economías africanas y complementariedad entre ellas, 2023</t>
+          <t>Arancel aplicado y de nación más favorecida de los países africanos según el origen de las importaciones (%)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WITS (Banco Mundial): exportaciones por grupos de la CUCI (alimentos, materias primas agrícolas, combustibles, minerales y metales, manufacturas) y exportaciones e importaciones por las 16 secciones del SA de WITS (complementariedad aproximada, MICHAELY, 1996). Cálculo propio (Code/figuras_afinidad.py).</t>
+          <t>WITS (Banco Mundial), tradestats-tariff: AHS-WGHTD-AVRG y MFN-WGHTD-AVRG por socio, ponderados por las importaciones de cada socio (MPRT-TRD-VL); último año disponible entre 2019 y 2022. Comunidad = socio de la misma comunidad con libre comercio (CEDEAO, CEEAC, EAC, COMESA, SADC, UEMOA, CEMAC). Cálculo propio (Code/figuras_afinidad.py).</t>
         </is>
       </c>
     </row>
@@ -51356,346 +51490,1043 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Alimentos (%)</t>
+          <t>Año</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Materias primas agrícolas (%)</t>
+          <t>Aplicado, comunidad</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Combustibles (%)</t>
+          <t>Aplicado, resto de África</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Minerales y metales (%)</t>
+          <t>Aplicado, fuera de África</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Manufacturas (%)</t>
+          <t>NMF, a África</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Otros (%)</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Complementariedad media con los demás</t>
+          <t>Importaciones desde África (USD)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TUN</t>
+          <t>AGO</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12.8</v>
+        <v>2021</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3</v>
+        <v>19.71</v>
       </c>
       <c r="D5" t="n">
-        <v>6.2</v>
+        <v>13.39</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3</v>
+        <v>12.07</v>
       </c>
       <c r="F5" t="n">
-        <v>79.2</v>
+        <v>15.64</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>63.5</v>
+        <v>1204584255.78</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>BDI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.8</v>
+        <v>2021</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6</v>
+        <v>0.14</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2</v>
+        <v>15.96</v>
       </c>
       <c r="E6" t="n">
-        <v>4.4</v>
+        <v>9.17</v>
       </c>
       <c r="F6" t="n">
-        <v>74.90000000000001</v>
+        <v>24.36</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>61.9</v>
+        <v>308315205.21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EGY</t>
+          <t>BEN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19.8</v>
+        <v>2021</v>
       </c>
       <c r="C7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>18.2</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>4.7</v>
+        <v>11.29</v>
       </c>
       <c r="F7" t="n">
-        <v>51.8</v>
+        <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H7" t="n">
-        <v>67.7</v>
+        <v>606400220.78</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ZAF</t>
+          <t>BFA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11.6</v>
+        <v>2021</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>10.7</v>
+        <v>4.38</v>
       </c>
       <c r="E8" t="n">
-        <v>28.9</v>
+        <v>7.82</v>
       </c>
       <c r="F8" t="n">
-        <v>40.7</v>
+        <v>12.73</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
-      </c>
-      <c r="H8" t="n">
-        <v>61.1</v>
+        <v>1226339315.57</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KEN</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>45.3</v>
+        <v>2021</v>
       </c>
       <c r="C9" t="n">
-        <v>11.3</v>
+        <v>0.31</v>
       </c>
       <c r="D9" t="n">
-        <v>5.2</v>
+        <v>7.96</v>
       </c>
       <c r="E9" t="n">
-        <v>4.8</v>
+        <v>1.15</v>
       </c>
       <c r="F9" t="n">
-        <v>32.9</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H9" t="n">
-        <v>47.9</v>
+        <v>5225078128.78</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CIV</t>
+          <t>CAF</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="C10" t="n">
-        <v>12.4</v>
+        <v>2022</v>
       </c>
       <c r="D10" t="n">
-        <v>15.8</v>
+        <v>14.08</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9</v>
+        <v>15.42</v>
       </c>
       <c r="F10" t="n">
-        <v>13.8</v>
+        <v>14.08</v>
       </c>
       <c r="G10" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="H10" t="n">
-        <v>48.2</v>
+        <v>22459046.35</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TZA</t>
+          <t>CIV</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32.6</v>
+        <v>2021</v>
       </c>
       <c r="C11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>3.9</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>4.9</v>
+        <v>8.73</v>
       </c>
       <c r="F11" t="n">
-        <v>13.4</v>
+        <v>6.08</v>
       </c>
       <c r="G11" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="H11" t="n">
-        <v>32.7</v>
+        <v>2684932850.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>CMR</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>80.3</v>
-      </c>
-      <c r="C12" t="n">
-        <v>9.6</v>
+        <v>2022</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>13.61</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7</v>
+        <v>17.33</v>
       </c>
       <c r="F12" t="n">
-        <v>9.199999999999999</v>
+        <v>13.61</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H12" t="n">
-        <v>19.2</v>
+        <v>371674071.87</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GHA</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>2020</v>
       </c>
       <c r="C13" t="n">
-        <v>1.1</v>
+        <v>9.1</v>
       </c>
       <c r="D13" t="n">
-        <v>24</v>
+        <v>11.46</v>
       </c>
       <c r="E13" t="n">
-        <v>3.7</v>
+        <v>8.32</v>
       </c>
       <c r="F13" t="n">
-        <v>7.8</v>
+        <v>9.23</v>
       </c>
       <c r="G13" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="H13" t="n">
-        <v>39.6</v>
+        <v>1379316852.59</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AGO</t>
+          <t>COG</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
+        <v>2022</v>
       </c>
       <c r="D14" t="n">
-        <v>88.90000000000001</v>
+        <v>16.18</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1</v>
+        <v>18.1</v>
       </c>
       <c r="F14" t="n">
-        <v>6.6</v>
+        <v>16.18</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>30.7</v>
+        <v>202024283.93</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>COM</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="G15" t="n">
+        <v>22904623.97</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D16" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="E16" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="G16" t="n">
+        <v>35981705.72</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EGY</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="F17" t="n">
+        <v>19.22</v>
+      </c>
+      <c r="G17" t="n">
+        <v>761727452.4299999</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C18" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="E18" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="F18" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1029169935.49</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>GAB</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D19" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.03</v>
+      </c>
+      <c r="F19" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="G19" t="n">
+        <v>186213242.18</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>GHA</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="E20" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="F20" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1570813372.57</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>GMB</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="F21" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="G21" t="n">
+        <v>217160662.91</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>KEN</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="D22" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="E22" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2082304715.01</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>LBR</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="E23" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="F23" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="G23" t="n">
+        <v>33434518.2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>LSO</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="F24" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1283905541.77</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="F25" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2209677095.37</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MDG</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="D26" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="E26" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="F26" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="G26" t="n">
+        <v>674841386.13</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MLI</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="E27" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="F27" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2096499380.4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MOZ</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="E28" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F28" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2684781614.41</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MRT</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D29" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="E29" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="F29" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="G29" t="n">
+        <v>439429615.63</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MUS</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G30" t="n">
+        <v>626086169.5700001</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MWI</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C31" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="D31" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="E31" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="F31" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="G31" t="n">
+        <v>900781299.25</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>NAM</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D32" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="F32" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3108338702.96</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NER</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="E33" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="F33" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="G33" t="n">
+        <v>613708212.34</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>NGA</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D15" t="n">
-        <v>91.59999999999999</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H15" t="n">
-        <v>29.7</v>
+      <c r="B34" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="E34" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="F34" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1004758955.42</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>RWA</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D35" t="n">
+        <v>28.71</v>
+      </c>
+      <c r="E35" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="F35" t="n">
+        <v>22.88</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1150118515.52</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SEN</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="E36" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="F36" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1303126876.8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>STP</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C37" t="n">
+        <v>20</v>
+      </c>
+      <c r="D37" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="E37" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="F37" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="G37" t="n">
+        <v>989374.77</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SWZ</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D38" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="E38" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="F38" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1603658639.66</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SYC</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="D39" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="G39" t="n">
+        <v>402117461.92</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TGO</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="E40" t="n">
+        <v>11.27</v>
+      </c>
+      <c r="F40" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="G40" t="n">
+        <v>414699470.15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TZA</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D41" t="n">
+        <v>19.78</v>
+      </c>
+      <c r="E41" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="F41" t="n">
+        <v>17.23</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1210013969</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>UGA</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D42" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="E42" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="F42" t="n">
+        <v>24.73</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2473782299.73</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ZAF</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E43" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="F43" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="G43" t="n">
+        <v>8571329481.81</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ZMB</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="E44" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="F44" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="G44" t="n">
+        <v>3116458590.37</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ZWE</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C45" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="D45" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="E45" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F45" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="G45" t="n">
+        <v>4096558244.66</v>
       </c>
     </row>
   </sheetData>
@@ -51709,1068 +52540,393 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Arancel aplicado y de nación más favorecida de los países africanos según el origen de las importaciones (%)</t>
+          <t>Exportaciones de los miembros de la PAFTA a otros miembros, con y sin combustibles (% del total)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WITS (Banco Mundial), tradestats-tariff: AHS-WGHTD-AVRG y MFN-WGHTD-AVRG por socio, ponderados por las importaciones de cada socio (MPRT-TRD-VL); último año disponible entre 2019 y 2022. Comunidad = socio de la misma comunidad con libre comercio (CEDEAO, CEEAC, EAC, COMESA, SADC, UEMOA, CEMAC). Cálculo propio (Code/figuras_afinidad.py).</t>
+          <t>WITS (Banco Mundial), exportaciones declaradas por cada miembro, total y grupo «Fuels» (CUCI 3); solo los miembros que declaran cada año (al menos la mitad). El petróleo que se declara sin destino cuenta en el total pero no en ningún socio. Cálculo propio.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>País</t>
+          <t>Año</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Año</t>
+          <t>Todas las exportaciones (%)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aplicado, comunidad</t>
+          <t>Sin combustibles (%)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Aplicado, resto de África</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Aplicado, fuera de África</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>NMF, a África</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Importaciones desde África (USD)</t>
+          <t>Miembros que declaran</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AGO</t>
-        </is>
+      <c r="A5" t="n">
+        <v>1999</v>
       </c>
       <c r="B5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B7" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="C7" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C8" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="D8" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C9" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="C10" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B11" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C12" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="D12" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B13" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C13" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B14" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="C14" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="C15" t="n">
+        <v>27</v>
+      </c>
+      <c r="D15" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B16" t="n">
+        <v>9</v>
+      </c>
+      <c r="C16" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B17" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C17" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B18" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="C18" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B19" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="C19" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="C20" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B21" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="C21" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="D21" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B22" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="C22" t="n">
+        <v>20</v>
+      </c>
+      <c r="D22" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B23" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="C23" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="D23" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B24" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="C24" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B25" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="C25" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B26" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="C26" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
         <v>2021</v>
       </c>
-      <c r="C5" t="n">
-        <v>19.71</v>
-      </c>
-      <c r="D5" t="n">
-        <v>13.39</v>
-      </c>
-      <c r="E5" t="n">
-        <v>12.07</v>
-      </c>
-      <c r="F5" t="n">
-        <v>15.64</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1204584255.78</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>BDI</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="D6" t="n">
-        <v>15.96</v>
-      </c>
-      <c r="E6" t="n">
-        <v>9.17</v>
-      </c>
-      <c r="F6" t="n">
-        <v>24.36</v>
-      </c>
-      <c r="G6" t="n">
-        <v>308315205.21</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>BEN</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>9</v>
-      </c>
-      <c r="E7" t="n">
-        <v>11.29</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="B27" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="C27" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="D27" t="n">
         <v>12</v>
       </c>
-      <c r="G7" t="n">
-        <v>606400220.78</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>BFA</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="E8" t="n">
-        <v>7.82</v>
-      </c>
-      <c r="F8" t="n">
-        <v>12.73</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1226339315.57</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>BWA</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="D9" t="n">
-        <v>7.96</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="F9" t="n">
-        <v>9.140000000000001</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5225078128.78</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
         <v>2022</v>
       </c>
-      <c r="D10" t="n">
-        <v>14.08</v>
-      </c>
-      <c r="E10" t="n">
-        <v>15.42</v>
-      </c>
-      <c r="F10" t="n">
-        <v>14.08</v>
-      </c>
-      <c r="G10" t="n">
-        <v>22459046.35</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CIV</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>9.619999999999999</v>
-      </c>
-      <c r="E11" t="n">
-        <v>8.73</v>
-      </c>
-      <c r="F11" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2684932850.6</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CMR</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D12" t="n">
-        <v>13.61</v>
-      </c>
-      <c r="E12" t="n">
-        <v>17.33</v>
-      </c>
-      <c r="F12" t="n">
-        <v>13.61</v>
-      </c>
-      <c r="G12" t="n">
-        <v>371674071.87</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>COD</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C13" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>11.46</v>
-      </c>
-      <c r="E13" t="n">
-        <v>8.32</v>
-      </c>
-      <c r="F13" t="n">
-        <v>9.23</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1379316852.59</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>COG</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D14" t="n">
-        <v>16.18</v>
-      </c>
-      <c r="E14" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>16.18</v>
-      </c>
-      <c r="G14" t="n">
-        <v>202024283.93</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>COM</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C15" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="D15" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="E15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="F15" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="G15" t="n">
-        <v>22904623.97</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>CPV</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="D16" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="E16" t="n">
-        <v>10.22</v>
-      </c>
-      <c r="F16" t="n">
-        <v>10.96</v>
-      </c>
-      <c r="G16" t="n">
-        <v>35981705.72</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>EGY</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E17" t="n">
-        <v>10.24</v>
-      </c>
-      <c r="F17" t="n">
-        <v>19.22</v>
-      </c>
-      <c r="G17" t="n">
-        <v>761727452.4299999</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C18" t="n">
-        <v>13.39</v>
-      </c>
-      <c r="D18" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="E18" t="n">
-        <v>12.22</v>
-      </c>
-      <c r="F18" t="n">
-        <v>9.380000000000001</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1029169935.49</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>GAB</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C19" t="n">
-        <v>30</v>
-      </c>
-      <c r="D19" t="n">
-        <v>17.16</v>
-      </c>
-      <c r="E19" t="n">
-        <v>16.03</v>
-      </c>
-      <c r="F19" t="n">
-        <v>17.16</v>
-      </c>
-      <c r="G19" t="n">
-        <v>186213242.18</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>GHA</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>9.609999999999999</v>
-      </c>
-      <c r="E20" t="n">
-        <v>10.65</v>
-      </c>
-      <c r="F20" t="n">
-        <v>11.67</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1570813372.57</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>GMB</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="E21" t="n">
-        <v>13.17</v>
-      </c>
-      <c r="F21" t="n">
-        <v>16.61</v>
-      </c>
-      <c r="G21" t="n">
-        <v>217160662.91</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>KEN</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C22" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="D22" t="n">
-        <v>10.35</v>
-      </c>
-      <c r="E22" t="n">
-        <v>9.369999999999999</v>
-      </c>
-      <c r="F22" t="n">
-        <v>28.12</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2082304715.01</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>LBR</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>14.02</v>
-      </c>
-      <c r="E23" t="n">
-        <v>10.32</v>
-      </c>
-      <c r="F23" t="n">
-        <v>14.16</v>
-      </c>
-      <c r="G23" t="n">
-        <v>33434518.2</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>LSO</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="E24" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="F24" t="n">
-        <v>12.27</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1283905541.77</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="E25" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="F25" t="n">
-        <v>12.64</v>
-      </c>
-      <c r="G25" t="n">
-        <v>2209677095.37</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>MDG</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C26" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="D26" t="n">
-        <v>11.28</v>
-      </c>
-      <c r="E26" t="n">
-        <v>7.12</v>
-      </c>
-      <c r="F26" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="G26" t="n">
-        <v>674841386.13</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>MLI</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" t="n">
-        <v>10.47</v>
-      </c>
-      <c r="E27" t="n">
-        <v>7.47</v>
-      </c>
-      <c r="F27" t="n">
-        <v>15.46</v>
-      </c>
-      <c r="G27" t="n">
-        <v>2096499380.4</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>MOZ</t>
-        </is>
-      </c>
       <c r="B28" t="n">
-        <v>2021</v>
+        <v>12.9</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>32.3</v>
       </c>
       <c r="D28" t="n">
-        <v>6.61</v>
-      </c>
-      <c r="E28" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="F28" t="n">
-        <v>8.51</v>
-      </c>
-      <c r="G28" t="n">
-        <v>2684781614.41</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>MRT</t>
-        </is>
+      <c r="A29" t="n">
+        <v>2023</v>
       </c>
       <c r="B29" t="n">
-        <v>2021</v>
+        <v>14.5</v>
+      </c>
+      <c r="C29" t="n">
+        <v>32.6</v>
       </c>
       <c r="D29" t="n">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="E29" t="n">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="F29" t="n">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="G29" t="n">
-        <v>439429615.63</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>MUS</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E30" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="G30" t="n">
-        <v>626086169.5700001</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>MWI</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C31" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="D31" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="E31" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="F31" t="n">
-        <v>13.12</v>
-      </c>
-      <c r="G31" t="n">
-        <v>900781299.25</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>NAM</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="D32" t="n">
-        <v>14.48</v>
-      </c>
-      <c r="E32" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="F32" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="G32" t="n">
-        <v>3108338702.96</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>NER</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="E33" t="n">
-        <v>9.01</v>
-      </c>
-      <c r="F33" t="n">
-        <v>16.77</v>
-      </c>
-      <c r="G33" t="n">
-        <v>613708212.34</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>NGA</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="n">
-        <v>9.08</v>
-      </c>
-      <c r="E34" t="n">
-        <v>10.83</v>
-      </c>
-      <c r="F34" t="n">
-        <v>9.94</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1004758955.42</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>RWA</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="D35" t="n">
-        <v>28.71</v>
-      </c>
-      <c r="E35" t="n">
-        <v>13.62</v>
-      </c>
-      <c r="F35" t="n">
-        <v>22.88</v>
-      </c>
-      <c r="G35" t="n">
-        <v>1150118515.52</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>SEN</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
-        <v>10.87</v>
-      </c>
-      <c r="E36" t="n">
-        <v>9.359999999999999</v>
-      </c>
-      <c r="F36" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="G36" t="n">
-        <v>1303126876.8</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>STP</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C37" t="n">
-        <v>20</v>
-      </c>
-      <c r="D37" t="n">
-        <v>8.210000000000001</v>
-      </c>
-      <c r="E37" t="n">
-        <v>10.87</v>
-      </c>
-      <c r="F37" t="n">
-        <v>9.41</v>
-      </c>
-      <c r="G37" t="n">
-        <v>989374.77</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>SWZ</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C38" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D38" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="E38" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="F38" t="n">
-        <v>9.470000000000001</v>
-      </c>
-      <c r="G38" t="n">
-        <v>1603658639.66</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>SYC</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C39" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="D39" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="E39" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="F39" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="G39" t="n">
-        <v>402117461.92</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>TGO</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" t="n">
-        <v>9.76</v>
-      </c>
-      <c r="E40" t="n">
-        <v>11.27</v>
-      </c>
-      <c r="F40" t="n">
-        <v>12.48</v>
-      </c>
-      <c r="G40" t="n">
-        <v>414699470.15</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>TZA</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C41" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="D41" t="n">
-        <v>19.78</v>
-      </c>
-      <c r="E41" t="n">
-        <v>9.630000000000001</v>
-      </c>
-      <c r="F41" t="n">
-        <v>17.23</v>
-      </c>
-      <c r="G41" t="n">
-        <v>1210013969</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>UGA</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C42" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="D42" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="E42" t="n">
-        <v>9.52</v>
-      </c>
-      <c r="F42" t="n">
-        <v>24.73</v>
-      </c>
-      <c r="G42" t="n">
-        <v>2473782299.73</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>ZAF</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C43" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="D43" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E43" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="F43" t="n">
-        <v>7.95</v>
-      </c>
-      <c r="G43" t="n">
-        <v>8571329481.81</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>ZMB</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C44" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="D44" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="E44" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="F44" t="n">
-        <v>10.31</v>
-      </c>
-      <c r="G44" t="n">
-        <v>3116458590.37</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>ZWE</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C45" t="n">
-        <v>11.85</v>
-      </c>
-      <c r="D45" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="E45" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="F45" t="n">
-        <v>11.84</v>
-      </c>
-      <c r="G45" t="n">
-        <v>4096558244.66</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -52784,20 +52940,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Exportaciones de los miembros de la PAFTA a otros miembros, con y sin combustibles (% del total)</t>
+          <t>Composición de las exportaciones de los miembros de la PAFTA a otros miembros y fuera de la PAFTA (%)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WITS (Banco Mundial), exportaciones declaradas por cada miembro, total y grupo «Fuels» (CUCI 3); solo los miembros que declaran cada año (al menos la mitad). El petróleo que se declara sin destino cuenta en el total pero no en ningún socio. Cálculo propio.</t>
+          <t>WITS (Banco Mundial), exportaciones declaradas por grupos de la CUCI. «Otros y sin clasificar» incluye el petróleo declarado sin desglose de producto. Cálculo propio (Code/figuras_afinidad.py).</t>
         </is>
       </c>
     </row>
@@ -52809,368 +52965,150 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Todas las exportaciones (%)</t>
+          <t>Destino</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sin combustibles (%)</t>
+          <t>Alimentos (%)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Miembros que declaran</t>
+          <t>Materias primas agrícolas (%)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Combustibles (%)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Minerales y metales (%)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Manufacturas (%)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Otros (%)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1999</v>
-      </c>
-      <c r="B5" t="n">
-        <v>4.5</v>
+        <v>2005</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
       </c>
       <c r="C5" t="n">
-        <v>15.1</v>
+        <v>15.4</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>0.7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2000</v>
-      </c>
-      <c r="B6" t="n">
-        <v>5.4</v>
+        <v>2005</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
       </c>
       <c r="C6" t="n">
-        <v>23.4</v>
+        <v>1.4</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>0.2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>9.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2001</v>
-      </c>
-      <c r="B7" t="n">
-        <v>7.7</v>
+        <v>2023</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
       </c>
       <c r="C7" t="n">
-        <v>29.9</v>
+        <v>12.6</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>0.2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G7" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2002</v>
-      </c>
-      <c r="B8" t="n">
-        <v>9</v>
+        <v>2023</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
       </c>
       <c r="C8" t="n">
-        <v>26.6</v>
+        <v>2.5</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>2003</v>
-      </c>
-      <c r="B9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="C9" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>2004</v>
-      </c>
-      <c r="B10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="C10" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="D10" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>2005</v>
-      </c>
-      <c r="B11" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="C11" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="D11" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>2006</v>
-      </c>
-      <c r="B12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="C12" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="D12" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>2007</v>
-      </c>
-      <c r="B13" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="C13" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="D13" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>2008</v>
-      </c>
-      <c r="B14" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="C14" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="D14" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>2009</v>
-      </c>
-      <c r="B15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="C15" t="n">
-        <v>27</v>
-      </c>
-      <c r="D15" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>2010</v>
-      </c>
-      <c r="B16" t="n">
-        <v>9</v>
-      </c>
-      <c r="C16" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="D16" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>2011</v>
-      </c>
-      <c r="B17" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="C17" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="D17" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>2012</v>
-      </c>
-      <c r="B18" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="C18" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="D18" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B19" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="C19" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="D19" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>2014</v>
-      </c>
-      <c r="B20" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="C20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G8" t="n">
         <v>21.5</v>
       </c>
-      <c r="D20" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B21" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="C21" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="D21" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>2016</v>
-      </c>
-      <c r="B22" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="C22" t="n">
-        <v>20</v>
-      </c>
-      <c r="D22" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>2017</v>
-      </c>
-      <c r="B23" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="C23" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="D23" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B24" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="C24" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="D24" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B25" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="C25" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="D25" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>2020</v>
-      </c>
-      <c r="B26" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="C26" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="D26" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B27" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="C27" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="D27" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B28" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="C28" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="D28" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B29" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="C29" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="D29" t="n">
-        <v>12</v>
+      <c r="H8" t="n">
+        <v>6.1</v>
       </c>
     </row>
   </sheetData>
@@ -53184,20 +53122,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Composición de las exportaciones de los miembros de la PAFTA a otros miembros y fuera de la PAFTA (%)</t>
+          <t>Manufacturas en las exportaciones de los países africanos a África y fuera de África (%)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WITS (Banco Mundial), exportaciones declaradas por grupos de la CUCI. «Otros y sin clasificar» incluye el petróleo declarado sin desglose de producto. Cálculo propio (Code/figuras_afinidad.py).</t>
+          <t>WITS (Banco Mundial), grupo «manuf» (CUCI 5 a 8 sin 667 y 68) y total, exportaciones declaradas por cada país a cada socio; solo los países que declaran cada año. Cálculo propio (Code/figuras_afinidad.py).</t>
         </is>
       </c>
     </row>
@@ -53209,150 +53147,212 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Destino</t>
+          <t>A África (%)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alimentos (%)</t>
+          <t>Fuera de África (%)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Materias primas agrícolas (%)</t>
+          <t>Países que declaran</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Combustibles (%)</t>
+          <t>AGO 2023: África / fuera</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Minerales y metales (%)</t>
+          <t>TUN 2023: África / fuera</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Manufacturas (%)</t>
+          <t>MAR 2023: África / fuera</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Otros (%)</t>
+          <t>EGY 2023: África / fuera</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ZAF 2023: África / fuera</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>KEN 2023: África / fuera</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>GHA 2023: África / fuera</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>CIV 2023: África / fuera</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>TZA 2023: África / fuera</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>ETH 2023: África / fuera</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>NGA 2023: África / fuera</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2005</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Dentro</t>
-        </is>
+        <v>2000</v>
+      </c>
+      <c r="B5" t="n">
+        <v>40.6</v>
       </c>
       <c r="C5" t="n">
-        <v>15.4</v>
+        <v>26.2</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>8.300000000000001</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>2005</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Fuera</t>
-        </is>
+      <c r="B6" t="n">
+        <v>45.3</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4</v>
+        <v>27.2</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E6" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>9.4</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Dentro</t>
-        </is>
+        <v>2010</v>
+      </c>
+      <c r="B7" t="n">
+        <v>45.7</v>
       </c>
       <c r="C7" t="n">
-        <v>12.6</v>
+        <v>20.6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E7" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="G7" t="n">
-        <v>67.90000000000001</v>
-      </c>
-      <c r="H7" t="n">
-        <v>6.7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B8" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="C8" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B9" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
         <v>2023</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Fuera</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G8" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>6.1</v>
+      <c r="B10" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="C10" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>40</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>72.8 / 2.4</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>71.9 / 80.0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>70.9 / 75.2</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>69.0 / 48.2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>61.9 / 32.9</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>57.6 / 14.3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>33.3 / 1.2</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>32.7 / 6.8</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>27.4 / 5.3</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>13.9 / 8.4</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>8.5 / 2.2</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Ejercicio-3/Parte-B/3.B.35/Code/datos/tablas_figuras.xlsx
+++ b/Ejercicio-3/Parte-B/3.B.35/Code/datos/tablas_figuras.xlsx
@@ -57,11 +57,11 @@
     <sheet name="MERCOSUR_reparto_manuf" sheetId="48" state="visible" r:id="rId48"/>
     <sheet name="CEFTA_convergencia" sheetId="49" state="visible" r:id="rId49"/>
     <sheet name="CEFTA_ancla" sheetId="50" state="visible" r:id="rId50"/>
-    <sheet name="AFCFTA_materias" sheetId="51" state="visible" r:id="rId51"/>
-    <sheet name="AFCFTA_aranceles" sheetId="52" state="visible" r:id="rId52"/>
-    <sheet name="PAFTA_sin_petroleo" sheetId="53" state="visible" r:id="rId53"/>
-    <sheet name="PAFTA_composicion" sheetId="54" state="visible" r:id="rId54"/>
-    <sheet name="AFCFTA_composicion" sheetId="55" state="visible" r:id="rId55"/>
+    <sheet name="PAFTA_sin_petroleo" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet name="PAFTA_composicion" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet name="AFCFTA_composicion" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet name="AFCFTA_materias" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet name="AFCFTA_aranceles" sheetId="55" state="visible" r:id="rId55"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -51087,371 +51087,393 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Estructura de las exportaciones de las grandes economías africanas y complementariedad entre ellas, 2023</t>
+          <t>Exportaciones de los miembros de la PAFTA a otros miembros, con y sin combustibles (% del total)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WITS (Banco Mundial): exportaciones por grupos de la CUCI (alimentos, materias primas agrícolas, combustibles, minerales y metales, manufacturas) y exportaciones e importaciones por las 16 secciones del SA de WITS (complementariedad aproximada, MICHAELY, 1996). Cálculo propio (Code/figuras_afinidad.py).</t>
+          <t>WITS (Banco Mundial), exportaciones declaradas por cada miembro, total y grupo «Fuels» (CUCI 3); solo los miembros que declaran cada año (al menos la mitad). El petróleo que se declara sin destino cuenta en el total pero no en ningún socio. Cálculo propio.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>País</t>
+          <t>Año</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Alimentos (%)</t>
+          <t>Todas las exportaciones (%)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Materias primas agrícolas (%)</t>
+          <t>Sin combustibles (%)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Combustibles (%)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Minerales y metales (%)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Manufacturas (%)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Otros (%)</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Complementariedad media con los demás</t>
+          <t>Miembros que declaran</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TUN</t>
-        </is>
+      <c r="A5" t="n">
+        <v>1999</v>
       </c>
       <c r="B5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B7" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="C7" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C8" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="D8" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C9" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="C10" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B11" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C12" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="D12" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B13" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C13" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B14" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="C14" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="C15" t="n">
+        <v>27</v>
+      </c>
+      <c r="D15" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B16" t="n">
+        <v>9</v>
+      </c>
+      <c r="C16" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B17" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C17" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B18" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="C18" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B19" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="C19" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="C20" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B21" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="C21" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="D21" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B22" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="C22" t="n">
+        <v>20</v>
+      </c>
+      <c r="D22" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B23" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="C23" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="D23" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B24" t="n">
         <v>12.8</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F5" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>63.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F6" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>61.9</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>EGY</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D7" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="E7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="F7" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H7" t="n">
-        <v>67.7</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ZAF</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="C8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="E8" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="F8" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="G8" t="n">
-        <v>6</v>
-      </c>
-      <c r="H8" t="n">
-        <v>61.1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>KEN</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="C9" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="D9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F9" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H9" t="n">
-        <v>47.9</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CIV</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="C10" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="D10" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F10" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="C24" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B25" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="C25" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B26" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="C26" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B27" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="C27" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B28" t="n">
         <v>12.9</v>
       </c>
-      <c r="H10" t="n">
-        <v>48.2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TZA</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+      <c r="C28" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="C29" t="n">
         <v>32.6</v>
       </c>
-      <c r="C11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="D11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="F11" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="G11" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="H11" t="n">
-        <v>32.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>80.3</v>
-      </c>
-      <c r="C12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H12" t="n">
-        <v>19.2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>GHA</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>18</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>24</v>
-      </c>
-      <c r="E13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="F13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="G13" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="H13" t="n">
-        <v>39.6</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>AGO</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>88.90000000000001</v>
-      </c>
-      <c r="E14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>30.7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>NGA</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D15" t="n">
-        <v>91.59999999999999</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H15" t="n">
-        <v>29.7</v>
+      <c r="D29" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -51465,1068 +51487,175 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Arancel aplicado y de nación más favorecida de los países africanos según el origen de las importaciones (%)</t>
+          <t>Composición de las exportaciones de los miembros de la PAFTA a otros miembros y fuera de la PAFTA (%)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WITS (Banco Mundial), tradestats-tariff: AHS-WGHTD-AVRG y MFN-WGHTD-AVRG por socio, ponderados por las importaciones de cada socio (MPRT-TRD-VL); último año disponible entre 2019 y 2022. Comunidad = socio de la misma comunidad con libre comercio (CEDEAO, CEEAC, EAC, COMESA, SADC, UEMOA, CEMAC). Cálculo propio (Code/figuras_afinidad.py).</t>
+          <t>WITS (Banco Mundial), exportaciones declaradas por grupos de la CUCI. «Otros y sin clasificar» incluye el petróleo declarado sin desglose de producto. Cálculo propio (Code/figuras_afinidad.py).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>País</t>
+          <t>Año</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Año</t>
+          <t>Destino</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aplicado, comunidad</t>
+          <t>Alimentos (%)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Aplicado, resto de África</t>
+          <t>Materias primas agrícolas (%)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aplicado, fuera de África</t>
+          <t>Combustibles (%)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NMF, a África</t>
+          <t>Minerales y metales (%)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Importaciones desde África (USD)</t>
+          <t>Manufacturas (%)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Otros (%)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AGO</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2021</v>
+      <c r="A5" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
       </c>
       <c r="C5" t="n">
-        <v>19.71</v>
+        <v>15.4</v>
       </c>
       <c r="D5" t="n">
-        <v>13.39</v>
+        <v>0.7</v>
       </c>
       <c r="E5" t="n">
-        <v>12.07</v>
+        <v>6.2</v>
       </c>
       <c r="F5" t="n">
-        <v>15.64</v>
+        <v>4.2</v>
       </c>
       <c r="G5" t="n">
-        <v>1204584255.78</v>
+        <v>65.2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>BDI</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2021</v>
+      <c r="A6" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
       </c>
       <c r="C6" t="n">
-        <v>0.14</v>
+        <v>1.4</v>
       </c>
       <c r="D6" t="n">
-        <v>15.96</v>
+        <v>0.2</v>
       </c>
       <c r="E6" t="n">
-        <v>9.17</v>
+        <v>76.7</v>
       </c>
       <c r="F6" t="n">
-        <v>24.36</v>
+        <v>1.2</v>
       </c>
       <c r="G6" t="n">
-        <v>308315205.21</v>
+        <v>11.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>9.4</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>BEN</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2021</v>
+      <c r="A7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dentro</t>
+        </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>12.6</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>0.2</v>
       </c>
       <c r="E7" t="n">
-        <v>11.29</v>
+        <v>7.1</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>5.6</v>
       </c>
       <c r="G7" t="n">
-        <v>606400220.78</v>
+        <v>67.90000000000001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6.7</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>BFA</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2021</v>
+      <c r="A8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Fuera</t>
+        </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D8" t="n">
-        <v>4.38</v>
+        <v>0.1</v>
       </c>
       <c r="E8" t="n">
-        <v>7.82</v>
+        <v>67.3</v>
       </c>
       <c r="F8" t="n">
-        <v>12.73</v>
+        <v>2.5</v>
       </c>
       <c r="G8" t="n">
-        <v>1226339315.57</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>BWA</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="D9" t="n">
-        <v>7.96</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="F9" t="n">
-        <v>9.140000000000001</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5225078128.78</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D10" t="n">
-        <v>14.08</v>
-      </c>
-      <c r="E10" t="n">
-        <v>15.42</v>
-      </c>
-      <c r="F10" t="n">
-        <v>14.08</v>
-      </c>
-      <c r="G10" t="n">
-        <v>22459046.35</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CIV</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>9.619999999999999</v>
-      </c>
-      <c r="E11" t="n">
-        <v>8.73</v>
-      </c>
-      <c r="F11" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2684932850.6</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CMR</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D12" t="n">
-        <v>13.61</v>
-      </c>
-      <c r="E12" t="n">
-        <v>17.33</v>
-      </c>
-      <c r="F12" t="n">
-        <v>13.61</v>
-      </c>
-      <c r="G12" t="n">
-        <v>371674071.87</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>COD</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C13" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>11.46</v>
-      </c>
-      <c r="E13" t="n">
-        <v>8.32</v>
-      </c>
-      <c r="F13" t="n">
-        <v>9.23</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1379316852.59</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>COG</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D14" t="n">
-        <v>16.18</v>
-      </c>
-      <c r="E14" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>16.18</v>
-      </c>
-      <c r="G14" t="n">
-        <v>202024283.93</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>COM</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C15" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="D15" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="E15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="F15" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="G15" t="n">
-        <v>22904623.97</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>CPV</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="D16" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="E16" t="n">
-        <v>10.22</v>
-      </c>
-      <c r="F16" t="n">
-        <v>10.96</v>
-      </c>
-      <c r="G16" t="n">
-        <v>35981705.72</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>EGY</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E17" t="n">
-        <v>10.24</v>
-      </c>
-      <c r="F17" t="n">
-        <v>19.22</v>
-      </c>
-      <c r="G17" t="n">
-        <v>761727452.4299999</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C18" t="n">
-        <v>13.39</v>
-      </c>
-      <c r="D18" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="E18" t="n">
-        <v>12.22</v>
-      </c>
-      <c r="F18" t="n">
-        <v>9.380000000000001</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1029169935.49</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>GAB</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C19" t="n">
-        <v>30</v>
-      </c>
-      <c r="D19" t="n">
-        <v>17.16</v>
-      </c>
-      <c r="E19" t="n">
-        <v>16.03</v>
-      </c>
-      <c r="F19" t="n">
-        <v>17.16</v>
-      </c>
-      <c r="G19" t="n">
-        <v>186213242.18</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>GHA</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>9.609999999999999</v>
-      </c>
-      <c r="E20" t="n">
-        <v>10.65</v>
-      </c>
-      <c r="F20" t="n">
-        <v>11.67</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1570813372.57</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>GMB</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="E21" t="n">
-        <v>13.17</v>
-      </c>
-      <c r="F21" t="n">
-        <v>16.61</v>
-      </c>
-      <c r="G21" t="n">
-        <v>217160662.91</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>KEN</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C22" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="D22" t="n">
-        <v>10.35</v>
-      </c>
-      <c r="E22" t="n">
-        <v>9.369999999999999</v>
-      </c>
-      <c r="F22" t="n">
-        <v>28.12</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2082304715.01</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>LBR</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>14.02</v>
-      </c>
-      <c r="E23" t="n">
-        <v>10.32</v>
-      </c>
-      <c r="F23" t="n">
-        <v>14.16</v>
-      </c>
-      <c r="G23" t="n">
-        <v>33434518.2</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>LSO</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="E24" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="F24" t="n">
-        <v>12.27</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1283905541.77</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="E25" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="F25" t="n">
-        <v>12.64</v>
-      </c>
-      <c r="G25" t="n">
-        <v>2209677095.37</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>MDG</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C26" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="D26" t="n">
-        <v>11.28</v>
-      </c>
-      <c r="E26" t="n">
-        <v>7.12</v>
-      </c>
-      <c r="F26" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="G26" t="n">
-        <v>674841386.13</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>MLI</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" t="n">
-        <v>10.47</v>
-      </c>
-      <c r="E27" t="n">
-        <v>7.47</v>
-      </c>
-      <c r="F27" t="n">
-        <v>15.46</v>
-      </c>
-      <c r="G27" t="n">
-        <v>2096499380.4</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>MOZ</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="n">
-        <v>6.61</v>
-      </c>
-      <c r="E28" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="F28" t="n">
-        <v>8.51</v>
-      </c>
-      <c r="G28" t="n">
-        <v>2684781614.41</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>MRT</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D29" t="n">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="E29" t="n">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="F29" t="n">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="G29" t="n">
-        <v>439429615.63</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>MUS</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E30" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="G30" t="n">
-        <v>626086169.5700001</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>MWI</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C31" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="D31" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="E31" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="F31" t="n">
-        <v>13.12</v>
-      </c>
-      <c r="G31" t="n">
-        <v>900781299.25</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>NAM</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="D32" t="n">
-        <v>14.48</v>
-      </c>
-      <c r="E32" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="F32" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="G32" t="n">
-        <v>3108338702.96</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>NER</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="E33" t="n">
-        <v>9.01</v>
-      </c>
-      <c r="F33" t="n">
-        <v>16.77</v>
-      </c>
-      <c r="G33" t="n">
-        <v>613708212.34</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>NGA</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="n">
-        <v>9.08</v>
-      </c>
-      <c r="E34" t="n">
-        <v>10.83</v>
-      </c>
-      <c r="F34" t="n">
-        <v>9.94</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1004758955.42</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>RWA</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="D35" t="n">
-        <v>28.71</v>
-      </c>
-      <c r="E35" t="n">
-        <v>13.62</v>
-      </c>
-      <c r="F35" t="n">
-        <v>22.88</v>
-      </c>
-      <c r="G35" t="n">
-        <v>1150118515.52</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>SEN</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
-        <v>10.87</v>
-      </c>
-      <c r="E36" t="n">
-        <v>9.359999999999999</v>
-      </c>
-      <c r="F36" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="G36" t="n">
-        <v>1303126876.8</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>STP</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C37" t="n">
-        <v>20</v>
-      </c>
-      <c r="D37" t="n">
-        <v>8.210000000000001</v>
-      </c>
-      <c r="E37" t="n">
-        <v>10.87</v>
-      </c>
-      <c r="F37" t="n">
-        <v>9.41</v>
-      </c>
-      <c r="G37" t="n">
-        <v>989374.77</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>SWZ</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C38" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D38" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="E38" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="F38" t="n">
-        <v>9.470000000000001</v>
-      </c>
-      <c r="G38" t="n">
-        <v>1603658639.66</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>SYC</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C39" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="D39" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="E39" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="F39" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="G39" t="n">
-        <v>402117461.92</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>TGO</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" t="n">
-        <v>9.76</v>
-      </c>
-      <c r="E40" t="n">
-        <v>11.27</v>
-      </c>
-      <c r="F40" t="n">
-        <v>12.48</v>
-      </c>
-      <c r="G40" t="n">
-        <v>414699470.15</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>TZA</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C41" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="D41" t="n">
-        <v>19.78</v>
-      </c>
-      <c r="E41" t="n">
-        <v>9.630000000000001</v>
-      </c>
-      <c r="F41" t="n">
-        <v>17.23</v>
-      </c>
-      <c r="G41" t="n">
-        <v>1210013969</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>UGA</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C42" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="D42" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="E42" t="n">
-        <v>9.52</v>
-      </c>
-      <c r="F42" t="n">
-        <v>24.73</v>
-      </c>
-      <c r="G42" t="n">
-        <v>2473782299.73</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>ZAF</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C43" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="D43" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E43" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="F43" t="n">
-        <v>7.95</v>
-      </c>
-      <c r="G43" t="n">
-        <v>8571329481.81</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>ZMB</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C44" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="D44" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="E44" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="F44" t="n">
-        <v>10.31</v>
-      </c>
-      <c r="G44" t="n">
-        <v>3116458590.37</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>ZWE</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C45" t="n">
-        <v>11.85</v>
-      </c>
-      <c r="D45" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="E45" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="F45" t="n">
-        <v>11.84</v>
-      </c>
-      <c r="G45" t="n">
-        <v>4096558244.66</v>
+        <v>21.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6.1</v>
       </c>
     </row>
   </sheetData>
@@ -52540,20 +51669,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Exportaciones de los miembros de la PAFTA a otros miembros, con y sin combustibles (% del total)</t>
+          <t>Manufacturas en las exportaciones de los países africanos a África y fuera de África (%)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WITS (Banco Mundial), exportaciones declaradas por cada miembro, total y grupo «Fuels» (CUCI 3); solo los miembros que declaran cada año (al menos la mitad). El petróleo que se declara sin destino cuenta en el total pero no en ningún socio. Cálculo propio.</t>
+          <t>WITS (Banco Mundial), grupo «manuf» (CUCI 5 a 8 sin 667 y 68) y total, exportaciones declaradas por cada país a cada socio; solo los países que declaran cada año. Cálculo propio (Code/figuras_afinidad.py).</t>
         </is>
       </c>
     </row>
@@ -52565,368 +51694,212 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Todas las exportaciones (%)</t>
+          <t>A África (%)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sin combustibles (%)</t>
+          <t>Fuera de África (%)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Miembros que declaran</t>
+          <t>Países que declaran</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AGO 2023: África / fuera</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>TUN 2023: África / fuera</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>MAR 2023: África / fuera</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>EGY 2023: África / fuera</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ZAF 2023: África / fuera</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>KEN 2023: África / fuera</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>GHA 2023: África / fuera</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>CIV 2023: África / fuera</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>TZA 2023: África / fuera</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>ETH 2023: África / fuera</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>NGA 2023: África / fuera</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="B5" t="n">
-        <v>4.5</v>
+        <v>40.6</v>
       </c>
       <c r="C5" t="n">
-        <v>15.1</v>
+        <v>26.2</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2000</v>
+        <v>2005</v>
       </c>
       <c r="B6" t="n">
-        <v>5.4</v>
+        <v>45.3</v>
       </c>
       <c r="C6" t="n">
-        <v>23.4</v>
+        <v>27.2</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2001</v>
+        <v>2010</v>
       </c>
       <c r="B7" t="n">
-        <v>7.7</v>
+        <v>45.7</v>
       </c>
       <c r="C7" t="n">
-        <v>29.9</v>
+        <v>20.6</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2002</v>
+        <v>2015</v>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>53.8</v>
       </c>
       <c r="C8" t="n">
-        <v>26.6</v>
+        <v>24.7</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2003</v>
+        <v>2019</v>
       </c>
       <c r="B9" t="n">
-        <v>7.6</v>
+        <v>49.3</v>
       </c>
       <c r="C9" t="n">
-        <v>22.5</v>
+        <v>24.5</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2004</v>
+        <v>2023</v>
       </c>
       <c r="B10" t="n">
-        <v>7.8</v>
+        <v>48.8</v>
       </c>
       <c r="C10" t="n">
-        <v>23.5</v>
+        <v>26.5</v>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>2005</v>
-      </c>
-      <c r="B11" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="C11" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="D11" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>2006</v>
-      </c>
-      <c r="B12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="C12" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="D12" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>2007</v>
-      </c>
-      <c r="B13" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="C13" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="D13" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>2008</v>
-      </c>
-      <c r="B14" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="C14" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="D14" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>2009</v>
-      </c>
-      <c r="B15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="C15" t="n">
-        <v>27</v>
-      </c>
-      <c r="D15" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>2010</v>
-      </c>
-      <c r="B16" t="n">
-        <v>9</v>
-      </c>
-      <c r="C16" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="D16" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>2011</v>
-      </c>
-      <c r="B17" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="C17" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="D17" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>2012</v>
-      </c>
-      <c r="B18" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="C18" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="D18" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B19" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="C19" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="D19" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>2014</v>
-      </c>
-      <c r="B20" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="C20" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="D20" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B21" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="C21" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="D21" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>2016</v>
-      </c>
-      <c r="B22" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="C22" t="n">
-        <v>20</v>
-      </c>
-      <c r="D22" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>2017</v>
-      </c>
-      <c r="B23" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="C23" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="D23" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B24" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="C24" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="D24" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B25" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="C25" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="D25" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>2020</v>
-      </c>
-      <c r="B26" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="C26" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="D26" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B27" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="C27" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="D27" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B28" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="C28" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="D28" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B29" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="C29" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="D29" t="n">
-        <v>12</v>
+        <v>40</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>72.8 / 2.4</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>71.9 / 80.0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>70.9 / 75.2</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>69.0 / 48.2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>61.9 / 32.9</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>57.6 / 14.3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>33.3 / 1.2</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>32.7 / 6.8</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>27.4 / 5.3</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>13.9 / 8.4</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>8.5 / 2.2</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -52940,175 +51913,371 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Composición de las exportaciones de los miembros de la PAFTA a otros miembros y fuera de la PAFTA (%)</t>
+          <t>Estructura de las exportaciones de las grandes economías africanas y complementariedad entre ellas, 2023</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WITS (Banco Mundial), exportaciones declaradas por grupos de la CUCI. «Otros y sin clasificar» incluye el petróleo declarado sin desglose de producto. Cálculo propio (Code/figuras_afinidad.py).</t>
+          <t>WITS (Banco Mundial): exportaciones por grupos de la CUCI (alimentos, materias primas agrícolas, combustibles, minerales y metales, manufacturas) y exportaciones e importaciones por las 16 secciones del SA de WITS (complementariedad aproximada, MICHAELY, 1996). Cálculo propio (Code/figuras_afinidad.py).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Año</t>
+          <t>País</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Destino</t>
+          <t>Alimentos (%)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alimentos (%)</t>
+          <t>Materias primas agrícolas (%)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Materias primas agrícolas (%)</t>
+          <t>Combustibles (%)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Combustibles (%)</t>
+          <t>Minerales y metales (%)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Minerales y metales (%)</t>
+          <t>Manufacturas (%)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Manufacturas (%)</t>
+          <t>Otros (%)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Otros (%)</t>
+          <t>Complementariedad media con los demás</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>2005</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Dentro</t>
-        </is>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TUN</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>12.8</v>
       </c>
       <c r="C5" t="n">
-        <v>15.4</v>
+        <v>0.3</v>
       </c>
       <c r="D5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>63.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>61.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EGY</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F7" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>67.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ZAF</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="F8" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="n">
+        <v>61.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KEN</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>47.9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CIV</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="C10" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F10" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="G10" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="H10" t="n">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TZA</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F11" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>32.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
         <v>0.7</v>
       </c>
-      <c r="E5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>8.300000000000001</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>2005</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Fuera</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="F12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>GHA</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>18</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>24</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G13" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="H13" t="n">
+        <v>39.6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AGO</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>30.7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NGA</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G15" t="n">
         <v>0.2</v>
       </c>
-      <c r="E6" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>9.4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Dentro</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E7" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="G7" t="n">
-        <v>67.90000000000001</v>
-      </c>
-      <c r="H7" t="n">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Fuera</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G8" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>6.1</v>
+      <c r="H15" t="n">
+        <v>29.7</v>
       </c>
     </row>
   </sheetData>
@@ -53122,237 +52291,1068 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Manufacturas en las exportaciones de los países africanos a África y fuera de África (%)</t>
+          <t>Arancel aplicado y de nación más favorecida de los países africanos según el origen de las importaciones (%)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WITS (Banco Mundial), grupo «manuf» (CUCI 5 a 8 sin 667 y 68) y total, exportaciones declaradas por cada país a cada socio; solo los países que declaran cada año. Cálculo propio (Code/figuras_afinidad.py).</t>
+          <t>WITS (Banco Mundial), tradestats-tariff: AHS-WGHTD-AVRG y MFN-WGHTD-AVRG por socio, ponderados por las importaciones de cada socio (MPRT-TRD-VL); último año disponible entre 2019 y 2022. Comunidad = socio de la misma comunidad con libre comercio (CEDEAO, CEEAC, EAC, COMESA, SADC, UEMOA, CEMAC). Cálculo propio (Code/figuras_afinidad.py).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>País</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>A África (%)</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fuera de África (%)</t>
+          <t>Aplicado, comunidad</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Países que declaran</t>
+          <t>Aplicado, resto de África</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AGO 2023: África / fuera</t>
+          <t>Aplicado, fuera de África</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>TUN 2023: África / fuera</t>
+          <t>NMF, a África</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MAR 2023: África / fuera</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>EGY 2023: África / fuera</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>ZAF 2023: África / fuera</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>KEN 2023: África / fuera</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>GHA 2023: África / fuera</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>CIV 2023: África / fuera</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>TZA 2023: África / fuera</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>ETH 2023: África / fuera</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>NGA 2023: África / fuera</t>
+          <t>Importaciones desde África (USD)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>2000</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AGO</t>
+        </is>
       </c>
       <c r="B5" t="n">
-        <v>40.6</v>
+        <v>2021</v>
       </c>
       <c r="C5" t="n">
-        <v>26.2</v>
+        <v>19.71</v>
       </c>
       <c r="D5" t="n">
-        <v>39</v>
+        <v>13.39</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="F5" t="n">
+        <v>15.64</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1204584255.78</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>2005</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BDI</t>
+        </is>
       </c>
       <c r="B6" t="n">
-        <v>45.3</v>
+        <v>2021</v>
       </c>
       <c r="C6" t="n">
-        <v>27.2</v>
+        <v>0.14</v>
       </c>
       <c r="D6" t="n">
-        <v>41</v>
+        <v>15.96</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="F6" t="n">
+        <v>24.36</v>
+      </c>
+      <c r="G6" t="n">
+        <v>308315205.21</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>2010</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
       </c>
       <c r="B7" t="n">
-        <v>45.7</v>
+        <v>2021</v>
       </c>
       <c r="C7" t="n">
-        <v>20.6</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>41</v>
+        <v>9</v>
+      </c>
+      <c r="E7" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="F7" t="n">
+        <v>12</v>
+      </c>
+      <c r="G7" t="n">
+        <v>606400220.78</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>2015</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BFA</t>
+        </is>
       </c>
       <c r="B8" t="n">
-        <v>53.8</v>
+        <v>2021</v>
       </c>
       <c r="C8" t="n">
-        <v>24.7</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>45</v>
+        <v>4.38</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="F8" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1226339315.57</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BWA</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F9" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5225078128.78</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CAF</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D10" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="F10" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>22459046.35</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CIV</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="E11" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2684932850.6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CMR</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D12" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="E12" t="n">
+        <v>17.33</v>
+      </c>
+      <c r="F12" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="G12" t="n">
+        <v>371674071.87</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C13" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="E13" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="F13" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1379316852.59</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>COG</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D14" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="E14" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="G14" t="n">
+        <v>202024283.93</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>COM</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="G15" t="n">
+        <v>22904623.97</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D16" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="E16" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="G16" t="n">
+        <v>35981705.72</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EGY</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
         <v>2019</v>
       </c>
-      <c r="B9" t="n">
-        <v>49.3</v>
-      </c>
-      <c r="C9" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B10" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="C10" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="D10" t="n">
-        <v>40</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>72.8 / 2.4</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>71.9 / 80.0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>70.9 / 75.2</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>69.0 / 48.2</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>61.9 / 32.9</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>57.6 / 14.3</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>33.3 / 1.2</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>32.7 / 6.8</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>27.4 / 5.3</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>13.9 / 8.4</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>8.5 / 2.2</t>
-        </is>
+      <c r="C17" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="F17" t="n">
+        <v>19.22</v>
+      </c>
+      <c r="G17" t="n">
+        <v>761727452.4299999</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C18" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="E18" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="F18" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1029169935.49</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>GAB</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D19" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.03</v>
+      </c>
+      <c r="F19" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="G19" t="n">
+        <v>186213242.18</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>GHA</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="E20" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="F20" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1570813372.57</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>GMB</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="F21" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="G21" t="n">
+        <v>217160662.91</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>KEN</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="D22" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="E22" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2082304715.01</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>LBR</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="E23" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="F23" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="G23" t="n">
+        <v>33434518.2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>LSO</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="F24" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1283905541.77</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="F25" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2209677095.37</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MDG</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="D26" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="E26" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="F26" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="G26" t="n">
+        <v>674841386.13</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MLI</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="E27" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="F27" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2096499380.4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MOZ</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="E28" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F28" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2684781614.41</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MRT</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D29" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="E29" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="F29" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="G29" t="n">
+        <v>439429615.63</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MUS</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G30" t="n">
+        <v>626086169.5700001</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MWI</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C31" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="D31" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="E31" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="F31" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="G31" t="n">
+        <v>900781299.25</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>NAM</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D32" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="F32" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3108338702.96</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NER</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="E33" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="F33" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="G33" t="n">
+        <v>613708212.34</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>NGA</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="E34" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="F34" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1004758955.42</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>RWA</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D35" t="n">
+        <v>28.71</v>
+      </c>
+      <c r="E35" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="F35" t="n">
+        <v>22.88</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1150118515.52</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SEN</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="E36" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="F36" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1303126876.8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>STP</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C37" t="n">
+        <v>20</v>
+      </c>
+      <c r="D37" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="E37" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="F37" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="G37" t="n">
+        <v>989374.77</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SWZ</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D38" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="E38" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="F38" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1603658639.66</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SYC</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="D39" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="G39" t="n">
+        <v>402117461.92</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TGO</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="E40" t="n">
+        <v>11.27</v>
+      </c>
+      <c r="F40" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="G40" t="n">
+        <v>414699470.15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TZA</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D41" t="n">
+        <v>19.78</v>
+      </c>
+      <c r="E41" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="F41" t="n">
+        <v>17.23</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1210013969</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>UGA</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D42" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="E42" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="F42" t="n">
+        <v>24.73</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2473782299.73</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ZAF</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E43" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="F43" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="G43" t="n">
+        <v>8571329481.81</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ZMB</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="E44" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="F44" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="G44" t="n">
+        <v>3116458590.37</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ZWE</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C45" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="D45" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="E45" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F45" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="G45" t="n">
+        <v>4096558244.66</v>
       </c>
     </row>
   </sheetData>

--- a/Ejercicio-3/Parte-B/3.B.35/Code/datos/tablas_figuras.xlsx
+++ b/Ejercicio-3/Parte-B/3.B.35/Code/datos/tablas_figuras.xlsx
@@ -2535,11 +2535,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Exportaciones intrarregionales / totales (sin Kosovo)</t>
+          <t>Exportaciones intrarregionales / totales (sin Kosovo; corregido el 15/10/2026: la caché tenía a cero las ventas a Serbia y Montenegro de 2007-2011)</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>15.1</v>
+        <v>22.5</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2568,19 +2568,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Exportaciones intrarregionales / totales (sin Kosovo; mínimo)</t>
+          <t>Exportaciones intrarregionales / totales (sin Kosovo; desde 2015, en torno a)</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>13.2</v>
+        <v>15</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E66" t="n">
-        <v>2017</v>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2015-2023</t>
+        </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -53055,7 +53057,6 @@
       <c r="E7" t="n">
         <v>6</v>
       </c>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -53073,7 +53074,6 @@
       <c r="E8" t="n">
         <v>6</v>
       </c>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -53091,7 +53091,6 @@
       <c r="E9" t="n">
         <v>6</v>
       </c>
-      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -53109,7 +53108,6 @@
       <c r="E10" t="n">
         <v>6</v>
       </c>
-      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -53127,7 +53125,6 @@
       <c r="E11" t="n">
         <v>6</v>
       </c>
-      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -53145,7 +53142,6 @@
       <c r="E12" t="n">
         <v>6</v>
       </c>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -53163,7 +53159,6 @@
       <c r="E13" t="n">
         <v>6</v>
       </c>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -53181,7 +53176,6 @@
       <c r="E14" t="n">
         <v>6</v>
       </c>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -53199,7 +53193,6 @@
       <c r="E15" t="n">
         <v>6</v>
       </c>
-      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -53217,7 +53210,6 @@
       <c r="E16" t="n">
         <v>6</v>
       </c>
-      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -53235,7 +53227,6 @@
       <c r="E17" t="n">
         <v>6</v>
       </c>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -53253,7 +53244,6 @@
       <c r="E18" t="n">
         <v>6</v>
       </c>
-      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -53271,7 +53261,6 @@
       <c r="E19" t="n">
         <v>6</v>
       </c>
-      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -53289,7 +53278,6 @@
       <c r="E20" t="n">
         <v>6</v>
       </c>
-      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -53307,7 +53295,6 @@
       <c r="E21" t="n">
         <v>6</v>
       </c>
-      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -53325,7 +53312,6 @@
       <c r="E22" t="n">
         <v>6</v>
       </c>
-      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -53343,7 +53329,6 @@
       <c r="E23" t="n">
         <v>6</v>
       </c>
-      <c r="F23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Ejercicio-3/Parte-B/3.B.35/Code/datos/tablas_figuras.xlsx
+++ b/Ejercicio-3/Parte-B/3.B.35/Code/datos/tablas_figuras.xlsx
@@ -62,6 +62,8 @@
     <sheet name="MERCOSUR_complementariedad" sheetId="53" state="visible" r:id="rId53"/>
     <sheet name="MERCOSUR_saldos" sheetId="54" state="visible" r:id="rId54"/>
     <sheet name="MERCOSUR_reparto_manuf" sheetId="55" state="visible" r:id="rId55"/>
+    <sheet name="CCG_diversificacion" sheetId="56" state="visible" r:id="rId56"/>
+    <sheet name="CCG_seguridad" sheetId="57" state="visible" r:id="rId57"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -53335,6 +53337,2424 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Peso de los combustibles en las exportaciones de mercancías (%) y exportaciones de mercancías no combustibles (% del PIB) de los miembros del CCG</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Banco Mundial (WDI): TX.VAL.FUEL.ZS.UN (combustibles, sección 3 de la CUCI, a partir de UN Comtrade), TX.VAL.MRCH.CD.WT y NY.GDP.MKTP.CD. No combustibles = exportaciones de mercancías x (1 - parte de los combustibles). Las de Emiratos incluyen reexportaciones. Cálculo propio (Code/figuras_geoestrategicas.py).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Indicador</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Combustibles, % de las exportaciones</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>83.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Combustibles, % de las exportaciones</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="G6" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>80.59999999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Combustibles, % de las exportaciones</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>77.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Combustibles, % de las exportaciones</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>76.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Combustibles, % de las exportaciones</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="D9" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="G9" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>91.09999999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Combustibles, % de las exportaciones</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>91</v>
+      </c>
+      <c r="D10" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="F10" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="G10" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>91.8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Combustibles, % de las exportaciones</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>91</v>
+      </c>
+      <c r="D11" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="G11" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="H11" t="n">
+        <v>91.40000000000001</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Combustibles, % de las exportaciones</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="E12" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="G12" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="H12" t="n">
+        <v>89.09999999999999</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Combustibles, % de las exportaciones</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="D13" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="G13" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="H13" t="n">
+        <v>86.40000000000001</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Combustibles, % de las exportaciones</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="D14" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="G14" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="H14" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Combustibles, % de las exportaciones</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="D15" t="n">
+        <v>50</v>
+      </c>
+      <c r="E15" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="F15" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="G15" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>77.8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Combustibles, % de las exportaciones</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="F16" t="n">
+        <v>93</v>
+      </c>
+      <c r="G16" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="H16" t="n">
+        <v>74.40000000000001</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Combustibles, % de las exportaciones</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>88</v>
+      </c>
+      <c r="G17" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>83.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Combustibles, % de las exportaciones</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="D18" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="E18" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>90</v>
+      </c>
+      <c r="G18" t="n">
+        <v>59</v>
+      </c>
+      <c r="H18" t="n">
+        <v>82.59999999999999</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Combustibles, % de las exportaciones</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="E19" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="G19" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="H19" t="n">
+        <v>81.7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Combustibles, % de las exportaciones</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="D20" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="E20" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="G20" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>76.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Combustibles, % de las exportaciones</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="F21" t="n">
+        <v>85</v>
+      </c>
+      <c r="G21" t="n">
+        <v>45</v>
+      </c>
+      <c r="H21" t="n">
+        <v>76.09999999999999</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Combustibles, % de las exportaciones</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="D22" t="n">
+        <v>36</v>
+      </c>
+      <c r="E22" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="G22" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>73.7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Combustibles, % de las exportaciones</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>81</v>
+      </c>
+      <c r="D23" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="F23" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="G23" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="H23" t="n">
+        <v>75.2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Combustibles, % de las exportaciones</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="D24" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="E24" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="F24" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="G24" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>76.3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Combustibles, % de las exportaciones</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="D25" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="E25" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="F25" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="G25" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>63.6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Combustibles, % de las exportaciones</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="D26" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="F26" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>67.2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Combustibles, % de las exportaciones</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="E27" t="n">
+        <v>96</v>
+      </c>
+      <c r="F27" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Combustibles, % de las exportaciones</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H28" t="n">
+        <v>74.2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Combustibles, % de las exportaciones</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="E29" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>77.2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>No combustibles, % del PIB</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F30" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G30" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="H30" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>No combustibles, % del PIB</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G31" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H31" t="n">
+        <v>9.699999999999999</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>No combustibles, % del PIB</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" t="n">
+        <v>21</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H32" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>No combustibles, % del PIB</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D33" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G33" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H33" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>No combustibles, % del PIB</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F34" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="G34" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>No combustibles, % del PIB</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D35" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="F35" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="G35" t="n">
+        <v>14</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>No combustibles, % del PIB</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F36" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G36" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H36" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>No combustibles, % del PIB</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D37" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G37" t="n">
+        <v>12</v>
+      </c>
+      <c r="H37" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>No combustibles, % del PIB</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D38" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F38" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G38" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="H38" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>No combustibles, % del PIB</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D39" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F39" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G39" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="H39" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>No combustibles, % del PIB</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="D40" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="E40" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G40" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H40" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>No combustibles, % del PIB</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>6</v>
+      </c>
+      <c r="D41" t="n">
+        <v>38</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G41" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H41" t="n">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>No combustibles, % del PIB</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="D42" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="F42" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G42" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="H42" t="n">
+        <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>No combustibles, % del PIB</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F43" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G43" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="H43" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>No combustibles, % del PIB</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D44" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="E44" t="n">
+        <v>3</v>
+      </c>
+      <c r="F44" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G44" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="H44" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>No combustibles, % del PIB</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="D45" t="n">
+        <v>49</v>
+      </c>
+      <c r="E45" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F45" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="G45" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="H45" t="n">
+        <v>9.699999999999999</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>No combustibles, % del PIB</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>6</v>
+      </c>
+      <c r="D46" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="E46" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G46" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H46" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>No combustibles, % del PIB</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>6</v>
+      </c>
+      <c r="D47" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F47" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G47" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="H47" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>No combustibles, % del PIB</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="D48" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="E48" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F48" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G48" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="H48" t="n">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>No combustibles, % del PIB</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="D49" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F49" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G49" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="H49" t="n">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>No combustibles, % del PIB</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="D50" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F50" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G50" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H50" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>No combustibles, % del PIB</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="D51" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F51" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G51" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="H51" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>No combustibles, % del PIB</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="D52" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F52" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G52" t="n">
+        <v>65</v>
+      </c>
+      <c r="H52" t="n">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>No combustibles, % del PIB</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D53" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F53" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G53" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="H53" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>No combustibles, % del PIB</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>5</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F54" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G54" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="H54" t="n">
+        <v>13.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Peso de EE. UU., China, Europa y Rusia en las importaciones de armas de los seis miembros del CCG (TIV, sumas móviles de cinco años) y peso de EE. UU. y de China en sus exportaciones de mercancías (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SIPRI Arms Transfers Database (valores TIV de las transferencias de armas convencionales principales entregadas, consulta del 15/10/2026): suma de los seis receptores, cinco años hasta el indicado; Europa = Reino Unido, Francia, Alemania, Italia, España, Suecia, Bélgica, Países Bajos, Suiza, Austria, Finlandia, Bulgaria, Eslovaquia y Serbia. Exportaciones: datos espejo de WITS (importaciones declaradas por cada país desde los seis), Code/datos/espejo.csv. Cálculo propio (Code/figuras_geoestrategicas.py).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Armas: EE. UU. (%)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Armas: China (%)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Armas: Europa (%)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Armas: Rusia (%)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Armas: total (TIV, millones)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Exportaciones: EE. UU. (%)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Exportaciones: China (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1989</v>
+      </c>
+      <c r="B5" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D5" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B6" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>55</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3353</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B7" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>55</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B8" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B9" t="n">
+        <v>49</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3695</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B11" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B12" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="E12" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3957</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B13" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4555</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4024</v>
+      </c>
+      <c r="G14" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2279</v>
+      </c>
+      <c r="G15" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F16" t="n">
+        <v>997</v>
+      </c>
+      <c r="G16" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B17" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F17" t="n">
+        <v>372</v>
+      </c>
+      <c r="G17" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B18" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D18" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>896</v>
+      </c>
+      <c r="G18" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B19" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>914</v>
+      </c>
+      <c r="G19" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B20" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2363</v>
+      </c>
+      <c r="G20" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B21" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2494</v>
+      </c>
+      <c r="G21" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H21" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B22" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D22" t="n">
+        <v>52</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2497</v>
+      </c>
+      <c r="G22" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B23" t="n">
+        <v>51</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1402</v>
+      </c>
+      <c r="G23" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H23" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D24" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1217</v>
+      </c>
+      <c r="G24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H24" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B25" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1821</v>
+      </c>
+      <c r="G25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B26" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D26" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2005</v>
+      </c>
+      <c r="G26" t="n">
+        <v>7</v>
+      </c>
+      <c r="H26" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B27" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D27" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="E27" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2724</v>
+      </c>
+      <c r="G27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H27" t="n">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B28" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D28" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2491</v>
+      </c>
+      <c r="G28" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H28" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B29" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D29" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>7</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4726</v>
+      </c>
+      <c r="G29" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H29" t="n">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B30" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="E30" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4929</v>
+      </c>
+      <c r="G30" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H30" t="n">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B31" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D31" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F31" t="n">
+        <v>6141</v>
+      </c>
+      <c r="G31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H31" t="n">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D32" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5595</v>
+      </c>
+      <c r="G32" t="n">
+        <v>6</v>
+      </c>
+      <c r="H32" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F33" t="n">
+        <v>5943</v>
+      </c>
+      <c r="G33" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H33" t="n">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B34" t="n">
+        <v>64</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D34" t="n">
+        <v>29</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F34" t="n">
+        <v>5172</v>
+      </c>
+      <c r="G34" t="n">
+        <v>5</v>
+      </c>
+      <c r="H34" t="n">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B35" t="n">
+        <v>63</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D35" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F35" t="n">
+        <v>6177</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H35" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B36" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D36" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4162</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H36" t="n">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B37" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D37" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>6365</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H37" t="n">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B38" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D38" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F38" t="n">
+        <v>8977</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H38" t="n">
+        <v>18.9</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B39" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D39" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F39" t="n">
+        <v>5045</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H39" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B40" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D40" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4756</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B41" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D41" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>5305</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Ejercicio-3/Parte-B/3.B.35/Code/datos/tablas_figuras.xlsx
+++ b/Ejercicio-3/Parte-B/3.B.35/Code/datos/tablas_figuras.xlsx
@@ -53343,7 +53343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53356,7 +53356,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Banco Mundial (WDI): TX.VAL.FUEL.ZS.UN (combustibles, sección 3 de la CUCI, a partir de UN Comtrade), TX.VAL.MRCH.CD.WT y NY.GDP.MKTP.CD. No combustibles = exportaciones de mercancías x (1 - parte de los combustibles). Las de Emiratos incluyen reexportaciones. Cálculo propio (Code/figuras_geoestrategicas.py).</t>
+          <t>Datos espejo de WITS (Banco Mundial): importaciones declaradas por todos los países desde cada miembro, totales y del grupo «Fuels» (combustibles, capítulo 27 del SA), en dólares CIF (Code/descargas_geoestrategicas.py, Code/datos/espejo_productos.csv); PIB en dólares corrientes del Banco Mundial (WDI, NY.GDP.MKTP.CD). Se usan los datos espejo porque las series de WDI (TX.VAL.FUEL.ZS.UN) de Emiratos y Bahréin tienen saltos y ceros. Los importadores suelen anotar las reexportaciones con el país de origen, no con Emiratos. Cálculo propio (Code/figuras_geoestrategicas.py).</t>
         </is>
       </c>
     </row>
@@ -53412,22 +53412,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>92.3</v>
+        <v>89.5</v>
       </c>
       <c r="D5" t="n">
-        <v>93.8</v>
+        <v>77</v>
       </c>
       <c r="E5" t="n">
-        <v>94.3</v>
+        <v>100.7</v>
       </c>
       <c r="F5" t="n">
-        <v>91.2</v>
+        <v>90.2</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>49.2</v>
       </c>
       <c r="H5" t="n">
-        <v>83.2</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6">
@@ -53440,22 +53440,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>89.5</v>
+        <v>86.3</v>
       </c>
       <c r="D6" t="n">
-        <v>91.8</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>93.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>92.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="G6" t="n">
-        <v>66.90000000000001</v>
+        <v>42.9</v>
       </c>
       <c r="H6" t="n">
-        <v>80.59999999999999</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="7">
@@ -53468,22 +53468,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>89.59999999999999</v>
+        <v>84</v>
       </c>
       <c r="D7" t="n">
-        <v>55.7</v>
+        <v>67</v>
       </c>
       <c r="E7" t="n">
-        <v>92.5</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>89.3</v>
+        <v>87.8</v>
       </c>
       <c r="G7" t="n">
-        <v>69.40000000000001</v>
+        <v>37.4</v>
       </c>
       <c r="H7" t="n">
-        <v>77.5</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -53496,22 +53496,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>89.7</v>
+        <v>84.3</v>
       </c>
       <c r="D8" t="n">
-        <v>48.3</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>93.40000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="F8" t="n">
-        <v>92.3</v>
+        <v>86.8</v>
       </c>
       <c r="G8" t="n">
-        <v>72.5</v>
+        <v>36.1</v>
       </c>
       <c r="H8" t="n">
-        <v>76.8</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="9">
@@ -53524,22 +53524,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>89.8</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>54.1</v>
+        <v>60.7</v>
       </c>
       <c r="E9" t="n">
-        <v>94.59999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>87.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="G9" t="n">
-        <v>75.5</v>
+        <v>39.4</v>
       </c>
       <c r="H9" t="n">
-        <v>91.09999999999999</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="10">
@@ -53552,19 +53552,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>91</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>57.7</v>
+        <v>64.90000000000001</v>
+      </c>
+      <c r="E10" t="n">
+        <v>93.3</v>
       </c>
       <c r="F10" t="n">
-        <v>85.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="G10" t="n">
-        <v>78.2</v>
+        <v>44.7</v>
       </c>
       <c r="H10" t="n">
-        <v>91.8</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="11">
@@ -53577,22 +53580,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>91</v>
+        <v>87.5</v>
       </c>
       <c r="D11" t="n">
-        <v>62.3</v>
+        <v>72.2</v>
       </c>
       <c r="E11" t="n">
-        <v>96.5</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>90.90000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="G11" t="n">
-        <v>80.59999999999999</v>
+        <v>40.7</v>
       </c>
       <c r="H11" t="n">
-        <v>91.40000000000001</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="12">
@@ -53605,22 +53608,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>90.2</v>
+        <v>86.3</v>
       </c>
       <c r="D12" t="n">
-        <v>63.7</v>
+        <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>96.3</v>
+        <v>94.8</v>
       </c>
       <c r="F12" t="n">
-        <v>90.7</v>
+        <v>89.8</v>
       </c>
       <c r="G12" t="n">
-        <v>80.8</v>
+        <v>39.8</v>
       </c>
       <c r="H12" t="n">
-        <v>89.09999999999999</v>
+        <v>90.09999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -53633,22 +53636,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>91.40000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>62.3</v>
+        <v>72.2</v>
       </c>
       <c r="E13" t="n">
-        <v>96.5</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>92.09999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="G13" t="n">
-        <v>69.09999999999999</v>
+        <v>46.6</v>
       </c>
       <c r="H13" t="n">
-        <v>86.40000000000001</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="14">
@@ -53661,22 +53664,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>87.8</v>
+        <v>85.7</v>
       </c>
       <c r="D14" t="n">
-        <v>43.5</v>
+        <v>59.8</v>
       </c>
       <c r="E14" t="n">
-        <v>93.2</v>
+        <v>94</v>
       </c>
       <c r="F14" t="n">
-        <v>73.90000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>68.59999999999999</v>
+        <v>37.2</v>
       </c>
       <c r="H14" t="n">
-        <v>75</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="15">
@@ -53689,22 +53692,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>87.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>50</v>
+        <v>54.4</v>
       </c>
       <c r="E15" t="n">
-        <v>92.8</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>92.59999999999999</v>
+        <v>91</v>
       </c>
       <c r="G15" t="n">
-        <v>74.3</v>
+        <v>41.1</v>
       </c>
       <c r="H15" t="n">
-        <v>77.8</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="16">
@@ -53717,22 +53720,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>88.7</v>
+        <v>86</v>
       </c>
       <c r="D16" t="n">
-        <v>53.5</v>
+        <v>59.2</v>
       </c>
       <c r="E16" t="n">
-        <v>94.8</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>93</v>
+        <v>91.5</v>
       </c>
       <c r="G16" t="n">
-        <v>71.8</v>
+        <v>40.6</v>
       </c>
       <c r="H16" t="n">
-        <v>74.40000000000001</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="17">
@@ -53745,19 +53748,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>88.59999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="D17" t="n">
-        <v>47.2</v>
+        <v>60.7</v>
+      </c>
+      <c r="E17" t="n">
+        <v>93.8</v>
       </c>
       <c r="F17" t="n">
-        <v>88</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>64.09999999999999</v>
+        <v>50.1</v>
       </c>
       <c r="H17" t="n">
-        <v>83.5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18">
@@ -53770,22 +53776,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>87.59999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>55.8</v>
+        <v>59.6</v>
       </c>
       <c r="E18" t="n">
-        <v>94.2</v>
+        <v>92.7</v>
       </c>
       <c r="F18" t="n">
-        <v>90</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>59</v>
+        <v>46.8</v>
       </c>
       <c r="H18" t="n">
-        <v>82.59999999999999</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19">
@@ -53798,22 +53804,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>85.2</v>
+        <v>83.8</v>
       </c>
       <c r="D19" t="n">
-        <v>50.8</v>
+        <v>60.9</v>
       </c>
       <c r="E19" t="n">
-        <v>95.2</v>
+        <v>92.7</v>
       </c>
       <c r="F19" t="n">
-        <v>87.8</v>
+        <v>90.2</v>
       </c>
       <c r="G19" t="n">
-        <v>66.8</v>
+        <v>43.6</v>
       </c>
       <c r="H19" t="n">
-        <v>81.7</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="20">
@@ -53826,22 +53832,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>78.40000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>37.7</v>
+        <v>51.8</v>
       </c>
       <c r="E20" t="n">
-        <v>92.5</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>83.7</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>50.4</v>
+        <v>36.7</v>
       </c>
       <c r="H20" t="n">
-        <v>76.2</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="21">
@@ -53854,22 +53860,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>77.5</v>
+        <v>73.5</v>
       </c>
       <c r="D21" t="n">
-        <v>31.6</v>
+        <v>44.3</v>
       </c>
       <c r="E21" t="n">
-        <v>92.7</v>
+        <v>89.5</v>
       </c>
       <c r="F21" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G21" t="n">
-        <v>45</v>
+        <v>33.5</v>
       </c>
       <c r="H21" t="n">
-        <v>76.09999999999999</v>
+        <v>67.90000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -53882,22 +53888,22 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>79.8</v>
+        <v>75.5</v>
       </c>
       <c r="D22" t="n">
-        <v>36</v>
+        <v>47.1</v>
       </c>
       <c r="E22" t="n">
-        <v>93.59999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>87.59999999999999</v>
+        <v>85</v>
       </c>
       <c r="G22" t="n">
-        <v>50.2</v>
+        <v>40.6</v>
       </c>
       <c r="H22" t="n">
-        <v>73.7</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="23">
@@ -53910,22 +53916,22 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>81</v>
+        <v>77.8</v>
       </c>
       <c r="D23" t="n">
-        <v>68.5</v>
+        <v>53.4</v>
       </c>
       <c r="E23" t="n">
-        <v>90.90000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="F23" t="n">
-        <v>86.09999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>53.3</v>
+        <v>46.8</v>
       </c>
       <c r="H23" t="n">
-        <v>75.2</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="24">
@@ -53938,22 +53944,22 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>80.09999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="D24" t="n">
-        <v>77.8</v>
+        <v>51.7</v>
       </c>
       <c r="E24" t="n">
-        <v>94.40000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="F24" t="n">
-        <v>88.8</v>
+        <v>85</v>
       </c>
       <c r="G24" t="n">
-        <v>42.1</v>
+        <v>47.6</v>
       </c>
       <c r="H24" t="n">
-        <v>76.3</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="25">
@@ -53969,19 +53975,19 @@
         <v>72.59999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>71.40000000000001</v>
+        <v>43</v>
       </c>
       <c r="E25" t="n">
-        <v>92.90000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>81.8</v>
+        <v>80.8</v>
       </c>
       <c r="G25" t="n">
-        <v>29.8</v>
+        <v>34.7</v>
       </c>
       <c r="H25" t="n">
-        <v>63.6</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26">
@@ -53994,22 +54000,22 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>76.59999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="D26" t="n">
-        <v>70.3</v>
+        <v>48.7</v>
       </c>
       <c r="E26" t="n">
-        <v>94.59999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>84.40000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1</v>
+        <v>32.2</v>
       </c>
       <c r="H26" t="n">
-        <v>67.2</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -54022,22 +54028,22 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>82.2</v>
+        <v>80.7</v>
       </c>
       <c r="D27" t="n">
-        <v>74.40000000000001</v>
+        <v>60</v>
       </c>
       <c r="E27" t="n">
-        <v>96</v>
+        <v>93.8</v>
       </c>
       <c r="F27" t="n">
-        <v>87.3</v>
+        <v>86.5</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>36.1</v>
       </c>
       <c r="H27" t="n">
-        <v>74</v>
+        <v>71.59999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -54050,52 +54056,55 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>81.3</v>
+        <v>80.8</v>
       </c>
       <c r="D28" t="n">
-        <v>68.2</v>
+        <v>58.3</v>
       </c>
       <c r="E28" t="n">
-        <v>95.5</v>
+        <v>92.7</v>
       </c>
       <c r="F28" t="n">
-        <v>86.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3</v>
+        <v>41.4</v>
       </c>
       <c r="H28" t="n">
-        <v>74.2</v>
+        <v>71.09999999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2024</v>
+        <v>2000</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Combustibles, % de las exportaciones</t>
+          <t>No combustibles, % del PIB</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>79.40000000000001</v>
+        <v>4.4</v>
+      </c>
+      <c r="D29" t="n">
+        <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>94.2</v>
+        <v>-0.4</v>
       </c>
       <c r="F29" t="n">
-        <v>83.8</v>
+        <v>6.4</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="H29" t="n">
-        <v>77.2</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -54103,27 +54112,27 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
       <c r="D30" t="n">
-        <v>2.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="F30" t="n">
-        <v>5.7</v>
+        <v>7.7</v>
       </c>
       <c r="G30" t="n">
-        <v>68.3</v>
+        <v>19.3</v>
       </c>
       <c r="H30" t="n">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -54131,27 +54140,27 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
       <c r="D31" t="n">
-        <v>3.9</v>
+        <v>10.2</v>
       </c>
       <c r="E31" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>4.7</v>
+        <v>6.9</v>
       </c>
       <c r="G31" t="n">
-        <v>20.5</v>
+        <v>19.1</v>
       </c>
       <c r="H31" t="n">
-        <v>9.699999999999999</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -54159,27 +54168,27 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="D32" t="n">
-        <v>21</v>
+        <v>13.4</v>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="F32" t="n">
-        <v>6.1</v>
+        <v>7.9</v>
       </c>
       <c r="G32" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="H32" t="n">
-        <v>10.9</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -54187,27 +54196,27 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4.5</v>
+        <v>7.1</v>
       </c>
       <c r="D33" t="n">
-        <v>27.9</v>
+        <v>17</v>
       </c>
       <c r="E33" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="F33" t="n">
-        <v>4.4</v>
+        <v>8.4</v>
       </c>
       <c r="G33" t="n">
-        <v>16.5</v>
+        <v>18.4</v>
       </c>
       <c r="H33" t="n">
-        <v>10.9</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -54215,27 +54224,27 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="D34" t="n">
-        <v>28.3</v>
+        <v>16.7</v>
       </c>
       <c r="E34" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="F34" t="n">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="G34" t="n">
-        <v>14.1</v>
+        <v>19.4</v>
       </c>
       <c r="H34" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -54243,24 +54252,27 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4.9</v>
+        <v>6.9</v>
       </c>
       <c r="D35" t="n">
-        <v>27.4</v>
+        <v>12.9</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2.8</v>
       </c>
       <c r="F35" t="n">
-        <v>8.6</v>
+        <v>6.1</v>
       </c>
       <c r="G35" t="n">
-        <v>14</v>
+        <v>23.5</v>
       </c>
       <c r="H35" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -54268,27 +54280,27 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5.1</v>
+        <v>7.3</v>
       </c>
       <c r="D36" t="n">
-        <v>24.7</v>
+        <v>13</v>
       </c>
       <c r="E36" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="F36" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="G36" t="n">
-        <v>12.8</v>
+        <v>21</v>
       </c>
       <c r="H36" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -54296,27 +54308,27 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="D37" t="n">
-        <v>25.1</v>
+        <v>14.7</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F37" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G37" t="n">
-        <v>12</v>
+        <v>21.7</v>
       </c>
       <c r="H37" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -54324,27 +54336,27 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>28.6</v>
+        <v>17.1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="F38" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="G38" t="n">
-        <v>20.8</v>
+        <v>17.6</v>
       </c>
       <c r="H38" t="n">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -54352,27 +54364,27 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>5.5</v>
+        <v>7.7</v>
       </c>
       <c r="D39" t="n">
-        <v>42.7</v>
+        <v>24.5</v>
       </c>
       <c r="E39" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="F39" t="n">
-        <v>12.8</v>
+        <v>4.9</v>
       </c>
       <c r="G39" t="n">
-        <v>16.3</v>
+        <v>20.5</v>
       </c>
       <c r="H39" t="n">
-        <v>12.5</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -54380,27 +54392,27 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5.9</v>
+        <v>7.3</v>
       </c>
       <c r="D40" t="n">
-        <v>34.7</v>
+        <v>24.6</v>
       </c>
       <c r="E40" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="F40" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="G40" t="n">
-        <v>14.3</v>
+        <v>20</v>
       </c>
       <c r="H40" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -54408,27 +54420,27 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="D41" t="n">
-        <v>38</v>
+        <v>23.5</v>
       </c>
       <c r="E41" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="F41" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="G41" t="n">
-        <v>18.5</v>
+        <v>19.3</v>
       </c>
       <c r="H41" t="n">
-        <v>15.6</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -54436,24 +54448,27 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="D42" t="n">
-        <v>48.3</v>
+        <v>24.9</v>
+      </c>
+      <c r="E42" t="n">
+        <v>4.6</v>
       </c>
       <c r="F42" t="n">
-        <v>8.5</v>
+        <v>5.6</v>
       </c>
       <c r="G42" t="n">
-        <v>22.2</v>
+        <v>18.5</v>
       </c>
       <c r="H42" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -54461,27 +54476,27 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6.1</v>
+        <v>7.3</v>
       </c>
       <c r="D43" t="n">
-        <v>40.3</v>
+        <v>22</v>
       </c>
       <c r="E43" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="F43" t="n">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="G43" t="n">
-        <v>26.6</v>
+        <v>18.4</v>
       </c>
       <c r="H43" t="n">
-        <v>10.7</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -54489,27 +54504,27 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="D44" t="n">
-        <v>39.7</v>
+        <v>20.8</v>
       </c>
       <c r="E44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F44" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="G44" t="n">
-        <v>19.2</v>
+        <v>17.8</v>
       </c>
       <c r="H44" t="n">
-        <v>10</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -54517,27 +54532,27 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="D45" t="n">
-        <v>49</v>
+        <v>23.3</v>
       </c>
       <c r="E45" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="F45" t="n">
-        <v>7.9</v>
+        <v>5.9</v>
       </c>
       <c r="G45" t="n">
-        <v>25.2</v>
+        <v>15.4</v>
       </c>
       <c r="H45" t="n">
-        <v>9.699999999999999</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -54545,27 +54560,27 @@
         </is>
       </c>
       <c r="C46" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="D46" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E46" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F46" t="n">
         <v>6</v>
       </c>
-      <c r="D46" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="E46" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="F46" t="n">
-        <v>5.6</v>
-      </c>
       <c r="G46" t="n">
-        <v>20.7</v>
+        <v>16.5</v>
       </c>
       <c r="H46" t="n">
-        <v>9.6</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -54573,27 +54588,27 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="D47" t="n">
-        <v>49.8</v>
+        <v>22.9</v>
       </c>
       <c r="E47" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="F47" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="G47" t="n">
-        <v>20.6</v>
+        <v>18.8</v>
       </c>
       <c r="H47" t="n">
-        <v>10.7</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -54604,24 +54619,24 @@
         <v>6.3</v>
       </c>
       <c r="D48" t="n">
-        <v>27.7</v>
+        <v>24.3</v>
       </c>
       <c r="E48" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="F48" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="G48" t="n">
-        <v>21.3</v>
+        <v>19.1</v>
       </c>
       <c r="H48" t="n">
-        <v>11.3</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -54629,27 +54644,27 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="D49" t="n">
-        <v>19.9</v>
+        <v>28.4</v>
       </c>
       <c r="E49" t="n">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="F49" t="n">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="G49" t="n">
-        <v>25.9</v>
+        <v>20.8</v>
       </c>
       <c r="H49" t="n">
-        <v>10.4</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -54657,27 +54672,27 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="D50" t="n">
-        <v>26.8</v>
+        <v>31.9</v>
       </c>
       <c r="E50" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="F50" t="n">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="G50" t="n">
-        <v>27.5</v>
+        <v>27.7</v>
       </c>
       <c r="H50" t="n">
-        <v>16</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -54685,27 +54700,27 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="D51" t="n">
-        <v>29.9</v>
+        <v>28.2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="F51" t="n">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="G51" t="n">
-        <v>54.7</v>
+        <v>29.8</v>
       </c>
       <c r="H51" t="n">
-        <v>16.7</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -54713,75 +54728,22 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="D52" t="n">
-        <v>25.8</v>
+        <v>24.7</v>
       </c>
       <c r="E52" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="F52" t="n">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="G52" t="n">
-        <v>65</v>
+        <v>25.2</v>
       </c>
       <c r="H52" t="n">
-        <v>15.6</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>No combustibles, % del PIB</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="D53" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="E53" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="F53" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="G53" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="H53" t="n">
-        <v>14.3</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>No combustibles, % del PIB</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>5</v>
-      </c>
-      <c r="E54" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="F54" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="G54" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="H54" t="n">
-        <v>13.9</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Ejercicio-3/Parte-B/3.B.35/Code/datos/tablas_figuras.xlsx
+++ b/Ejercicio-3/Parte-B/3.B.35/Code/datos/tablas_figuras.xlsx
@@ -53417,9 +53417,6 @@
       <c r="D5" t="n">
         <v>77</v>
       </c>
-      <c r="E5" t="n">
-        <v>100.7</v>
-      </c>
       <c r="F5" t="n">
         <v>90.2</v>
       </c>
@@ -54088,9 +54085,6 @@
       </c>
       <c r="D29" t="n">
         <v>8</v>
-      </c>
-      <c r="E29" t="n">
-        <v>-0.4</v>
       </c>
       <c r="F29" t="n">
         <v>6.4</v>

--- a/Ejercicio-3/Parte-B/3.B.35/Code/datos/tablas_figuras.xlsx
+++ b/Ejercicio-3/Parte-B/3.B.35/Code/datos/tablas_figuras.xlsx
@@ -64,6 +64,7 @@
     <sheet name="MERCOSUR_reparto_manuf" sheetId="55" state="visible" r:id="rId55"/>
     <sheet name="CCG_diversificacion" sheetId="56" state="visible" r:id="rId56"/>
     <sheet name="CCG_seguridad" sheetId="57" state="visible" r:id="rId57"/>
+    <sheet name="CCG_complementariedad" sheetId="58" state="visible" r:id="rId58"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -55711,6 +55712,3278 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D183"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Complementariedad comercial (MICHAELY, 1996) entre los miembros del CCG y con China, la India y Japón</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>UN Comtrade, API pública, grupos de 3 dígitos de la CUCI (Rev. 3 en 2005 y Rev. 4 desde 2007): exportaciones del primer país y importaciones del segundo, con el mundo. Kuwait y Catar no declaran en 2005. Cálculo propio (Code/figuras_geoestrategicas.py).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Exportador</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Importador</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Índice (0-100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>48.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>37.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>52.7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>33.9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>50.1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>36.5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>34.1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>31.4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>40.1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>31.3</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>29.3</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>32.1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>31.6</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>31.6</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>31.1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>26.9</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>34.2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>30.9</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>17.1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>35.7</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>39.4</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>39.4</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>33.9</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>35.7</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>30.2</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>31.9</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>29.3</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>26.9</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>42.4</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>9.699999999999999</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>32.3</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>39.7</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>55.4</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>40.8</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>33.8</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>46.1</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>33.4</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>41.9</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>29.4</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>39.8</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>33.9</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>40.1</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>35.4</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>12.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Ejercicio-3/Parte-B/3.B.35/Code/datos/tablas_figuras.xlsx
+++ b/Ejercicio-3/Parte-B/3.B.35/Code/datos/tablas_figuras.xlsx
@@ -66,12 +66,12 @@
     <sheet name="CCG_complementariedad" sheetId="57" state="visible" r:id="rId57"/>
     <sheet name="ASEAN_fabrica" sheetId="58" state="visible" r:id="rId58"/>
     <sheet name="ASEAN_preferencia" sheetId="59" state="visible" r:id="rId59"/>
-    <sheet name="UEE_intrarregional" sheetId="60" state="visible" r:id="rId60"/>
-    <sheet name="UEE_intensidad" sheetId="61" state="visible" r:id="rId61"/>
-    <sheet name="UEE_remesas" sheetId="62" state="visible" r:id="rId62"/>
-    <sheet name="UEE_desvio" sheetId="63" state="visible" r:id="rId63"/>
-    <sheet name="RCEP_china" sheetId="64" state="visible" r:id="rId64"/>
-    <sheet name="RCEP_enlaces" sheetId="65" state="visible" r:id="rId65"/>
+    <sheet name="RCEP_china" sheetId="60" state="visible" r:id="rId60"/>
+    <sheet name="RCEP_enlaces" sheetId="61" state="visible" r:id="rId61"/>
+    <sheet name="UEE_intrarregional" sheetId="62" state="visible" r:id="rId62"/>
+    <sheet name="UEE_intensidad" sheetId="63" state="visible" r:id="rId63"/>
+    <sheet name="UEE_remesas" sheetId="64" state="visible" r:id="rId64"/>
+    <sheet name="UEE_desvio" sheetId="65" state="visible" r:id="rId65"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -64062,567 +64062,437 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Exportaciones intrarregionales del UEE: Unión Económica Euroasiática (composición actual): Rusia, Bielorrusia, Kazajistán, Armenia y Kirguistán. Rusia y Bielorrusia no publican su comercio desde 2022</t>
+          <t>Peso de China y de Japón en el comercio (exportaciones más importaciones) de cada miembro del RCEP, hacia 2000 y hacia 2023, y peso de cada miembro en el comercio de China (%)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Fuente: UN Comtrade (CUCI Rev. 1) (1962-1995) y WITS (Banco Mundial) a partir de UN Comtrade (desde 1996); exportaciones declaradas por el exportador, dólares corrientes. Cálculo propio (Code/datos_comercio.py).</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>La cuota solo se calcula cuando declaran todos los miembros; si falta alguno, se deja vacía.</t>
+          <t>WITS (Banco Mundial): exportaciones e importaciones declaradas por cada miembro por socio (2000, o 2001 si falta; 2023, o el último año disponible) y por China (2023). Cálculo propio (Code/figuras_geoestrategicas.py).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Miembro</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Año inicial</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>China, inicio (%)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Japón, inicio (%)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Año final</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>China, final (%)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Japón, final (%)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>El miembro en el comercio de China (%)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Año</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Exportaciones intrarregionales (millones USD)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Exportaciones totales (millones USD)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Cuota intrarregional (%)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Miembros con datos</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Faltan</t>
-        </is>
+          <t>LAO</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F5" t="n">
+        <v>33.69020810240913</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.883603530529259</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>1996</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AUS</t>
+        </is>
       </c>
       <c r="B6" t="n">
-        <v>9068.299999999999</v>
+        <v>2000</v>
       </c>
       <c r="C6" t="n">
-        <v>95106.89999999999</v>
+        <v>6.682911941496319</v>
+      </c>
+      <c r="D6" t="n">
+        <v>16.26755265612091</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>ARM, BLR</t>
-        </is>
+        <v>2023</v>
+      </c>
+      <c r="F6" t="n">
+        <v>29.22551651509064</v>
+      </c>
+      <c r="G6" t="n">
+        <v>8.263495744913985</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.87</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>1997</v>
-      </c>
-      <c r="B7" t="n">
-        <v>9812.1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>94069.89999999999</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MMR</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>BLR, KGZ</t>
-        </is>
+        <v>2023</v>
+      </c>
+      <c r="F7" t="n">
+        <v>27.31036914741853</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.484072002179941</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>1998</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KHM</t>
+        </is>
       </c>
       <c r="B8" t="n">
-        <v>13178.2</v>
+        <v>2000</v>
       </c>
       <c r="C8" t="n">
-        <v>84552.2</v>
+        <v>4.90288237831569</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.482487218108917</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ARM, KGZ</t>
-        </is>
+        <v>2023</v>
+      </c>
+      <c r="F8" t="n">
+        <v>26.67418860686435</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3.910517842186802</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>1999</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>IDN</t>
+        </is>
       </c>
       <c r="B9" t="n">
-        <v>9650.299999999999</v>
+        <v>2000</v>
       </c>
       <c r="C9" t="n">
-        <v>84896.89999999999</v>
+        <v>5.008092949723334</v>
+      </c>
+      <c r="D9" t="n">
+        <v>20.71591237029323</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>KGZ</t>
-        </is>
+        <v>2023</v>
+      </c>
+      <c r="F9" t="n">
+        <v>26.59164482170349</v>
+      </c>
+      <c r="G9" t="n">
+        <v>7.76080805559023</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.35</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>VNM</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>2000</v>
       </c>
-      <c r="B10" t="n">
-        <v>13623</v>
-      </c>
       <c r="C10" t="n">
-        <v>119901.8</v>
+        <v>9.753014688305134</v>
       </c>
       <c r="D10" t="n">
-        <v>11.36</v>
+        <v>16.189507025419</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>2023</v>
+      </c>
+      <c r="F10" t="n">
+        <v>25.2356297953493</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6.621200196898553</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.87</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NZL</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4.754082450426075</v>
+      </c>
+      <c r="D11" t="n">
+        <v>12.33289708769273</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F11" t="n">
+        <v>23.51425849558344</v>
+      </c>
+      <c r="G11" t="n">
+        <v>6.230328547018148</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>KOR</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C12" t="n">
+        <v>9.392509601918581</v>
+      </c>
+      <c r="D12" t="n">
+        <v>15.71559087111491</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F12" t="n">
+        <v>20.9918123221648</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6.014325689722008</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5.23</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PHL</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2.0493263688377</v>
+      </c>
+      <c r="D13" t="n">
+        <v>16.74025379034062</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F13" t="n">
+        <v>20.11938533535454</v>
+      </c>
+      <c r="G13" t="n">
+        <v>10.32827822192589</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C14" t="n">
+        <v>9.952327400743204</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F14" t="n">
+        <v>20.03795342710329</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5.36</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>THA</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4.731054823145715</v>
+      </c>
+      <c r="D15" t="n">
+        <v>19.42031690280892</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F15" t="n">
+        <v>18.3062661596693</v>
+      </c>
+      <c r="G15" t="n">
+        <v>9.726608470063967</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.13</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MYS</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.480001331949586</v>
+      </c>
+      <c r="D16" t="n">
+        <v>16.69077125430803</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F16" t="n">
+        <v>17.09558092359095</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5.939855735391522</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BRN</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
         <v>2001</v>
       </c>
-      <c r="B11" t="n">
-        <v>14177.2</v>
-      </c>
-      <c r="C11" t="n">
-        <v>116616.5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>12.16</v>
-      </c>
-      <c r="E11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>2002</v>
-      </c>
-      <c r="B12" t="n">
-        <v>14347.2</v>
-      </c>
-      <c r="C12" t="n">
-        <v>125343.1</v>
-      </c>
-      <c r="D12" t="n">
-        <v>11.45</v>
-      </c>
-      <c r="E12" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>2003</v>
-      </c>
-      <c r="B13" t="n">
-        <v>18522.2</v>
-      </c>
-      <c r="C13" t="n">
-        <v>157769.4</v>
-      </c>
-      <c r="D13" t="n">
-        <v>11.74</v>
-      </c>
-      <c r="E13" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>2004</v>
-      </c>
-      <c r="B14" t="n">
-        <v>26277.5</v>
-      </c>
-      <c r="C14" t="n">
-        <v>216872.7</v>
-      </c>
-      <c r="D14" t="n">
-        <v>12.12</v>
-      </c>
-      <c r="E14" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>2005</v>
-      </c>
-      <c r="B15" t="n">
-        <v>26733.4</v>
-      </c>
-      <c r="C15" t="n">
-        <v>286884</v>
-      </c>
-      <c r="D15" t="n">
-        <v>9.32</v>
-      </c>
-      <c r="E15" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>2006</v>
-      </c>
-      <c r="B16" t="n">
-        <v>34695.8</v>
-      </c>
-      <c r="C16" t="n">
-        <v>361331.7</v>
-      </c>
-      <c r="D16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="E16" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>2007</v>
-      </c>
-      <c r="B17" t="n">
-        <v>45167.6</v>
-      </c>
       <c r="C17" t="n">
-        <v>426544.9</v>
+        <v>3.936818784460854</v>
       </c>
       <c r="D17" t="n">
-        <v>10.59</v>
+        <v>36.55804395799926</v>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>2023</v>
+      </c>
+      <c r="F17" t="n">
+        <v>14.21000295325999</v>
+      </c>
+      <c r="G17" t="n">
+        <v>8.822173695478842</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>2008</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SGP</t>
+        </is>
       </c>
       <c r="B18" t="n">
-        <v>57540.8</v>
+        <v>2000</v>
       </c>
       <c r="C18" t="n">
-        <v>574409.3</v>
+        <v>4.588044148748678</v>
       </c>
       <c r="D18" t="n">
-        <v>10.02</v>
+        <v>12.32015920573376</v>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>2009</v>
-      </c>
-      <c r="B19" t="n">
-        <v>38929.8</v>
-      </c>
-      <c r="C19" t="n">
-        <v>368158.3</v>
-      </c>
-      <c r="D19" t="n">
-        <v>10.57</v>
-      </c>
-      <c r="E19" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>2010</v>
-      </c>
-      <c r="B20" t="n">
-        <v>44784</v>
-      </c>
-      <c r="C20" t="n">
-        <v>482094.9</v>
-      </c>
-      <c r="D20" t="n">
-        <v>9.289999999999999</v>
-      </c>
-      <c r="E20" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>2011</v>
-      </c>
-      <c r="B21" t="n">
-        <v>64947.6</v>
-      </c>
-      <c r="C21" t="n">
-        <v>649818.6</v>
-      </c>
-      <c r="D21" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="E21" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>2012</v>
-      </c>
-      <c r="B22" t="n">
-        <v>63979.8</v>
-      </c>
-      <c r="C22" t="n">
-        <v>666219.2</v>
-      </c>
-      <c r="D22" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="E22" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B23" t="n">
-        <v>61816.1</v>
-      </c>
-      <c r="C23" t="n">
-        <v>652408.5</v>
-      </c>
-      <c r="D23" t="n">
-        <v>9.48</v>
-      </c>
-      <c r="E23" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>2014</v>
-      </c>
-      <c r="B24" t="n">
-        <v>56792.3</v>
-      </c>
-      <c r="C24" t="n">
-        <v>616682.5</v>
-      </c>
-      <c r="D24" t="n">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="E24" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B25" t="n">
-        <v>41191.9</v>
-      </c>
-      <c r="C25" t="n">
-        <v>419446.6</v>
-      </c>
-      <c r="D25" t="n">
-        <v>9.82</v>
-      </c>
-      <c r="E25" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>2016</v>
-      </c>
-      <c r="B26" t="n">
-        <v>43710.3</v>
-      </c>
-      <c r="C26" t="n">
-        <v>365323.9</v>
-      </c>
-      <c r="D26" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="E26" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>2017</v>
-      </c>
-      <c r="B27" t="n">
-        <v>57159.4</v>
-      </c>
-      <c r="C27" t="n">
-        <v>460851.8</v>
-      </c>
-      <c r="D27" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="E27" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B28" t="n">
-        <v>59849.2</v>
-      </c>
-      <c r="C28" t="n">
-        <v>550547.9</v>
-      </c>
-      <c r="D28" t="n">
-        <v>10.87</v>
-      </c>
-      <c r="E28" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B29" t="n">
-        <v>61512.5</v>
-      </c>
-      <c r="C29" t="n">
-        <v>522345.5</v>
-      </c>
-      <c r="D29" t="n">
-        <v>11.78</v>
-      </c>
-      <c r="E29" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>2020</v>
-      </c>
-      <c r="B30" t="n">
-        <v>53760.3</v>
-      </c>
-      <c r="C30" t="n">
-        <v>412353.4</v>
-      </c>
-      <c r="D30" t="n">
-        <v>13.04</v>
-      </c>
-      <c r="E30" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B31" t="n">
-        <v>69980.60000000001</v>
-      </c>
-      <c r="C31" t="n">
-        <v>590988.5</v>
-      </c>
-      <c r="D31" t="n">
-        <v>11.84</v>
-      </c>
-      <c r="E31" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>ARM, BLR, KAZ, KGZ, RUS</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
         <v>2023</v>
       </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>ARM, BLR, KAZ, KGZ, RUS</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B34" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>ARM, BLR, KAZ, KGZ, RUS</t>
-        </is>
+      <c r="F18" t="n">
+        <v>13.85356366726853</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4.515627071106264</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.83</v>
       </c>
     </row>
   </sheetData>
@@ -64636,351 +64506,483 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Intensidad del comercio intrarregional. Unión Económica Euroasiática (composición actual): Rusia, Bielorrusia, Kazajistán, Armenia y Kirguistán. Rusia y Bielorrusia no publican su comercio desde 2022</t>
+          <t>Acuerdos de libre comercio en vigor entre las seis economías del RCEP antes de 2022 y aranceles aplicados entre China, Japón y Corea (%)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cuota: exportaciones a los socios / exportaciones totales (Code/datos_comercio.py). Peso: importaciones de mercancías de los miembros / importaciones mundiales (Banco Mundial, WDI, TM.VAL.MRCH.CD.WT). Intensidad = cuota / peso. Rusia y Bielorrusia no publican su comercio desde 2022, por lo que la serie acaba en 2021. Cálculo propio (Code/figuras_geoestrategicas.py).</t>
+          <t>Acuerdos: OMC (base de datos de acuerdos comerciales regionales) y textos de los acuerdos; año de entrada en vigor. Aranceles: WITS (Banco Mundial), tradestats-tariff, arancel aplicado efectivo (AHS) y de nación más favorecida (NMF) medios ponderados por el comercio, por socio. Cálculo propio (Code/figuras_geoestrategicas.py).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Año</t>
+          <t>Par o importador a origen</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cuota intrarregional (%)</t>
+          <t>Año o indicador</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Peso en las importaciones mundiales (%)</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Intensidad</t>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2023</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>2000</v>
-      </c>
-      <c r="B5" t="n">
-        <v>11.36</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.899</v>
-      </c>
-      <c r="D5" t="n">
-        <v>12.6</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ASEAN-China</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2005 ACFTA</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>2001</v>
-      </c>
-      <c r="B6" t="n">
-        <v>12.16</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1.0862</v>
-      </c>
-      <c r="D6" t="n">
-        <v>11.2</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ASEAN-Japón</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2008 AJCEP</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>2002</v>
-      </c>
-      <c r="B7" t="n">
-        <v>11.45</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1.1708</v>
-      </c>
-      <c r="D7" t="n">
-        <v>9.800000000000001</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ASEAN-Corea</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2007 AKFTA</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>2003</v>
-      </c>
-      <c r="B8" t="n">
-        <v>11.74</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1.257</v>
-      </c>
-      <c r="D8" t="n">
-        <v>9.300000000000001</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ASEAN-Australia</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2010 AANZFTA</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>2004</v>
-      </c>
-      <c r="B9" t="n">
-        <v>12.12</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.3565</v>
-      </c>
-      <c r="D9" t="n">
-        <v>8.9</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ASEAN-N. Zelanda</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2010 AANZFTA</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>2005</v>
-      </c>
-      <c r="B10" t="n">
-        <v>9.32</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1.4973</v>
-      </c>
-      <c r="D10" t="n">
-        <v>6.2</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>China-Japón</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>RCEP (2022)</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>2006</v>
-      </c>
-      <c r="B11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1.7239</v>
-      </c>
-      <c r="D11" t="n">
-        <v>5.6</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>China-Corea</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2015 bilateral</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>2007</v>
-      </c>
-      <c r="B12" t="n">
-        <v>10.59</v>
-      </c>
-      <c r="C12" t="n">
-        <v>2.0278</v>
-      </c>
-      <c r="D12" t="n">
-        <v>5.2</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>China-Australia</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2015 bilateral</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>2008</v>
-      </c>
-      <c r="B13" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2.2736</v>
-      </c>
-      <c r="D13" t="n">
-        <v>4.4</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>China-N. Zelanda</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2008 bilateral</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>2009</v>
-      </c>
-      <c r="B14" t="n">
-        <v>10.57</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1.9902</v>
-      </c>
-      <c r="D14" t="n">
-        <v>5.3</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Japón-Corea</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>RCEP (2022)</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>2010</v>
-      </c>
-      <c r="B15" t="n">
-        <v>9.289999999999999</v>
-      </c>
-      <c r="C15" t="n">
-        <v>2.0739</v>
-      </c>
-      <c r="D15" t="n">
-        <v>4.5</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Japón-Australia</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2015 bilateral</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>2011</v>
-      </c>
-      <c r="B16" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="C16" t="n">
-        <v>2.2416</v>
-      </c>
-      <c r="D16" t="n">
-        <v>4.5</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Japón-N. Zelanda</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2018 CPTPP</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>2012</v>
-      </c>
-      <c r="B17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="C17" t="n">
-        <v>2.337</v>
-      </c>
-      <c r="D17" t="n">
-        <v>4.1</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Corea-Australia</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2014 bilateral</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B18" t="n">
-        <v>9.48</v>
-      </c>
-      <c r="C18" t="n">
-        <v>2.329</v>
-      </c>
-      <c r="D18" t="n">
-        <v>4.1</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Corea-N. Zelanda</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2015 bilateral</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>2014</v>
-      </c>
-      <c r="B19" t="n">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="C19" t="n">
-        <v>2.0894</v>
-      </c>
-      <c r="D19" t="n">
-        <v>4.4</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Australia-N. Zelanda</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1983 ANZCERTA</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B20" t="n">
-        <v>9.82</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Japón a China</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>AHS</t>
+        </is>
       </c>
       <c r="C20" t="n">
-        <v>1.5543</v>
+        <v>2.47</v>
       </c>
       <c r="D20" t="n">
-        <v>6.3</v>
+        <v>2.98</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.97</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>2016</v>
-      </c>
-      <c r="B21" t="n">
-        <v>11.96</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Japón a China</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>NMF</t>
+        </is>
       </c>
       <c r="C21" t="n">
-        <v>1.5453</v>
+        <v>2.92</v>
       </c>
       <c r="D21" t="n">
-        <v>7.7</v>
+        <v>2.98</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.62</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>2017</v>
-      </c>
-      <c r="B22" t="n">
-        <v>12.4</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Japón a Corea</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>AHS</t>
+        </is>
       </c>
       <c r="C22" t="n">
-        <v>1.7229</v>
+        <v>1.81</v>
       </c>
       <c r="D22" t="n">
-        <v>7.2</v>
+        <v>4.92</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.3</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B23" t="n">
-        <v>10.87</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Japón a Corea</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NMF</t>
+        </is>
       </c>
       <c r="C23" t="n">
-        <v>1.6607</v>
+        <v>1.81</v>
       </c>
       <c r="D23" t="n">
-        <v>6.5</v>
+        <v>4.92</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.6</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B24" t="n">
-        <v>11.78</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>China a Japón</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>AHS</t>
+        </is>
       </c>
       <c r="C24" t="n">
-        <v>1.7621</v>
+        <v>6.09</v>
       </c>
       <c r="D24" t="n">
-        <v>6.7</v>
+        <v>4.75</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>2020</v>
-      </c>
-      <c r="B25" t="n">
-        <v>13.04</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>China a Japón</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NMF</t>
+        </is>
       </c>
       <c r="C25" t="n">
-        <v>1.7753</v>
+        <v>6.09</v>
       </c>
       <c r="D25" t="n">
-        <v>7.3</v>
+        <v>4.75</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.64</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B26" t="n">
-        <v>11.84</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Corea a Japón</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>AHS</t>
+        </is>
       </c>
       <c r="C26" t="n">
-        <v>1.7422</v>
+        <v>5.7</v>
       </c>
       <c r="D26" t="n">
-        <v>6.8</v>
+        <v>3.92</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Corea a Japón</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NMF</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="E27" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.13</v>
       </c>
     </row>
   </sheetData>
@@ -65000,61 +65002,54 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Remesas personales recibidas, % del PIB: miembros de la UEE con más emigración a Rusia y no miembros de Asia central</t>
+          <t>Exportaciones intrarregionales del UEE: Unión Económica Euroasiática (composición actual): Rusia, Bielorrusia, Kazajistán, Armenia y Kirguistán. Rusia y Bielorrusia no publican su comercio desde 2022</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Banco Mundial (WDI), BX.TRF.PWKR.DT.GD.ZS. Tayikistán y Uzbekistán no son miembros (Uzbekistán es observador).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+          <t>Fuente: UN Comtrade (CUCI Rev. 1) (1962-1995) y WITS (Banco Mundial) a partir de UN Comtrade (desde 1996); exportaciones declaradas por el exportador, dólares corrientes. Cálculo propio (Code/datos_comercio.py).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>La cuota solo se calcula cuando declaran todos los miembros; si falta alguno, se deja vacía.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>KGZ</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ARM</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>TJK</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>UZB</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>KAZ</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1995</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="C5" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.57</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Exportaciones intrarregionales (millones USD)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Exportaciones totales (millones USD)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Cuota intrarregional (%)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Miembros con datos</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Faltan</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -65062,13 +65057,18 @@
         <v>1996</v>
       </c>
       <c r="B6" t="n">
-        <v>0.13</v>
+        <v>9068.299999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>9.630000000000001</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.01</v>
+        <v>95106.89999999999</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ARM, BLR</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -65076,13 +65076,18 @@
         <v>1997</v>
       </c>
       <c r="B7" t="n">
-        <v>0.15</v>
+        <v>9812.1</v>
       </c>
       <c r="C7" t="n">
-        <v>13.97</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.01</v>
+        <v>94069.89999999999</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>BLR, KGZ</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -65090,13 +65095,18 @@
         <v>1998</v>
       </c>
       <c r="B8" t="n">
-        <v>0.13</v>
+        <v>13178.2</v>
       </c>
       <c r="C8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.03</v>
+        <v>84552.2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ARM, KGZ</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -65104,13 +65114,18 @@
         <v>1999</v>
       </c>
       <c r="B9" t="n">
-        <v>0.09</v>
+        <v>9650.299999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.02</v>
+        <v>84896.89999999999</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>KGZ</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -65118,13 +65133,16 @@
         <v>2000</v>
       </c>
       <c r="B10" t="n">
-        <v>0.16</v>
+        <v>13623</v>
       </c>
       <c r="C10" t="n">
-        <v>9.529999999999999</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.37</v>
+        <v>119901.8</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -65132,13 +65150,16 @@
         <v>2001</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3</v>
+        <v>14177.2</v>
       </c>
       <c r="C11" t="n">
-        <v>9.880000000000001</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.38</v>
+        <v>116616.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -65146,16 +65167,16 @@
         <v>2002</v>
       </c>
       <c r="B12" t="n">
-        <v>1.89</v>
+        <v>14347.2</v>
       </c>
       <c r="C12" t="n">
-        <v>11.1</v>
+        <v>125343.1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.45</v>
+        <v>11.45</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -65163,16 +65184,16 @@
         <v>2003</v>
       </c>
       <c r="B13" t="n">
-        <v>3.66</v>
+        <v>18522.2</v>
       </c>
       <c r="C13" t="n">
-        <v>11.96</v>
+        <v>157769.4</v>
       </c>
       <c r="D13" t="n">
-        <v>9.390000000000001</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.14</v>
+        <v>11.74</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -65180,16 +65201,16 @@
         <v>2004</v>
       </c>
       <c r="B14" t="n">
-        <v>8.1</v>
+        <v>26277.5</v>
       </c>
       <c r="C14" t="n">
-        <v>22.02</v>
+        <v>216872.7</v>
       </c>
       <c r="D14" t="n">
-        <v>12.14</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.13</v>
+        <v>12.12</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -65197,19 +65218,16 @@
         <v>2005</v>
       </c>
       <c r="B15" t="n">
-        <v>12.73</v>
+        <v>26733.4</v>
       </c>
       <c r="C15" t="n">
-        <v>18.68</v>
+        <v>286884</v>
       </c>
       <c r="D15" t="n">
-        <v>24.41</v>
+        <v>9.32</v>
       </c>
       <c r="E15" t="n">
-        <v>7.17</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -65217,19 +65235,16 @@
         <v>2006</v>
       </c>
       <c r="B16" t="n">
-        <v>16.69</v>
+        <v>34695.8</v>
       </c>
       <c r="C16" t="n">
-        <v>18.31</v>
+        <v>361331.7</v>
       </c>
       <c r="D16" t="n">
-        <v>34.48</v>
+        <v>9.6</v>
       </c>
       <c r="E16" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -65237,19 +65252,16 @@
         <v>2007</v>
       </c>
       <c r="B17" t="n">
-        <v>18.51</v>
+        <v>45167.6</v>
       </c>
       <c r="C17" t="n">
-        <v>17.86</v>
+        <v>426544.9</v>
       </c>
       <c r="D17" t="n">
-        <v>40.7</v>
+        <v>10.59</v>
       </c>
       <c r="E17" t="n">
-        <v>7.65</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -65257,19 +65269,16 @@
         <v>2008</v>
       </c>
       <c r="B18" t="n">
-        <v>23.8</v>
+        <v>57540.8</v>
       </c>
       <c r="C18" t="n">
-        <v>16.33</v>
+        <v>574409.3</v>
       </c>
       <c r="D18" t="n">
-        <v>44.13</v>
+        <v>10.02</v>
       </c>
       <c r="E18" t="n">
-        <v>12.28</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.09</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -65277,19 +65286,16 @@
         <v>2009</v>
       </c>
       <c r="B19" t="n">
-        <v>20.94</v>
+        <v>38929.8</v>
       </c>
       <c r="C19" t="n">
-        <v>16.65</v>
+        <v>368158.3</v>
       </c>
       <c r="D19" t="n">
-        <v>31.44</v>
+        <v>10.57</v>
       </c>
       <c r="E19" t="n">
-        <v>6.47</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -65297,19 +65303,16 @@
         <v>2010</v>
       </c>
       <c r="B20" t="n">
-        <v>26.41</v>
+        <v>44784</v>
       </c>
       <c r="C20" t="n">
-        <v>18.03</v>
+        <v>482094.9</v>
       </c>
       <c r="D20" t="n">
-        <v>35.81</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -65317,19 +65320,16 @@
         <v>2011</v>
       </c>
       <c r="B21" t="n">
-        <v>27.57</v>
+        <v>64947.6</v>
       </c>
       <c r="C21" t="n">
-        <v>17.73</v>
+        <v>649818.6</v>
       </c>
       <c r="D21" t="n">
-        <v>41.74</v>
+        <v>9.99</v>
       </c>
       <c r="E21" t="n">
-        <v>7.28</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.09</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -65337,19 +65337,16 @@
         <v>2012</v>
       </c>
       <c r="B22" t="n">
-        <v>30.75</v>
+        <v>63979.8</v>
       </c>
       <c r="C22" t="n">
-        <v>18.03</v>
+        <v>666219.2</v>
       </c>
       <c r="D22" t="n">
-        <v>42.22</v>
+        <v>9.6</v>
       </c>
       <c r="E22" t="n">
-        <v>8.08</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -65357,19 +65354,16 @@
         <v>2013</v>
       </c>
       <c r="B23" t="n">
-        <v>31.06</v>
+        <v>61816.1</v>
       </c>
       <c r="C23" t="n">
-        <v>19.71</v>
+        <v>652408.5</v>
       </c>
       <c r="D23" t="n">
-        <v>43.77</v>
+        <v>9.48</v>
       </c>
       <c r="E23" t="n">
-        <v>7.79</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -65377,19 +65371,16 @@
         <v>2014</v>
       </c>
       <c r="B24" t="n">
-        <v>30.03</v>
+        <v>56792.3</v>
       </c>
       <c r="C24" t="n">
-        <v>17.9</v>
+        <v>616682.5</v>
       </c>
       <c r="D24" t="n">
-        <v>37.14</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>7.46</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -65397,19 +65388,16 @@
         <v>2015</v>
       </c>
       <c r="B25" t="n">
-        <v>25.27</v>
+        <v>41191.9</v>
       </c>
       <c r="C25" t="n">
-        <v>14.13</v>
+        <v>419446.6</v>
       </c>
       <c r="D25" t="n">
-        <v>27.31</v>
+        <v>9.82</v>
       </c>
       <c r="E25" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -65417,19 +65405,16 @@
         <v>2016</v>
       </c>
       <c r="B26" t="n">
-        <v>29.28</v>
+        <v>43710.3</v>
       </c>
       <c r="C26" t="n">
-        <v>13.11</v>
+        <v>365323.9</v>
       </c>
       <c r="D26" t="n">
-        <v>26.71</v>
+        <v>11.96</v>
       </c>
       <c r="E26" t="n">
-        <v>5.92</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -65437,19 +65422,16 @@
         <v>2017</v>
       </c>
       <c r="B27" t="n">
-        <v>32.27</v>
+        <v>57159.4</v>
       </c>
       <c r="C27" t="n">
-        <v>13.35</v>
+        <v>460851.8</v>
       </c>
       <c r="D27" t="n">
-        <v>29.68</v>
+        <v>12.4</v>
       </c>
       <c r="E27" t="n">
-        <v>9.869999999999999</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -65457,19 +65439,16 @@
         <v>2018</v>
       </c>
       <c r="B28" t="n">
-        <v>32.51</v>
+        <v>59849.2</v>
       </c>
       <c r="C28" t="n">
-        <v>11.94</v>
+        <v>550547.9</v>
       </c>
       <c r="D28" t="n">
-        <v>28.12</v>
+        <v>10.87</v>
       </c>
       <c r="E28" t="n">
-        <v>12.41</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -65477,19 +65456,16 @@
         <v>2019</v>
       </c>
       <c r="B29" t="n">
-        <v>28.79</v>
+        <v>61512.5</v>
       </c>
       <c r="C29" t="n">
-        <v>11.22</v>
+        <v>522345.5</v>
       </c>
       <c r="D29" t="n">
-        <v>27.97</v>
+        <v>11.78</v>
       </c>
       <c r="E29" t="n">
-        <v>12.18</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -65497,19 +65473,16 @@
         <v>2020</v>
       </c>
       <c r="B30" t="n">
-        <v>31.81</v>
+        <v>53760.3</v>
       </c>
       <c r="C30" t="n">
-        <v>10.5</v>
+        <v>412353.4</v>
       </c>
       <c r="D30" t="n">
-        <v>26.88</v>
+        <v>13.04</v>
       </c>
       <c r="E30" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -65517,19 +65490,16 @@
         <v>2021</v>
       </c>
       <c r="B31" t="n">
-        <v>32.56</v>
+        <v>69980.60000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>11.22</v>
+        <v>590988.5</v>
       </c>
       <c r="D31" t="n">
-        <v>32.69</v>
+        <v>11.84</v>
       </c>
       <c r="E31" t="n">
-        <v>11.43</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
@@ -65537,19 +65507,18 @@
         <v>2022</v>
       </c>
       <c r="B32" t="n">
-        <v>26.92</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>10.87</v>
-      </c>
-      <c r="D32" t="n">
-        <v>49.9</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>16.45</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.21</v>
+        <v>0</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ARM, BLR, KAZ, KGZ, RUS</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -65557,19 +65526,18 @@
         <v>2023</v>
       </c>
       <c r="B33" t="n">
-        <v>18.86</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="D33" t="n">
-        <v>37.84</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>13.18</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.12</v>
+        <v>0</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ARM, BLR, KAZ, KGZ, RUS</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -65577,19 +65545,18 @@
         <v>2024</v>
       </c>
       <c r="B34" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>5.39</v>
-      </c>
-      <c r="D34" t="n">
-        <v>47.15</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>13.66</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.08</v>
+        <v>0</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ARM, BLR, KAZ, KGZ, RUS</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -65603,20 +65570,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Exportaciones de la UE-27 a Armenia, Kazajistán, Kirguistán y Rusia, y exportaciones de los tres primeros a Rusia (millones de USD)</t>
+          <t>Intensidad del comercio intrarregional. Unión Económica Euroasiática (composición actual): Rusia, Bielorrusia, Kazajistán, Armenia y Kirguistán. Rusia y Bielorrusia no publican su comercio desde 2022</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WITS (Banco Mundial): exportaciones declaradas por cada Estado de la UE-27 (sumadas) y por Armenia, Kazajistán y Kirguistán, dólares corrientes. Solo se suman los años en que declaran los 27. Cálculo propio (Code/figuras_geoestrategicas.py).</t>
+          <t>Cuota: exportaciones a los socios / exportaciones totales (Code/datos_comercio.py). Peso: importaciones de mercancías de los miembros / importaciones mundiales (Banco Mundial, WDI, TM.VAL.MRCH.CD.WT). Intensidad = cuota / peso. Rusia y Bielorrusia no publican su comercio desde 2022, por lo que la serie acaba en 2021. Cálculo propio (Code/figuras_geoestrategicas.py).</t>
         </is>
       </c>
     </row>
@@ -65628,168 +65595,326 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>UE-27 a ARM</t>
+          <t>Cuota intrarregional (%)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UE-27 a KAZ</t>
+          <t>Peso en las importaciones mundiales (%)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>UE-27 a KGZ</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>UE-27 a RUS</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>ARM a RUS</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>KAZ a RUS</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>KGZ a RUS</t>
+          <t>Intensidad</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2019</v>
+        <v>2000</v>
       </c>
       <c r="B5" t="n">
-        <v>865.1</v>
+        <v>11.36</v>
       </c>
       <c r="C5" t="n">
-        <v>6485</v>
+        <v>0.899</v>
       </c>
       <c r="D5" t="n">
-        <v>363.8</v>
-      </c>
-      <c r="E5" t="n">
-        <v>95429.2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>718.5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>5670.9</v>
-      </c>
-      <c r="H5" t="n">
-        <v>281.3</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2020</v>
+        <v>2001</v>
       </c>
       <c r="B6" t="n">
-        <v>811.7</v>
+        <v>12.16</v>
       </c>
       <c r="C6" t="n">
-        <v>6639.6</v>
+        <v>1.0862</v>
       </c>
       <c r="D6" t="n">
-        <v>280.9</v>
-      </c>
-      <c r="E6" t="n">
-        <v>87627</v>
-      </c>
-      <c r="F6" t="n">
-        <v>611</v>
-      </c>
-      <c r="G6" t="n">
-        <v>5007.1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>217.5</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2021</v>
+        <v>2002</v>
       </c>
       <c r="B7" t="n">
-        <v>885.1</v>
+        <v>11.45</v>
       </c>
       <c r="C7" t="n">
-        <v>6322.8</v>
+        <v>1.1708</v>
       </c>
       <c r="D7" t="n">
-        <v>299.9</v>
-      </c>
-      <c r="E7" t="n">
-        <v>101675.6</v>
-      </c>
-      <c r="F7" t="n">
-        <v>793.9</v>
-      </c>
-      <c r="G7" t="n">
-        <v>7018.8</v>
-      </c>
-      <c r="H7" t="n">
-        <v>392.4</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2022</v>
+        <v>2003</v>
       </c>
       <c r="B8" t="n">
-        <v>1941.5</v>
+        <v>11.74</v>
       </c>
       <c r="C8" t="n">
-        <v>10478.3</v>
+        <v>1.257</v>
       </c>
       <c r="D8" t="n">
-        <v>1210.6</v>
-      </c>
-      <c r="E8" t="n">
-        <v>56006.8</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2417</v>
-      </c>
-      <c r="G8" t="n">
-        <v>8780.700000000001</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1069.4</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2023</v>
+        <v>2004</v>
       </c>
       <c r="B9" t="n">
-        <v>2289.1</v>
+        <v>12.12</v>
       </c>
       <c r="C9" t="n">
-        <v>12674.2</v>
+        <v>1.3565</v>
       </c>
       <c r="D9" t="n">
-        <v>2827.4</v>
-      </c>
-      <c r="E9" t="n">
-        <v>39810.3</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3505.4</v>
-      </c>
-      <c r="G9" t="n">
-        <v>9788.200000000001</v>
-      </c>
-      <c r="H9" t="n">
-        <v>821.6</v>
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B10" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.4973</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.7239</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B12" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2.0278</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B13" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2.2736</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B14" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.9902</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B15" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2.0739</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B16" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2.2416</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2.337</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B18" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2.329</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B19" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2.0894</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B20" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.5543</v>
+      </c>
+      <c r="D20" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B21" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.5453</v>
+      </c>
+      <c r="D21" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B22" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.7229</v>
+      </c>
+      <c r="D22" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B23" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.6607</v>
+      </c>
+      <c r="D23" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B24" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.7621</v>
+      </c>
+      <c r="D24" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B25" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.7753</v>
+      </c>
+      <c r="D25" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B26" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.7422</v>
+      </c>
+      <c r="D26" t="n">
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -65803,437 +65928,602 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Peso de China y de Japón en el comercio (exportaciones más importaciones) de cada miembro del RCEP, hacia 2000 y hacia 2023, y peso de cada miembro en el comercio de China (%)</t>
+          <t>Remesas personales recibidas, % del PIB: miembros de la UEE con más emigración a Rusia y no miembros de Asia central</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WITS (Banco Mundial): exportaciones e importaciones declaradas por cada miembro por socio (2000, o 2001 si falta; 2023, o el último año disponible) y por China (2023). Cálculo propio (Code/figuras_geoestrategicas.py).</t>
+          <t>Banco Mundial (WDI), BX.TRF.PWKR.DT.GD.ZS. Tayikistán y Uzbekistán no son miembros (Uzbekistán es observador).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Miembro</t>
+          <t>Año</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Año inicial</t>
+          <t>KGZ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China, inicio (%)</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Japón, inicio (%)</t>
+          <t>TJK</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Año final</t>
+          <t>UZB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>China, final (%)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Japón, final (%)</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>El miembro en el comercio de China (%)</t>
+          <t>KAZ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>LAO</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
+      <c r="A5" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="C6" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C7" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="C8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="C9" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="C12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B13" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="C13" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="D13" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="D14" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B15" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="C15" t="n">
+        <v>18.68</v>
+      </c>
+      <c r="D15" t="n">
+        <v>24.41</v>
+      </c>
+      <c r="E15" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B16" t="n">
+        <v>16.69</v>
+      </c>
+      <c r="C16" t="n">
+        <v>18.31</v>
+      </c>
+      <c r="D16" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="E16" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B17" t="n">
+        <v>18.51</v>
+      </c>
+      <c r="C17" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="D17" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="E17" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B18" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="C18" t="n">
+        <v>16.33</v>
+      </c>
+      <c r="D18" t="n">
+        <v>44.13</v>
+      </c>
+      <c r="E18" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B19" t="n">
+        <v>20.94</v>
+      </c>
+      <c r="C19" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="D19" t="n">
+        <v>31.44</v>
+      </c>
+      <c r="E19" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B20" t="n">
+        <v>26.41</v>
+      </c>
+      <c r="C20" t="n">
+        <v>18.03</v>
+      </c>
+      <c r="D20" t="n">
+        <v>35.81</v>
+      </c>
+      <c r="E20" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B21" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="C21" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="D21" t="n">
+        <v>41.74</v>
+      </c>
+      <c r="E21" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B22" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="C22" t="n">
+        <v>18.03</v>
+      </c>
+      <c r="D22" t="n">
+        <v>42.22</v>
+      </c>
+      <c r="E22" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B23" t="n">
+        <v>31.06</v>
+      </c>
+      <c r="C23" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="D23" t="n">
+        <v>43.77</v>
+      </c>
+      <c r="E23" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B24" t="n">
+        <v>30.03</v>
+      </c>
+      <c r="C24" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="D24" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="E24" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B25" t="n">
+        <v>25.27</v>
+      </c>
+      <c r="C25" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="D25" t="n">
+        <v>27.31</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B26" t="n">
+        <v>29.28</v>
+      </c>
+      <c r="C26" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="D26" t="n">
+        <v>26.71</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B27" t="n">
+        <v>32.27</v>
+      </c>
+      <c r="C27" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="D27" t="n">
+        <v>29.68</v>
+      </c>
+      <c r="E27" t="n">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B28" t="n">
+        <v>32.51</v>
+      </c>
+      <c r="C28" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="D28" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="E28" t="n">
+        <v>12.41</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B29" t="n">
+        <v>28.79</v>
+      </c>
+      <c r="C29" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="D29" t="n">
+        <v>27.97</v>
+      </c>
+      <c r="E29" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B30" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="C30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D30" t="n">
+        <v>26.88</v>
+      </c>
+      <c r="E30" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B31" t="n">
+        <v>32.56</v>
+      </c>
+      <c r="C31" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="D31" t="n">
+        <v>32.69</v>
+      </c>
+      <c r="E31" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B32" t="n">
+        <v>26.92</v>
+      </c>
+      <c r="C32" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="D32" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="E32" t="n">
+        <v>16.45</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
         <v>2023</v>
       </c>
-      <c r="F5" t="n">
-        <v>33.69020810240913</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.883603530529259</v>
-      </c>
-      <c r="H5" t="n">
+      <c r="B33" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="C33" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="D33" t="n">
+        <v>37.84</v>
+      </c>
+      <c r="E33" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="F33" t="n">
         <v>0.12</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AUS</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C6" t="n">
-        <v>6.682911941496319</v>
-      </c>
-      <c r="D6" t="n">
-        <v>16.26755265612091</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F6" t="n">
-        <v>29.22551651509064</v>
-      </c>
-      <c r="G6" t="n">
-        <v>8.263495744913985</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3.87</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>MMR</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F7" t="n">
-        <v>27.31036914741853</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4.484072002179941</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>KHM</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C8" t="n">
-        <v>4.90288237831569</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2.482487218108917</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F8" t="n">
-        <v>26.67418860686435</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3.910517842186802</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>IDN</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C9" t="n">
-        <v>5.008092949723334</v>
-      </c>
-      <c r="D9" t="n">
-        <v>20.71591237029323</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F9" t="n">
-        <v>26.59164482170349</v>
-      </c>
-      <c r="G9" t="n">
-        <v>7.76080805559023</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.35</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>VNM</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C10" t="n">
-        <v>9.753014688305134</v>
-      </c>
-      <c r="D10" t="n">
-        <v>16.189507025419</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F10" t="n">
-        <v>25.2356297953493</v>
-      </c>
-      <c r="G10" t="n">
-        <v>6.621200196898553</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3.87</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>NZL</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C11" t="n">
-        <v>4.754082450426075</v>
-      </c>
-      <c r="D11" t="n">
-        <v>12.33289708769273</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F11" t="n">
-        <v>23.51425849558344</v>
-      </c>
-      <c r="G11" t="n">
-        <v>6.230328547018148</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>KOR</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C12" t="n">
-        <v>9.392509601918581</v>
-      </c>
-      <c r="D12" t="n">
-        <v>15.71559087111491</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F12" t="n">
-        <v>20.9918123221648</v>
-      </c>
-      <c r="G12" t="n">
-        <v>6.014325689722008</v>
-      </c>
-      <c r="H12" t="n">
-        <v>5.23</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>PHL</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2.0493263688377</v>
-      </c>
-      <c r="D13" t="n">
-        <v>16.74025379034062</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F13" t="n">
-        <v>20.11938533535454</v>
-      </c>
-      <c r="G13" t="n">
-        <v>10.32827822192589</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.21</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>JPN</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C14" t="n">
-        <v>9.952327400743204</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F14" t="n">
-        <v>20.03795342710329</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>5.36</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>THA</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C15" t="n">
-        <v>4.731054823145715</v>
-      </c>
-      <c r="D15" t="n">
-        <v>19.42031690280892</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F15" t="n">
-        <v>18.3062661596693</v>
-      </c>
-      <c r="G15" t="n">
-        <v>9.726608470063967</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2.13</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>MYS</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.480001331949586</v>
-      </c>
-      <c r="D16" t="n">
-        <v>16.69077125430803</v>
-      </c>
-      <c r="E16" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F16" t="n">
-        <v>17.09558092359095</v>
-      </c>
-      <c r="G16" t="n">
-        <v>5.939855735391522</v>
-      </c>
-      <c r="H16" t="n">
-        <v>3.21</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>BRN</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2001</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.936818784460854</v>
-      </c>
-      <c r="D17" t="n">
-        <v>36.55804395799926</v>
-      </c>
-      <c r="E17" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F17" t="n">
-        <v>14.21000295325999</v>
-      </c>
-      <c r="G17" t="n">
-        <v>8.822173695478842</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>SGP</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C18" t="n">
-        <v>4.588044148748678</v>
-      </c>
-      <c r="D18" t="n">
-        <v>12.32015920573376</v>
-      </c>
-      <c r="E18" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F18" t="n">
-        <v>13.85356366726853</v>
-      </c>
-      <c r="G18" t="n">
-        <v>4.515627071106264</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.83</v>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B34" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="C34" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="D34" t="n">
+        <v>47.15</v>
+      </c>
+      <c r="E34" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>
@@ -66247,483 +66537,193 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Acuerdos de libre comercio en vigor entre las seis economías del RCEP antes de 2022 y aranceles aplicados entre China, Japón y Corea (%)</t>
+          <t>Exportaciones de la UE-27 a Armenia, Kazajistán, Kirguistán y Rusia, y exportaciones de los tres primeros a Rusia (millones de USD)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Acuerdos: OMC (base de datos de acuerdos comerciales regionales) y textos de los acuerdos; año de entrada en vigor. Aranceles: WITS (Banco Mundial), tradestats-tariff, arancel aplicado efectivo (AHS) y de nación más favorecida (NMF) medios ponderados por el comercio, por socio. Cálculo propio (Code/figuras_geoestrategicas.py).</t>
+          <t>WITS (Banco Mundial): exportaciones declaradas por cada Estado de la UE-27 (sumadas) y por Armenia, Kazajistán y Kirguistán, dólares corrientes. Solo se suman los años en que declaran los 27. Cálculo propio (Code/figuras_geoestrategicas.py).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Par o importador a origen</t>
+          <t>Año</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Año o indicador</t>
+          <t>UE-27 a ARM</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>UE-27 a KAZ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>UE-27 a KGZ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>UE-27 a RUS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>ARM a RUS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>KAZ a RUS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>KGZ a RUS</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ASEAN-China</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2005 ACFTA</t>
-        </is>
+      <c r="A5" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B5" t="n">
+        <v>865.1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>6485</v>
+      </c>
+      <c r="D5" t="n">
+        <v>363.8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>95429.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>718.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5670.9</v>
+      </c>
+      <c r="H5" t="n">
+        <v>281.3</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ASEAN-Japón</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2008 AJCEP</t>
-        </is>
+      <c r="A6" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B6" t="n">
+        <v>811.7</v>
+      </c>
+      <c r="C6" t="n">
+        <v>6639.6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>280.9</v>
+      </c>
+      <c r="E6" t="n">
+        <v>87627</v>
+      </c>
+      <c r="F6" t="n">
+        <v>611</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5007.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>217.5</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ASEAN-Corea</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2007 AKFTA</t>
-        </is>
+      <c r="A7" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B7" t="n">
+        <v>885.1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>6322.8</v>
+      </c>
+      <c r="D7" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="E7" t="n">
+        <v>101675.6</v>
+      </c>
+      <c r="F7" t="n">
+        <v>793.9</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7018.8</v>
+      </c>
+      <c r="H7" t="n">
+        <v>392.4</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ASEAN-Australia</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2010 AANZFTA</t>
-        </is>
+      <c r="A8" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1941.5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>10478.3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1210.6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>56006.8</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2417</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8780.700000000001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1069.4</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ASEAN-N. Zelanda</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2010 AANZFTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>China-Japón</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>RCEP (2022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>China-Corea</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2015 bilateral</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>China-Australia</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2015 bilateral</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>China-N. Zelanda</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2008 bilateral</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Japón-Corea</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>RCEP (2022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Japón-Australia</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2015 bilateral</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Japón-N. Zelanda</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2018 CPTPP</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Corea-Australia</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2014 bilateral</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Corea-N. Zelanda</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2015 bilateral</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Australia-N. Zelanda</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1983 ANZCERTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Japón a China</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>AHS</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="D20" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="E20" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="F20" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="G20" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.97</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Japón a China</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>NMF</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="E21" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="G21" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="H21" t="n">
-        <v>2.62</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Japón a Corea</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>AHS</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="D22" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="E22" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Japón a Corea</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>NMF</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="D23" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>China a Japón</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>AHS</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="D24" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="E24" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="F24" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="G24" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="H24" t="n">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>China a Japón</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>NMF</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="D25" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="E25" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="F25" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="G25" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="H25" t="n">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Corea a Japón</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>AHS</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="D26" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="E26" t="n">
-        <v>5.54</v>
-      </c>
-      <c r="F26" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="G26" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="H26" t="n">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Corea a Japón</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>NMF</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="D27" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="E27" t="n">
-        <v>5.54</v>
-      </c>
-      <c r="F27" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="G27" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="H27" t="n">
-        <v>3.13</v>
+      <c r="A9" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2289.1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>12674.2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2827.4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>39810.3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3505.4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>9788.200000000001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>821.6</v>
       </c>
     </row>
   </sheetData>

--- a/Ejercicio-3/Parte-B/3.B.35/Code/datos/tablas_figuras.xlsx
+++ b/Ejercicio-3/Parte-B/3.B.35/Code/datos/tablas_figuras.xlsx
@@ -73,6 +73,7 @@
     <sheet name="RCEP_china" sheetId="64" state="visible" r:id="rId64"/>
     <sheet name="RCEP_enlaces" sheetId="65" state="visible" r:id="rId65"/>
     <sheet name="RCEP_acuerdos" sheetId="66" state="visible" r:id="rId66"/>
+    <sheet name="UE_peso_mutuo" sheetId="67" state="visible" r:id="rId67"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -67361,6 +67362,524 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Peso mutuo entre la UE y cada proceso de integración, comercio de mercancías, 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>WITS (Banco Mundial): exportaciones e importaciones declaradas por los 27 Estados miembros con cada socio; Banco Mundial (WDI): exportaciones e importaciones totales de mercancías de los miembros de cada bloque. Peso para la UE = comercio con el bloque / comercio con fuera de la UE; peso para el bloque = comercio con la UE / comercio total del bloque (aproximado: importaciones de la UE CIF, exportaciones del bloque FOB). Cálculo propio (Code/relacion_ue.py).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bloque</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>El bloque en el comercio exterior de la UE (%)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>En las exportaciones de la UE (%)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>En las importaciones de la UE (%)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>La UE en el comercio del bloque (%)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Exportaciones de la UE (miles de millones de USD)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Importaciones de la UE (miles de millones de USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MCCA (con Panamá)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="G5" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>EFTA</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="D7" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="F7" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>271.1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>271.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NAFTA/USMCA</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>23.06</v>
+      </c>
+      <c r="E8" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="F8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>634</v>
+      </c>
+      <c r="H8" t="n">
+        <v>452.9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MERCOSUR</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="G9" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="H9" t="n">
+        <v>58.3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CEFTA</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F10" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="G10" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AfCFTA</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="E11" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="F11" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="G11" t="n">
+        <v>175.2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>211.4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PAFTA</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="D12" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="E12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="F12" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>204.7</v>
+      </c>
+      <c r="H12" t="n">
+        <v>221.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ASEAN</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E13" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="F13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="G13" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="H13" t="n">
+        <v>189.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CCG</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F14" t="n">
+        <v>9</v>
+      </c>
+      <c r="G14" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>80.59999999999999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>RCEP</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>26.12</v>
+      </c>
+      <c r="D15" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>33.41</v>
+      </c>
+      <c r="F15" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G15" t="n">
+        <v>505.9</v>
+      </c>
+      <c r="H15" t="n">
+        <v>972.8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CPTPP</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>20.21</v>
+      </c>
+      <c r="D16" t="n">
+        <v>23.51</v>
+      </c>
+      <c r="E16" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="F16" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="G16" t="n">
+        <v>646.2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>497.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>UEE</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="F17" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="G17" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>87.59999999999999</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>EE. UU. (referencia)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="D18" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="E18" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="F18" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="G18" t="n">
+        <v>528.1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>391.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>China (referencia)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="D19" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="E19" t="n">
+        <v>20.41</v>
+      </c>
+      <c r="F19" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="G19" t="n">
+        <v>233.4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>594.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Reino Unido (referencia)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="D20" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="E20" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="F20" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="G20" t="n">
+        <v>350.4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>199.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
